--- a/thesis-recommendation-dataset.xlsx
+++ b/thesis-recommendation-dataset.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="270">
   <si>
     <t>PWD ID</t>
   </si>
@@ -550,16 +550,19 @@
     <t>Points for how the applicant's highest education compares to the job's minimum requirement.</t>
   </si>
   <si>
-    <t>Weight: Location</t>
-  </si>
-  <si>
-    <t>Points for proximity: remote &gt; same barangay &gt; same municipality &gt; same province &gt; far.</t>
-  </si>
-  <si>
-    <t>Weight: Preference</t>
-  </si>
-  <si>
-    <t>Points for matching the applicant's preferred employment type and work arrangement.</t>
+    <t>Location (not scored)</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Proximity is computed but only drives the Jobs page location filter — it no longer earns or costs match-score points.</t>
+  </si>
+  <si>
+    <t>Preference (not scored)</t>
+  </si>
+  <si>
+    <t>Preferred employment type / work arrangement no longer affect the match score.</t>
   </si>
   <si>
     <t>Minimum match score</t>
@@ -619,7 +622,7 @@
     <t>Skill Coverage (0-1)</t>
   </si>
   <si>
-    <t>Skills Points (/35)</t>
+    <t>Skills Points (/47)</t>
   </si>
   <si>
     <t>Disability Listed?</t>
@@ -631,7 +634,7 @@
     <t>Accommodations Unmet</t>
   </si>
   <si>
-    <t>Suitability Points (/25)</t>
+    <t>Suitability Points (/33)</t>
   </si>
   <si>
     <t>Education Status</t>
@@ -640,19 +643,13 @@
     <t>Education Fraction (0-1)</t>
   </si>
   <si>
-    <t>Education Points (/15)</t>
-  </si>
-  <si>
-    <t>Location Level</t>
-  </si>
-  <si>
-    <t>Location Fraction (0-1)</t>
-  </si>
-  <si>
-    <t>Location Points (/15)</t>
-  </si>
-  <si>
-    <t>Preference Points (/10)</t>
+    <t>Education Points (/20)</t>
+  </si>
+  <si>
+    <t>Location Level (filter only, not scored)</t>
+  </si>
+  <si>
+    <t>Location Fraction (filter only, not scored)</t>
   </si>
   <si>
     <t>TOTAL SCORE (0-100)</t>
@@ -697,6 +694,9 @@
     <t>HTML, CSS</t>
   </si>
   <si>
+    <t>Fair</t>
+  </si>
+  <si>
     <t>Communication</t>
   </si>
   <si>
@@ -712,15 +712,15 @@
     <t>remote</t>
   </si>
   <si>
+    <t>Microsoft Office, Computer Literacy, Customer Service</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
     <t>Excellent</t>
   </si>
   <si>
-    <t>Microsoft Office, Computer Literacy, Customer Service</t>
-  </si>
-  <si>
-    <t>Administration</t>
-  </si>
-  <si>
     <t>Communication, Customer Service, Computer Literacy</t>
   </si>
   <si>
@@ -740,9 +740,6 @@
   </si>
   <si>
     <t>Accounting, Bookkeeping</t>
-  </si>
-  <si>
-    <t>Fair</t>
   </si>
   <si>
     <t>barangay</t>
@@ -2207,7 +2204,7 @@
         <v>172</v>
       </c>
       <c r="B2">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
         <v>173</v>
@@ -2218,7 +2215,7 @@
         <v>174</v>
       </c>
       <c r="B3">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
         <v>175</v>
@@ -2229,7 +2226,7 @@
         <v>176</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
         <v>177</v>
@@ -2239,66 +2236,66 @@
       <c r="A5" t="s">
         <v>178</v>
       </c>
-      <c r="B5">
-        <v>15</v>
+      <c r="B5" t="s">
+        <v>179</v>
       </c>
       <c r="C5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B6">
-        <v>10</v>
+        <v>181</v>
+      </c>
+      <c r="B6" t="s">
+        <v>179</v>
       </c>
       <c r="C6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B7">
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2309,7 +2306,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA92"/>
+  <dimension ref="A1:Y92"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2324,19 +2321,18 @@
     <col min="14" max="15" width="26" customWidth="1"/>
     <col min="16" max="18" width="14" customWidth="1"/>
     <col min="19" max="19" width="12" customWidth="1"/>
-    <col min="20" max="20" width="14" customWidth="1"/>
-    <col min="21" max="23" width="12" customWidth="1"/>
-    <col min="24" max="24" width="14" customWidth="1"/>
-    <col min="25" max="25" width="12" customWidth="1"/>
-    <col min="26" max="27" width="14" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1"/>
+    <col min="21" max="22" width="14" customWidth="1"/>
+    <col min="23" max="23" width="12" customWidth="1"/>
+    <col min="24" max="25" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
@@ -2345,76 +2341,70 @@
         <v>82</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="AA1" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -2431,73 +2421,67 @@
         <v>96</v>
       </c>
       <c r="F2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
         <v>217</v>
       </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" t="s">
         <v>218</v>
-      </c>
-      <c r="I2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J2" t="s">
-        <v>219</v>
       </c>
       <c r="K2">
         <v>0.75</v>
       </c>
       <c r="L2">
-        <v>26.25</v>
+        <v>35.25</v>
       </c>
       <c r="M2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N2" t="s">
         <v>101</v>
       </c>
       <c r="O2" t="s">
+        <v>219</v>
+      </c>
+      <c r="P2">
+        <v>14.63</v>
+      </c>
+      <c r="Q2" t="s">
         <v>220</v>
       </c>
-      <c r="P2">
-        <v>11.08</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>20</v>
+      </c>
+      <c r="T2" t="s">
         <v>221</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>15</v>
-      </c>
-      <c r="T2" t="s">
-        <v>222</v>
       </c>
       <c r="U2">
         <v>0.7</v>
       </c>
       <c r="V2">
-        <v>10.5</v>
-      </c>
-      <c r="W2">
-        <v>10</v>
-      </c>
-      <c r="X2">
-        <v>73</v>
+        <v>70</v>
+      </c>
+      <c r="W2" t="s">
+        <v>222</v>
+      </c>
+      <c r="X2" t="s">
+        <v>25</v>
       </c>
       <c r="Y2" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -2514,73 +2498,67 @@
         <v>105</v>
       </c>
       <c r="F3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G3" t="s">
         <v>25</v>
       </c>
       <c r="H3" t="s">
+        <v>223</v>
+      </c>
+      <c r="I3" t="s">
         <v>224</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>225</v>
-      </c>
-      <c r="J3" t="s">
-        <v>226</v>
       </c>
       <c r="K3">
         <v>0.48</v>
       </c>
       <c r="L3">
-        <v>16.8</v>
+        <v>22.56</v>
       </c>
       <c r="M3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N3" t="s">
         <v>101</v>
       </c>
       <c r="O3" t="s">
+        <v>219</v>
+      </c>
+      <c r="P3">
+        <v>14.63</v>
+      </c>
+      <c r="Q3" t="s">
         <v>220</v>
       </c>
-      <c r="P3">
-        <v>11.08</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>20</v>
+      </c>
+      <c r="T3" t="s">
         <v>221</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3">
-        <v>15</v>
-      </c>
-      <c r="T3" t="s">
-        <v>222</v>
       </c>
       <c r="U3">
         <v>0.7</v>
       </c>
       <c r="V3">
-        <v>10.5</v>
-      </c>
-      <c r="W3">
-        <v>10</v>
-      </c>
-      <c r="X3">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="W3" t="s">
+        <v>226</v>
+      </c>
+      <c r="X3" t="s">
+        <v>25</v>
       </c>
       <c r="Y3" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -2597,7 +2575,7 @@
         <v>109</v>
       </c>
       <c r="F4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G4" t="s">
         <v>25</v>
@@ -2615,10 +2593,10 @@
         <v>0.35</v>
       </c>
       <c r="L4">
-        <v>12.25</v>
+        <v>16.45</v>
       </c>
       <c r="M4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N4" t="s">
         <v>230</v>
@@ -2627,16 +2605,16 @@
         <v>80</v>
       </c>
       <c r="P4">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R4">
         <v>1</v>
       </c>
       <c r="S4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="s">
         <v>231</v>
@@ -2645,25 +2623,19 @@
         <v>1</v>
       </c>
       <c r="V4">
-        <v>15</v>
-      </c>
-      <c r="W4">
-        <v>10</v>
-      </c>
-      <c r="X4">
-        <v>75</v>
+        <v>66</v>
+      </c>
+      <c r="W4" t="s">
+        <v>222</v>
+      </c>
+      <c r="X4" t="s">
+        <v>216</v>
       </c>
       <c r="Y4" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -2680,16 +2652,16 @@
         <v>117</v>
       </c>
       <c r="F5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G5" t="s">
         <v>25</v>
       </c>
       <c r="H5" t="s">
+        <v>232</v>
+      </c>
+      <c r="I5" t="s">
         <v>233</v>
-      </c>
-      <c r="I5" t="s">
-        <v>234</v>
       </c>
       <c r="J5" t="s">
         <v>80</v>
@@ -2698,55 +2670,49 @@
         <v>0.85</v>
       </c>
       <c r="L5">
-        <v>29.75</v>
+        <v>39.95</v>
       </c>
       <c r="M5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N5" t="s">
         <v>101</v>
       </c>
       <c r="O5" t="s">
+        <v>219</v>
+      </c>
+      <c r="P5">
+        <v>14.63</v>
+      </c>
+      <c r="Q5" t="s">
         <v>220</v>
       </c>
-      <c r="P5">
-        <v>11.08</v>
-      </c>
-      <c r="Q5" t="s">
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>20</v>
+      </c>
+      <c r="T5" t="s">
         <v>221</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <v>15</v>
-      </c>
-      <c r="T5" t="s">
-        <v>222</v>
       </c>
       <c r="U5">
         <v>0.7</v>
       </c>
       <c r="V5">
-        <v>10.5</v>
-      </c>
-      <c r="W5">
-        <v>5</v>
-      </c>
-      <c r="X5">
-        <v>71</v>
+        <v>75</v>
+      </c>
+      <c r="W5" t="s">
+        <v>234</v>
+      </c>
+      <c r="X5" t="s">
+        <v>25</v>
       </c>
       <c r="Y5" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2763,7 +2729,7 @@
         <v>123</v>
       </c>
       <c r="F6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G6" t="s">
         <v>25</v>
@@ -2781,10 +2747,10 @@
         <v>0.85</v>
       </c>
       <c r="L6">
-        <v>29.75</v>
+        <v>39.95</v>
       </c>
       <c r="M6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N6" t="s">
         <v>127</v>
@@ -2793,16 +2759,16 @@
         <v>236</v>
       </c>
       <c r="P6">
-        <v>16.92</v>
+        <v>22.33</v>
       </c>
       <c r="Q6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R6">
         <v>1</v>
       </c>
       <c r="S6">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="s">
         <v>237</v>
@@ -2811,25 +2777,19 @@
         <v>0.35</v>
       </c>
       <c r="V6">
-        <v>5.25</v>
-      </c>
-      <c r="W6">
-        <v>10</v>
-      </c>
-      <c r="X6">
-        <v>77</v>
+        <v>82</v>
+      </c>
+      <c r="W6" t="s">
+        <v>234</v>
+      </c>
+      <c r="X6" t="s">
+        <v>25</v>
       </c>
       <c r="Y6" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2846,7 +2806,7 @@
         <v>129</v>
       </c>
       <c r="F7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G7" t="s">
         <v>25</v>
@@ -2864,10 +2824,10 @@
         <v>0.7</v>
       </c>
       <c r="L7">
-        <v>24.5</v>
+        <v>32.9</v>
       </c>
       <c r="M7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N7" t="s">
         <v>127</v>
@@ -2876,16 +2836,16 @@
         <v>236</v>
       </c>
       <c r="P7">
-        <v>16.92</v>
+        <v>22.33</v>
       </c>
       <c r="Q7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R7">
         <v>1</v>
       </c>
       <c r="S7">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="s">
         <v>237</v>
@@ -2894,25 +2854,19 @@
         <v>0.35</v>
       </c>
       <c r="V7">
-        <v>5.25</v>
-      </c>
-      <c r="W7">
-        <v>10</v>
-      </c>
-      <c r="X7">
-        <v>72</v>
+        <v>75</v>
+      </c>
+      <c r="W7" t="s">
+        <v>234</v>
+      </c>
+      <c r="X7" t="s">
+        <v>25</v>
       </c>
       <c r="Y7" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2929,7 +2883,7 @@
         <v>133</v>
       </c>
       <c r="F8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G8" t="s">
         <v>25</v>
@@ -2941,61 +2895,55 @@
         <v>241</v>
       </c>
       <c r="J8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K8">
         <v>0.56</v>
       </c>
       <c r="L8">
-        <v>19.6</v>
+        <v>26.32</v>
       </c>
       <c r="M8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N8" t="s">
         <v>101</v>
       </c>
       <c r="O8" t="s">
+        <v>219</v>
+      </c>
+      <c r="P8">
+        <v>14.63</v>
+      </c>
+      <c r="Q8" t="s">
         <v>220</v>
       </c>
-      <c r="P8">
-        <v>11.08</v>
-      </c>
-      <c r="Q8" t="s">
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>20</v>
+      </c>
+      <c r="T8" t="s">
         <v>221</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8">
-        <v>15</v>
-      </c>
-      <c r="T8" t="s">
-        <v>222</v>
       </c>
       <c r="U8">
         <v>0.7</v>
       </c>
       <c r="V8">
-        <v>10.5</v>
-      </c>
-      <c r="W8">
-        <v>10</v>
-      </c>
-      <c r="X8">
-        <v>66</v>
+        <v>61</v>
+      </c>
+      <c r="W8" t="s">
+        <v>222</v>
+      </c>
+      <c r="X8" t="s">
+        <v>25</v>
       </c>
       <c r="Y8" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -3012,7 +2960,7 @@
         <v>138</v>
       </c>
       <c r="F9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G9" t="s">
         <v>25</v>
@@ -3033,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N9" t="s">
         <v>236</v>
@@ -3042,43 +2990,37 @@
         <v>127</v>
       </c>
       <c r="P9">
-        <v>11.08</v>
+        <v>14.63</v>
       </c>
       <c r="Q9" t="s">
+        <v>220</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>20</v>
+      </c>
+      <c r="T9" t="s">
         <v>221</v>
-      </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="S9">
-        <v>15</v>
-      </c>
-      <c r="T9" t="s">
-        <v>222</v>
       </c>
       <c r="U9">
         <v>0.7</v>
       </c>
       <c r="V9">
-        <v>10.5</v>
-      </c>
-      <c r="W9">
-        <v>5</v>
-      </c>
-      <c r="X9">
-        <v>42</v>
+        <v>35</v>
+      </c>
+      <c r="W9" t="s">
+        <v>226</v>
+      </c>
+      <c r="X9" t="s">
+        <v>216</v>
       </c>
       <c r="Y9" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -3095,7 +3037,7 @@
         <v>143</v>
       </c>
       <c r="F10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G10" t="s">
         <v>25</v>
@@ -3116,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N10" t="s">
         <v>80</v>
@@ -3125,43 +3067,37 @@
         <v>230</v>
       </c>
       <c r="P10">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q10" t="s">
+        <v>220</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>20</v>
+      </c>
+      <c r="T10" t="s">
         <v>221</v>
-      </c>
-      <c r="R10">
-        <v>1</v>
-      </c>
-      <c r="S10">
-        <v>15</v>
-      </c>
-      <c r="T10" t="s">
-        <v>222</v>
       </c>
       <c r="U10">
         <v>0.7</v>
       </c>
       <c r="V10">
-        <v>10.5</v>
-      </c>
-      <c r="W10">
-        <v>10</v>
-      </c>
-      <c r="X10">
-        <v>41</v>
+        <v>27</v>
+      </c>
+      <c r="W10" t="s">
+        <v>226</v>
+      </c>
+      <c r="X10" t="s">
+        <v>216</v>
       </c>
       <c r="Y10" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -3178,7 +3114,7 @@
         <v>149</v>
       </c>
       <c r="F11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G11" t="s">
         <v>25</v>
@@ -3199,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N11" t="s">
         <v>80</v>
@@ -3208,43 +3144,37 @@
         <v>230</v>
       </c>
       <c r="P11">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q11" t="s">
+        <v>220</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>20</v>
+      </c>
+      <c r="T11" t="s">
         <v>221</v>
-      </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
-      <c r="S11">
-        <v>15</v>
-      </c>
-      <c r="T11" t="s">
-        <v>222</v>
       </c>
       <c r="U11">
         <v>0.7</v>
       </c>
       <c r="V11">
-        <v>10.5</v>
-      </c>
-      <c r="W11">
-        <v>10</v>
-      </c>
-      <c r="X11">
-        <v>41</v>
+        <v>27</v>
+      </c>
+      <c r="W11" t="s">
+        <v>226</v>
+      </c>
+      <c r="X11" t="s">
+        <v>216</v>
       </c>
       <c r="Y11" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -3261,7 +3191,7 @@
         <v>155</v>
       </c>
       <c r="F12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G12" t="s">
         <v>25</v>
@@ -3282,52 +3212,46 @@
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N12" t="s">
         <v>101</v>
       </c>
       <c r="O12" t="s">
+        <v>219</v>
+      </c>
+      <c r="P12">
+        <v>14.63</v>
+      </c>
+      <c r="Q12" t="s">
         <v>220</v>
       </c>
-      <c r="P12">
-        <v>11.08</v>
-      </c>
-      <c r="Q12" t="s">
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>20</v>
+      </c>
+      <c r="T12" t="s">
         <v>221</v>
-      </c>
-      <c r="R12">
-        <v>1</v>
-      </c>
-      <c r="S12">
-        <v>15</v>
-      </c>
-      <c r="T12" t="s">
-        <v>222</v>
       </c>
       <c r="U12">
         <v>0.7</v>
       </c>
       <c r="V12">
-        <v>10.5</v>
-      </c>
-      <c r="W12">
-        <v>10</v>
-      </c>
-      <c r="X12">
-        <v>47</v>
+        <v>35</v>
+      </c>
+      <c r="W12" t="s">
+        <v>226</v>
+      </c>
+      <c r="X12" t="s">
+        <v>216</v>
       </c>
       <c r="Y12" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -3344,7 +3268,7 @@
         <v>160</v>
       </c>
       <c r="F13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G13" t="s">
         <v>25</v>
@@ -3365,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N13" t="s">
         <v>80</v>
@@ -3374,43 +3298,37 @@
         <v>230</v>
       </c>
       <c r="P13">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q13" t="s">
+        <v>220</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>20</v>
+      </c>
+      <c r="T13" t="s">
         <v>221</v>
-      </c>
-      <c r="R13">
-        <v>1</v>
-      </c>
-      <c r="S13">
-        <v>15</v>
-      </c>
-      <c r="T13" t="s">
-        <v>222</v>
       </c>
       <c r="U13">
         <v>0.7</v>
       </c>
       <c r="V13">
-        <v>10.5</v>
-      </c>
-      <c r="W13">
-        <v>5</v>
-      </c>
-      <c r="X13">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="W13" t="s">
+        <v>226</v>
+      </c>
+      <c r="X13" t="s">
+        <v>216</v>
       </c>
       <c r="Y13" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -3427,7 +3345,7 @@
         <v>165</v>
       </c>
       <c r="F14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G14" t="s">
         <v>25</v>
@@ -3448,25 +3366,25 @@
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N14" t="s">
         <v>101</v>
       </c>
       <c r="O14" t="s">
+        <v>219</v>
+      </c>
+      <c r="P14">
+        <v>14.63</v>
+      </c>
+      <c r="Q14" t="s">
         <v>220</v>
       </c>
-      <c r="P14">
-        <v>11.08</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>221</v>
-      </c>
       <c r="R14">
         <v>1</v>
       </c>
       <c r="S14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="s">
         <v>231</v>
@@ -3475,25 +3393,19 @@
         <v>1</v>
       </c>
       <c r="V14">
-        <v>15</v>
-      </c>
-      <c r="W14">
-        <v>5</v>
-      </c>
-      <c r="X14">
-        <v>46</v>
+        <v>35</v>
+      </c>
+      <c r="W14" t="s">
+        <v>226</v>
+      </c>
+      <c r="X14" t="s">
+        <v>216</v>
       </c>
       <c r="Y14" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -3510,28 +3422,28 @@
         <v>96</v>
       </c>
       <c r="F15" t="s">
+        <v>216</v>
+      </c>
+      <c r="G15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" t="s">
         <v>217</v>
       </c>
-      <c r="G15" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J15" t="s">
         <v>218</v>
-      </c>
-      <c r="I15" t="s">
-        <v>80</v>
-      </c>
-      <c r="J15" t="s">
-        <v>219</v>
       </c>
       <c r="K15">
         <v>0.75</v>
       </c>
       <c r="L15">
-        <v>26.25</v>
+        <v>35.25</v>
       </c>
       <c r="M15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N15" t="s">
         <v>101</v>
@@ -3540,43 +3452,37 @@
         <v>80</v>
       </c>
       <c r="P15">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q15" t="s">
+        <v>220</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>20</v>
+      </c>
+      <c r="T15" t="s">
         <v>221</v>
-      </c>
-      <c r="R15">
-        <v>1</v>
-      </c>
-      <c r="S15">
-        <v>15</v>
-      </c>
-      <c r="T15" t="s">
-        <v>222</v>
       </c>
       <c r="U15">
         <v>0.7</v>
       </c>
       <c r="V15">
-        <v>10.5</v>
-      </c>
-      <c r="W15">
-        <v>10</v>
-      </c>
-      <c r="X15">
         <v>85</v>
       </c>
+      <c r="W15" t="s">
+        <v>234</v>
+      </c>
+      <c r="X15" t="s">
+        <v>25</v>
+      </c>
       <c r="Y15" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -3593,28 +3499,28 @@
         <v>105</v>
       </c>
       <c r="F16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G16" t="s">
         <v>25</v>
       </c>
       <c r="H16" t="s">
+        <v>223</v>
+      </c>
+      <c r="I16" t="s">
         <v>224</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>225</v>
-      </c>
-      <c r="J16" t="s">
-        <v>226</v>
       </c>
       <c r="K16">
         <v>0.48</v>
       </c>
       <c r="L16">
-        <v>16.8</v>
+        <v>22.56</v>
       </c>
       <c r="M16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N16" t="s">
         <v>101</v>
@@ -3623,43 +3529,37 @@
         <v>80</v>
       </c>
       <c r="P16">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R16">
         <v>1</v>
       </c>
       <c r="S16">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U16">
         <v>1</v>
       </c>
       <c r="V16">
-        <v>15</v>
-      </c>
-      <c r="W16">
-        <v>10</v>
-      </c>
-      <c r="X16">
-        <v>80</v>
+        <v>73</v>
+      </c>
+      <c r="W16" t="s">
+        <v>222</v>
+      </c>
+      <c r="X16" t="s">
+        <v>25</v>
       </c>
       <c r="Y16" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3676,7 +3576,7 @@
         <v>109</v>
       </c>
       <c r="F17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G17" t="s">
         <v>25</v>
@@ -3697,7 +3597,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N17" t="s">
         <v>101</v>
@@ -3706,16 +3606,16 @@
         <v>80</v>
       </c>
       <c r="P17">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R17">
         <v>1</v>
       </c>
       <c r="S17">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="s">
         <v>231</v>
@@ -3724,25 +3624,19 @@
         <v>1</v>
       </c>
       <c r="V17">
-        <v>15</v>
-      </c>
-      <c r="W17">
-        <v>5</v>
-      </c>
-      <c r="X17">
-        <v>58</v>
+        <v>50</v>
+      </c>
+      <c r="W17" t="s">
+        <v>226</v>
+      </c>
+      <c r="X17" t="s">
+        <v>216</v>
       </c>
       <c r="Y17" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -3759,28 +3653,28 @@
         <v>117</v>
       </c>
       <c r="F18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G18" t="s">
         <v>25</v>
       </c>
       <c r="H18" t="s">
+        <v>243</v>
+      </c>
+      <c r="I18" t="s">
+        <v>80</v>
+      </c>
+      <c r="J18" t="s">
         <v>244</v>
-      </c>
-      <c r="I18" t="s">
-        <v>80</v>
-      </c>
-      <c r="J18" t="s">
-        <v>245</v>
       </c>
       <c r="K18">
         <v>0.75</v>
       </c>
       <c r="L18">
-        <v>26.25</v>
+        <v>35.25</v>
       </c>
       <c r="M18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N18" t="s">
         <v>101</v>
@@ -3789,43 +3683,37 @@
         <v>80</v>
       </c>
       <c r="P18">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q18" t="s">
+        <v>220</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>20</v>
+      </c>
+      <c r="T18" t="s">
         <v>221</v>
-      </c>
-      <c r="R18">
-        <v>1</v>
-      </c>
-      <c r="S18">
-        <v>15</v>
-      </c>
-      <c r="T18" t="s">
-        <v>222</v>
       </c>
       <c r="U18">
         <v>0.7</v>
       </c>
       <c r="V18">
-        <v>10.5</v>
-      </c>
-      <c r="W18">
-        <v>5</v>
-      </c>
-      <c r="X18">
-        <v>80</v>
+        <v>85</v>
+      </c>
+      <c r="W18" t="s">
+        <v>234</v>
+      </c>
+      <c r="X18" t="s">
+        <v>25</v>
       </c>
       <c r="Y18" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -3842,28 +3730,28 @@
         <v>123</v>
       </c>
       <c r="F19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G19" t="s">
         <v>25</v>
       </c>
       <c r="H19" t="s">
+        <v>245</v>
+      </c>
+      <c r="I19" t="s">
+        <v>80</v>
+      </c>
+      <c r="J19" t="s">
         <v>246</v>
-      </c>
-      <c r="I19" t="s">
-        <v>80</v>
-      </c>
-      <c r="J19" t="s">
-        <v>247</v>
       </c>
       <c r="K19">
         <v>0.25</v>
       </c>
       <c r="L19">
-        <v>8.75</v>
+        <v>11.75</v>
       </c>
       <c r="M19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N19" t="s">
         <v>101</v>
@@ -3872,16 +3760,16 @@
         <v>80</v>
       </c>
       <c r="P19">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R19">
         <v>1</v>
       </c>
       <c r="S19">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="s">
         <v>237</v>
@@ -3890,25 +3778,19 @@
         <v>0.35</v>
       </c>
       <c r="V19">
-        <v>5.25</v>
-      </c>
-      <c r="W19">
-        <v>10</v>
-      </c>
-      <c r="X19">
         <v>62</v>
       </c>
+      <c r="W19" t="s">
+        <v>222</v>
+      </c>
+      <c r="X19" t="s">
+        <v>216</v>
+      </c>
       <c r="Y19" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -3925,28 +3807,28 @@
         <v>129</v>
       </c>
       <c r="F20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G20" t="s">
         <v>25</v>
       </c>
       <c r="H20" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I20" t="s">
         <v>80</v>
       </c>
       <c r="J20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K20">
         <v>0.25</v>
       </c>
       <c r="L20">
-        <v>8.75</v>
+        <v>11.75</v>
       </c>
       <c r="M20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N20" t="s">
         <v>101</v>
@@ -3955,16 +3837,16 @@
         <v>80</v>
       </c>
       <c r="P20">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q20" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R20">
         <v>1</v>
       </c>
       <c r="S20">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="s">
         <v>237</v>
@@ -3973,25 +3855,19 @@
         <v>0.35</v>
       </c>
       <c r="V20">
-        <v>5.25</v>
-      </c>
-      <c r="W20">
-        <v>10</v>
-      </c>
-      <c r="X20">
         <v>62</v>
       </c>
+      <c r="W20" t="s">
+        <v>222</v>
+      </c>
+      <c r="X20" t="s">
+        <v>216</v>
+      </c>
       <c r="Y20" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -4008,7 +3884,7 @@
         <v>133</v>
       </c>
       <c r="F21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G21" t="s">
         <v>25</v>
@@ -4020,16 +3896,16 @@
         <v>241</v>
       </c>
       <c r="J21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K21">
         <v>0.56</v>
       </c>
       <c r="L21">
-        <v>19.6</v>
+        <v>26.32</v>
       </c>
       <c r="M21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N21" t="s">
         <v>101</v>
@@ -4038,43 +3914,37 @@
         <v>80</v>
       </c>
       <c r="P21">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q21" t="s">
+        <v>220</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>20</v>
+      </c>
+      <c r="T21" t="s">
         <v>221</v>
-      </c>
-      <c r="R21">
-        <v>1</v>
-      </c>
-      <c r="S21">
-        <v>15</v>
-      </c>
-      <c r="T21" t="s">
-        <v>222</v>
       </c>
       <c r="U21">
         <v>0.7</v>
       </c>
       <c r="V21">
-        <v>10.5</v>
-      </c>
-      <c r="W21">
-        <v>10</v>
-      </c>
-      <c r="X21">
-        <v>78</v>
+        <v>76</v>
+      </c>
+      <c r="W21" t="s">
+        <v>234</v>
+      </c>
+      <c r="X21" t="s">
+        <v>25</v>
       </c>
       <c r="Y21" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -4091,7 +3961,7 @@
         <v>138</v>
       </c>
       <c r="F22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G22" t="s">
         <v>25</v>
@@ -4112,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N22" t="s">
         <v>80</v>
@@ -4121,43 +3991,37 @@
         <v>101</v>
       </c>
       <c r="P22">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q22" t="s">
+        <v>220</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>20</v>
+      </c>
+      <c r="T22" t="s">
         <v>221</v>
-      </c>
-      <c r="R22">
-        <v>1</v>
-      </c>
-      <c r="S22">
-        <v>15</v>
-      </c>
-      <c r="T22" t="s">
-        <v>222</v>
       </c>
       <c r="U22">
         <v>0.7</v>
       </c>
       <c r="V22">
-        <v>10.5</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="W22" t="s">
+        <v>226</v>
+      </c>
+      <c r="X22" t="s">
+        <v>216</v>
       </c>
       <c r="Y22" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -4174,7 +4038,7 @@
         <v>143</v>
       </c>
       <c r="F23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G23" t="s">
         <v>25</v>
@@ -4195,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N23" t="s">
         <v>80</v>
@@ -4204,43 +4068,37 @@
         <v>101</v>
       </c>
       <c r="P23">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R23">
         <v>1</v>
       </c>
       <c r="S23">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U23">
         <v>1</v>
       </c>
       <c r="V23">
-        <v>15</v>
-      </c>
-      <c r="W23">
-        <v>10</v>
-      </c>
-      <c r="X23">
-        <v>45</v>
+        <v>27</v>
+      </c>
+      <c r="W23" t="s">
+        <v>226</v>
+      </c>
+      <c r="X23" t="s">
+        <v>216</v>
       </c>
       <c r="Y23" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -4257,7 +4115,7 @@
         <v>149</v>
       </c>
       <c r="F24" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G24" t="s">
         <v>25</v>
@@ -4278,7 +4136,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N24" t="s">
         <v>80</v>
@@ -4287,43 +4145,37 @@
         <v>101</v>
       </c>
       <c r="P24">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q24" t="s">
+        <v>220</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>20</v>
+      </c>
+      <c r="T24" t="s">
         <v>221</v>
-      </c>
-      <c r="R24">
-        <v>1</v>
-      </c>
-      <c r="S24">
-        <v>15</v>
-      </c>
-      <c r="T24" t="s">
-        <v>222</v>
       </c>
       <c r="U24">
         <v>0.7</v>
       </c>
       <c r="V24">
-        <v>10.5</v>
-      </c>
-      <c r="W24">
-        <v>5</v>
-      </c>
-      <c r="X24">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="W24" t="s">
+        <v>226</v>
+      </c>
+      <c r="X24" t="s">
+        <v>216</v>
       </c>
       <c r="Y24" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -4340,7 +4192,7 @@
         <v>155</v>
       </c>
       <c r="F25" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G25" t="s">
         <v>25</v>
@@ -4361,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N25" t="s">
         <v>101</v>
@@ -4370,43 +4222,37 @@
         <v>80</v>
       </c>
       <c r="P25">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q25" t="s">
+        <v>220</v>
+      </c>
+      <c r="R25">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <v>20</v>
+      </c>
+      <c r="T25" t="s">
         <v>221</v>
-      </c>
-      <c r="R25">
-        <v>1</v>
-      </c>
-      <c r="S25">
-        <v>15</v>
-      </c>
-      <c r="T25" t="s">
-        <v>222</v>
       </c>
       <c r="U25">
         <v>0.7</v>
       </c>
       <c r="V25">
-        <v>10.5</v>
-      </c>
-      <c r="W25">
-        <v>10</v>
-      </c>
-      <c r="X25">
-        <v>58</v>
+        <v>50</v>
+      </c>
+      <c r="W25" t="s">
+        <v>226</v>
+      </c>
+      <c r="X25" t="s">
+        <v>216</v>
       </c>
       <c r="Y25" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -4423,7 +4269,7 @@
         <v>160</v>
       </c>
       <c r="F26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G26" t="s">
         <v>25</v>
@@ -4444,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N26" t="s">
         <v>80</v>
@@ -4453,43 +4299,37 @@
         <v>101</v>
       </c>
       <c r="P26">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q26" t="s">
+        <v>220</v>
+      </c>
+      <c r="R26">
+        <v>1</v>
+      </c>
+      <c r="S26">
+        <v>20</v>
+      </c>
+      <c r="T26" t="s">
         <v>221</v>
-      </c>
-      <c r="R26">
-        <v>1</v>
-      </c>
-      <c r="S26">
-        <v>15</v>
-      </c>
-      <c r="T26" t="s">
-        <v>222</v>
       </c>
       <c r="U26">
         <v>0.7</v>
       </c>
       <c r="V26">
-        <v>10.5</v>
-      </c>
-      <c r="W26">
-        <v>5</v>
-      </c>
-      <c r="X26">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="W26" t="s">
+        <v>226</v>
+      </c>
+      <c r="X26" t="s">
+        <v>216</v>
       </c>
       <c r="Y26" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA26" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -4506,7 +4346,7 @@
         <v>165</v>
       </c>
       <c r="F27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G27" t="s">
         <v>25</v>
@@ -4527,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N27" t="s">
         <v>101</v>
@@ -4536,16 +4376,16 @@
         <v>80</v>
       </c>
       <c r="P27">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q27" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R27">
         <v>1</v>
       </c>
       <c r="S27">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T27" t="s">
         <v>231</v>
@@ -4554,25 +4394,19 @@
         <v>1</v>
       </c>
       <c r="V27">
-        <v>15</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="W27" t="s">
+        <v>226</v>
+      </c>
+      <c r="X27" t="s">
+        <v>216</v>
       </c>
       <c r="Y27" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA27" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -4589,7 +4423,7 @@
         <v>96</v>
       </c>
       <c r="F28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G28" t="s">
         <v>25</v>
@@ -4610,52 +4444,46 @@
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N28" t="s">
         <v>80</v>
       </c>
       <c r="O28" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P28">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q28" t="s">
+        <v>220</v>
+      </c>
+      <c r="R28">
+        <v>1</v>
+      </c>
+      <c r="S28">
+        <v>20</v>
+      </c>
+      <c r="T28" t="s">
         <v>221</v>
-      </c>
-      <c r="R28">
-        <v>1</v>
-      </c>
-      <c r="S28">
-        <v>15</v>
-      </c>
-      <c r="T28" t="s">
-        <v>222</v>
       </c>
       <c r="U28">
         <v>0.7</v>
       </c>
       <c r="V28">
-        <v>10.5</v>
-      </c>
-      <c r="W28">
-        <v>5</v>
-      </c>
-      <c r="X28">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="W28" t="s">
+        <v>226</v>
+      </c>
+      <c r="X28" t="s">
+        <v>216</v>
       </c>
       <c r="Y28" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z28" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -4672,7 +4500,7 @@
         <v>105</v>
       </c>
       <c r="F29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G29" t="s">
         <v>25</v>
@@ -4693,52 +4521,46 @@
         <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N29" t="s">
         <v>80</v>
       </c>
       <c r="O29" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P29">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q29" t="s">
+        <v>220</v>
+      </c>
+      <c r="R29">
+        <v>1</v>
+      </c>
+      <c r="S29">
+        <v>20</v>
+      </c>
+      <c r="T29" t="s">
         <v>221</v>
-      </c>
-      <c r="R29">
-        <v>1</v>
-      </c>
-      <c r="S29">
-        <v>15</v>
-      </c>
-      <c r="T29" t="s">
-        <v>222</v>
       </c>
       <c r="U29">
         <v>0.7</v>
       </c>
       <c r="V29">
-        <v>10.5</v>
-      </c>
-      <c r="W29">
-        <v>5</v>
-      </c>
-      <c r="X29">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="W29" t="s">
+        <v>226</v>
+      </c>
+      <c r="X29" t="s">
+        <v>216</v>
       </c>
       <c r="Y29" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>36</v>
       </c>
@@ -4755,16 +4577,16 @@
         <v>109</v>
       </c>
       <c r="F30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G30" t="s">
         <v>25</v>
       </c>
       <c r="H30" t="s">
+        <v>249</v>
+      </c>
+      <c r="I30" t="s">
         <v>250</v>
-      </c>
-      <c r="I30" t="s">
-        <v>251</v>
       </c>
       <c r="J30" t="s">
         <v>227</v>
@@ -4773,28 +4595,28 @@
         <v>0.45</v>
       </c>
       <c r="L30">
-        <v>15.75</v>
+        <v>21.15</v>
       </c>
       <c r="M30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N30" t="s">
         <v>80</v>
       </c>
       <c r="O30" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P30">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R30">
         <v>1</v>
       </c>
       <c r="S30">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="s">
         <v>231</v>
@@ -4803,25 +4625,19 @@
         <v>1</v>
       </c>
       <c r="V30">
-        <v>15</v>
-      </c>
-      <c r="W30">
-        <v>10</v>
-      </c>
-      <c r="X30">
-        <v>61</v>
+        <v>48</v>
+      </c>
+      <c r="W30" t="s">
+        <v>226</v>
+      </c>
+      <c r="X30" t="s">
+        <v>25</v>
       </c>
       <c r="Y30" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -4838,7 +4654,7 @@
         <v>117</v>
       </c>
       <c r="F31" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G31" t="s">
         <v>25</v>
@@ -4859,52 +4675,46 @@
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N31" t="s">
         <v>80</v>
       </c>
       <c r="O31" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P31">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q31" t="s">
+        <v>220</v>
+      </c>
+      <c r="R31">
+        <v>1</v>
+      </c>
+      <c r="S31">
+        <v>20</v>
+      </c>
+      <c r="T31" t="s">
         <v>221</v>
-      </c>
-      <c r="R31">
-        <v>1</v>
-      </c>
-      <c r="S31">
-        <v>15</v>
-      </c>
-      <c r="T31" t="s">
-        <v>222</v>
       </c>
       <c r="U31">
         <v>0.7</v>
       </c>
       <c r="V31">
-        <v>10.5</v>
-      </c>
-      <c r="W31">
-        <v>10</v>
-      </c>
-      <c r="X31">
-        <v>41</v>
+        <v>27</v>
+      </c>
+      <c r="W31" t="s">
+        <v>226</v>
+      </c>
+      <c r="X31" t="s">
+        <v>216</v>
       </c>
       <c r="Y31" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -4921,7 +4731,7 @@
         <v>123</v>
       </c>
       <c r="F32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G32" t="s">
         <v>25</v>
@@ -4939,28 +4749,28 @@
         <v>0.1</v>
       </c>
       <c r="L32">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="M32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N32" t="s">
         <v>80</v>
       </c>
       <c r="O32" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P32">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R32">
         <v>1</v>
       </c>
       <c r="S32">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T32" t="s">
         <v>237</v>
@@ -4969,25 +4779,19 @@
         <v>0.35</v>
       </c>
       <c r="V32">
-        <v>5.25</v>
-      </c>
-      <c r="W32">
-        <v>5</v>
-      </c>
-      <c r="X32">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="W32" t="s">
+        <v>226</v>
+      </c>
+      <c r="X32" t="s">
+        <v>216</v>
       </c>
       <c r="Y32" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z32" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -5004,7 +4808,7 @@
         <v>129</v>
       </c>
       <c r="F33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G33" t="s">
         <v>25</v>
@@ -5016,34 +4820,34 @@
         <v>228</v>
       </c>
       <c r="J33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K33">
         <v>0.1</v>
       </c>
       <c r="L33">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="M33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N33" t="s">
         <v>80</v>
       </c>
       <c r="O33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P33">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q33" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R33">
         <v>1</v>
       </c>
       <c r="S33">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T33" t="s">
         <v>237</v>
@@ -5052,25 +4856,19 @@
         <v>0.35</v>
       </c>
       <c r="V33">
-        <v>5.25</v>
-      </c>
-      <c r="W33">
-        <v>5</v>
-      </c>
-      <c r="X33">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="W33" t="s">
+        <v>226</v>
+      </c>
+      <c r="X33" t="s">
+        <v>216</v>
       </c>
       <c r="Y33" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z33" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA33" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -5087,7 +4885,7 @@
         <v>133</v>
       </c>
       <c r="F34" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G34" t="s">
         <v>25</v>
@@ -5108,52 +4906,46 @@
         <v>0</v>
       </c>
       <c r="M34" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N34" t="s">
         <v>80</v>
       </c>
       <c r="O34" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P34">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q34" t="s">
+        <v>220</v>
+      </c>
+      <c r="R34">
+        <v>1</v>
+      </c>
+      <c r="S34">
+        <v>20</v>
+      </c>
+      <c r="T34" t="s">
         <v>221</v>
-      </c>
-      <c r="R34">
-        <v>1</v>
-      </c>
-      <c r="S34">
-        <v>15</v>
-      </c>
-      <c r="T34" t="s">
-        <v>222</v>
       </c>
       <c r="U34">
         <v>0.7</v>
       </c>
       <c r="V34">
-        <v>10.5</v>
-      </c>
-      <c r="W34">
-        <v>5</v>
-      </c>
-      <c r="X34">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="W34" t="s">
+        <v>226</v>
+      </c>
+      <c r="X34" t="s">
+        <v>216</v>
       </c>
       <c r="Y34" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA34" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -5170,7 +4962,7 @@
         <v>138</v>
       </c>
       <c r="F35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G35" t="s">
         <v>25</v>
@@ -5188,55 +4980,49 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="M35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N35" t="s">
         <v>80</v>
       </c>
       <c r="O35" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P35">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q35" t="s">
+        <v>220</v>
+      </c>
+      <c r="R35">
+        <v>1</v>
+      </c>
+      <c r="S35">
+        <v>20</v>
+      </c>
+      <c r="T35" t="s">
         <v>221</v>
-      </c>
-      <c r="R35">
-        <v>1</v>
-      </c>
-      <c r="S35">
-        <v>15</v>
-      </c>
-      <c r="T35" t="s">
-        <v>222</v>
       </c>
       <c r="U35">
         <v>0.7</v>
       </c>
       <c r="V35">
-        <v>10.5</v>
-      </c>
-      <c r="W35">
-        <v>10</v>
-      </c>
-      <c r="X35">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="W35" t="s">
+        <v>222</v>
+      </c>
+      <c r="X35" t="s">
+        <v>25</v>
       </c>
       <c r="Y35" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z35" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA35" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -5253,7 +5039,7 @@
         <v>143</v>
       </c>
       <c r="F36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G36" t="s">
         <v>25</v>
@@ -5274,52 +5060,46 @@
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N36" t="s">
+        <v>252</v>
+      </c>
+      <c r="O36" t="s">
         <v>253</v>
       </c>
-      <c r="O36" t="s">
-        <v>254</v>
-      </c>
       <c r="P36">
-        <v>14</v>
+        <v>18.48</v>
       </c>
       <c r="Q36" t="s">
+        <v>220</v>
+      </c>
+      <c r="R36">
+        <v>1</v>
+      </c>
+      <c r="S36">
+        <v>20</v>
+      </c>
+      <c r="T36" t="s">
         <v>221</v>
-      </c>
-      <c r="R36">
-        <v>1</v>
-      </c>
-      <c r="S36">
-        <v>15</v>
-      </c>
-      <c r="T36" t="s">
-        <v>222</v>
       </c>
       <c r="U36">
         <v>0.7</v>
       </c>
       <c r="V36">
-        <v>10.5</v>
-      </c>
-      <c r="W36">
-        <v>5</v>
-      </c>
-      <c r="X36">
-        <v>45</v>
+        <v>38</v>
+      </c>
+      <c r="W36" t="s">
+        <v>226</v>
+      </c>
+      <c r="X36" t="s">
+        <v>216</v>
       </c>
       <c r="Y36" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z36" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA36" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -5336,7 +5116,7 @@
         <v>149</v>
       </c>
       <c r="F37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G37" t="s">
         <v>25</v>
@@ -5357,52 +5137,46 @@
         <v>0</v>
       </c>
       <c r="M37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N37" t="s">
+        <v>252</v>
+      </c>
+      <c r="O37" t="s">
         <v>253</v>
       </c>
-      <c r="O37" t="s">
-        <v>254</v>
-      </c>
       <c r="P37">
-        <v>14</v>
+        <v>18.48</v>
       </c>
       <c r="Q37" t="s">
+        <v>220</v>
+      </c>
+      <c r="R37">
+        <v>1</v>
+      </c>
+      <c r="S37">
+        <v>20</v>
+      </c>
+      <c r="T37" t="s">
         <v>221</v>
-      </c>
-      <c r="R37">
-        <v>1</v>
-      </c>
-      <c r="S37">
-        <v>15</v>
-      </c>
-      <c r="T37" t="s">
-        <v>222</v>
       </c>
       <c r="U37">
         <v>0.7</v>
       </c>
       <c r="V37">
-        <v>10.5</v>
-      </c>
-      <c r="W37">
-        <v>5</v>
-      </c>
-      <c r="X37">
-        <v>45</v>
+        <v>38</v>
+      </c>
+      <c r="W37" t="s">
+        <v>226</v>
+      </c>
+      <c r="X37" t="s">
+        <v>216</v>
       </c>
       <c r="Y37" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z37" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA37" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -5419,7 +5193,7 @@
         <v>155</v>
       </c>
       <c r="F38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G38" t="s">
         <v>25</v>
@@ -5440,52 +5214,46 @@
         <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N38" t="s">
         <v>80</v>
       </c>
       <c r="O38" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P38">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q38" t="s">
+        <v>220</v>
+      </c>
+      <c r="R38">
+        <v>1</v>
+      </c>
+      <c r="S38">
+        <v>20</v>
+      </c>
+      <c r="T38" t="s">
         <v>221</v>
-      </c>
-      <c r="R38">
-        <v>1</v>
-      </c>
-      <c r="S38">
-        <v>15</v>
-      </c>
-      <c r="T38" t="s">
-        <v>222</v>
       </c>
       <c r="U38">
         <v>0.7</v>
       </c>
       <c r="V38">
-        <v>10.5</v>
-      </c>
-      <c r="W38">
-        <v>5</v>
-      </c>
-      <c r="X38">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="W38" t="s">
+        <v>226</v>
+      </c>
+      <c r="X38" t="s">
+        <v>216</v>
       </c>
       <c r="Y38" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA38" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>36</v>
       </c>
@@ -5502,7 +5270,7 @@
         <v>160</v>
       </c>
       <c r="F39" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G39" t="s">
         <v>25</v>
@@ -5523,52 +5291,46 @@
         <v>0</v>
       </c>
       <c r="M39" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N39" t="s">
+        <v>252</v>
+      </c>
+      <c r="O39" t="s">
         <v>253</v>
       </c>
-      <c r="O39" t="s">
-        <v>254</v>
-      </c>
       <c r="P39">
-        <v>14</v>
+        <v>18.48</v>
       </c>
       <c r="Q39" t="s">
+        <v>220</v>
+      </c>
+      <c r="R39">
+        <v>1</v>
+      </c>
+      <c r="S39">
+        <v>20</v>
+      </c>
+      <c r="T39" t="s">
         <v>221</v>
-      </c>
-      <c r="R39">
-        <v>1</v>
-      </c>
-      <c r="S39">
-        <v>15</v>
-      </c>
-      <c r="T39" t="s">
-        <v>222</v>
       </c>
       <c r="U39">
         <v>0.7</v>
       </c>
       <c r="V39">
-        <v>10.5</v>
-      </c>
-      <c r="W39">
-        <v>0</v>
-      </c>
-      <c r="X39">
-        <v>40</v>
+        <v>38</v>
+      </c>
+      <c r="W39" t="s">
+        <v>226</v>
+      </c>
+      <c r="X39" t="s">
+        <v>216</v>
       </c>
       <c r="Y39" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z39" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA39" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>36</v>
       </c>
@@ -5585,16 +5347,16 @@
         <v>165</v>
       </c>
       <c r="F40" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G40" t="s">
         <v>25</v>
       </c>
       <c r="H40" t="s">
+        <v>254</v>
+      </c>
+      <c r="I40" t="s">
         <v>255</v>
-      </c>
-      <c r="I40" t="s">
-        <v>256</v>
       </c>
       <c r="J40" t="s">
         <v>80</v>
@@ -5603,28 +5365,28 @@
         <v>0.6</v>
       </c>
       <c r="L40">
-        <v>21</v>
+        <v>28.2</v>
       </c>
       <c r="M40" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N40" t="s">
+        <v>252</v>
+      </c>
+      <c r="O40" t="s">
         <v>253</v>
       </c>
-      <c r="O40" t="s">
-        <v>254</v>
-      </c>
       <c r="P40">
-        <v>14</v>
+        <v>18.48</v>
       </c>
       <c r="Q40" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R40">
         <v>1</v>
       </c>
       <c r="S40">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T40" t="s">
         <v>231</v>
@@ -5633,25 +5395,19 @@
         <v>1</v>
       </c>
       <c r="V40">
-        <v>15</v>
-      </c>
-      <c r="W40">
-        <v>5</v>
-      </c>
-      <c r="X40">
-        <v>70</v>
+        <v>67</v>
+      </c>
+      <c r="W40" t="s">
+        <v>222</v>
+      </c>
+      <c r="X40" t="s">
+        <v>25</v>
       </c>
       <c r="Y40" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA40" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -5668,7 +5424,7 @@
         <v>96</v>
       </c>
       <c r="F41" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G41" t="s">
         <v>25</v>
@@ -5689,7 +5445,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N41" t="s">
         <v>80</v>
@@ -5698,43 +5454,37 @@
         <v>147</v>
       </c>
       <c r="P41">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R41">
         <v>0.3</v>
       </c>
       <c r="S41">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U41">
         <v>0.7</v>
       </c>
       <c r="V41">
-        <v>10.5</v>
-      </c>
-      <c r="W41">
-        <v>10</v>
-      </c>
-      <c r="X41">
-        <v>30</v>
+        <v>13</v>
+      </c>
+      <c r="W41" t="s">
+        <v>226</v>
+      </c>
+      <c r="X41" t="s">
+        <v>216</v>
       </c>
       <c r="Y41" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z41" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA41" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -5751,7 +5501,7 @@
         <v>105</v>
       </c>
       <c r="F42" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G42" t="s">
         <v>25</v>
@@ -5772,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N42" t="s">
         <v>80</v>
@@ -5781,43 +5531,37 @@
         <v>147</v>
       </c>
       <c r="P42">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q42" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R42">
         <v>0.1</v>
       </c>
       <c r="S42">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T42" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U42">
         <v>0.7</v>
       </c>
       <c r="V42">
-        <v>10.5</v>
-      </c>
-      <c r="W42">
-        <v>10</v>
-      </c>
-      <c r="X42">
-        <v>27</v>
+        <v>9</v>
+      </c>
+      <c r="W42" t="s">
+        <v>226</v>
+      </c>
+      <c r="X42" t="s">
+        <v>216</v>
       </c>
       <c r="Y42" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z42" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA42" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -5834,7 +5578,7 @@
         <v>109</v>
       </c>
       <c r="F43" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G43" t="s">
         <v>25</v>
@@ -5855,25 +5599,25 @@
         <v>0</v>
       </c>
       <c r="M43" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N43" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O43" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P43">
-        <v>14</v>
+        <v>18.48</v>
       </c>
       <c r="Q43" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R43">
         <v>0.1</v>
       </c>
       <c r="S43">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T43" t="s">
         <v>231</v>
@@ -5882,25 +5626,19 @@
         <v>1</v>
       </c>
       <c r="V43">
-        <v>15</v>
-      </c>
-      <c r="W43">
-        <v>5</v>
-      </c>
-      <c r="X43">
-        <v>36</v>
+        <v>20</v>
+      </c>
+      <c r="W43" t="s">
+        <v>226</v>
+      </c>
+      <c r="X43" t="s">
+        <v>216</v>
       </c>
       <c r="Y43" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z43" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA43" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -5917,7 +5655,7 @@
         <v>117</v>
       </c>
       <c r="F44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G44" t="s">
         <v>25</v>
@@ -5938,7 +5676,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N44" t="s">
         <v>80</v>
@@ -5947,43 +5685,37 @@
         <v>147</v>
       </c>
       <c r="P44">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q44" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R44">
         <v>0.1</v>
       </c>
       <c r="S44">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T44" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U44">
         <v>0.7</v>
       </c>
       <c r="V44">
-        <v>10.5</v>
-      </c>
-      <c r="W44">
-        <v>5</v>
-      </c>
-      <c r="X44">
-        <v>22</v>
+        <v>9</v>
+      </c>
+      <c r="W44" t="s">
+        <v>226</v>
+      </c>
+      <c r="X44" t="s">
+        <v>216</v>
       </c>
       <c r="Y44" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z44" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA44" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -6000,7 +5732,7 @@
         <v>123</v>
       </c>
       <c r="F45" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G45" t="s">
         <v>25</v>
@@ -6021,7 +5753,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N45" t="s">
         <v>80</v>
@@ -6030,16 +5762,16 @@
         <v>147</v>
       </c>
       <c r="P45">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q45" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R45">
         <v>0.3</v>
       </c>
       <c r="S45">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="T45" t="s">
         <v>237</v>
@@ -6048,25 +5780,19 @@
         <v>0.35</v>
       </c>
       <c r="V45">
-        <v>5.25</v>
-      </c>
-      <c r="W45">
-        <v>10</v>
-      </c>
-      <c r="X45">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="W45" t="s">
+        <v>226</v>
+      </c>
+      <c r="X45" t="s">
+        <v>216</v>
       </c>
       <c r="Y45" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z45" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA45" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -6083,7 +5809,7 @@
         <v>129</v>
       </c>
       <c r="F46" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G46" t="s">
         <v>25</v>
@@ -6104,7 +5830,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N46" t="s">
         <v>80</v>
@@ -6113,16 +5839,16 @@
         <v>147</v>
       </c>
       <c r="P46">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q46" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R46">
         <v>1</v>
       </c>
       <c r="S46">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="s">
         <v>237</v>
@@ -6131,25 +5857,19 @@
         <v>0.35</v>
       </c>
       <c r="V46">
-        <v>5.25</v>
-      </c>
-      <c r="W46">
-        <v>10</v>
-      </c>
-      <c r="X46">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="W46" t="s">
+        <v>226</v>
+      </c>
+      <c r="X46" t="s">
+        <v>216</v>
       </c>
       <c r="Y46" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z46" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA46" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -6166,7 +5886,7 @@
         <v>133</v>
       </c>
       <c r="F47" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G47" t="s">
         <v>25</v>
@@ -6187,7 +5907,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N47" t="s">
         <v>80</v>
@@ -6196,43 +5916,37 @@
         <v>147</v>
       </c>
       <c r="P47">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R47">
         <v>0.1</v>
       </c>
       <c r="S47">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T47" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U47">
         <v>0.7</v>
       </c>
       <c r="V47">
-        <v>10.5</v>
-      </c>
-      <c r="W47">
-        <v>10</v>
-      </c>
-      <c r="X47">
-        <v>27</v>
+        <v>9</v>
+      </c>
+      <c r="W47" t="s">
+        <v>226</v>
+      </c>
+      <c r="X47" t="s">
+        <v>216</v>
       </c>
       <c r="Y47" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z47" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA47" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -6249,7 +5963,7 @@
         <v>138</v>
       </c>
       <c r="F48" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G48" t="s">
         <v>25</v>
@@ -6270,52 +5984,46 @@
         <v>0</v>
       </c>
       <c r="M48" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N48" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O48" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P48">
-        <v>14</v>
+        <v>18.48</v>
       </c>
       <c r="Q48" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R48">
         <v>0.3</v>
       </c>
       <c r="S48">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U48">
         <v>0.7</v>
       </c>
       <c r="V48">
-        <v>10.5</v>
-      </c>
-      <c r="W48">
-        <v>0</v>
-      </c>
-      <c r="X48">
-        <v>29</v>
+        <v>24</v>
+      </c>
+      <c r="W48" t="s">
+        <v>226</v>
+      </c>
+      <c r="X48" t="s">
+        <v>216</v>
       </c>
       <c r="Y48" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z48" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA48" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -6332,7 +6040,7 @@
         <v>143</v>
       </c>
       <c r="F49" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G49" t="s">
         <v>25</v>
@@ -6350,10 +6058,10 @@
         <v>1</v>
       </c>
       <c r="L49">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="M49" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N49" t="s">
         <v>147</v>
@@ -6362,43 +6070,37 @@
         <v>80</v>
       </c>
       <c r="P49">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q49" t="s">
+        <v>220</v>
+      </c>
+      <c r="R49">
+        <v>1</v>
+      </c>
+      <c r="S49">
+        <v>20</v>
+      </c>
+      <c r="T49" t="s">
         <v>221</v>
-      </c>
-      <c r="R49">
-        <v>1</v>
-      </c>
-      <c r="S49">
-        <v>15</v>
-      </c>
-      <c r="T49" t="s">
-        <v>222</v>
       </c>
       <c r="U49">
         <v>0.7</v>
       </c>
       <c r="V49">
-        <v>10.5</v>
-      </c>
-      <c r="W49">
-        <v>10</v>
-      </c>
-      <c r="X49">
-        <v>93</v>
+        <v>97</v>
+      </c>
+      <c r="W49" t="s">
+        <v>234</v>
+      </c>
+      <c r="X49" t="s">
+        <v>25</v>
       </c>
       <c r="Y49" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z49" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA49" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>46</v>
       </c>
@@ -6415,7 +6117,7 @@
         <v>149</v>
       </c>
       <c r="F50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G50" t="s">
         <v>25</v>
@@ -6436,7 +6138,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N50" t="s">
         <v>147</v>
@@ -6445,43 +6147,37 @@
         <v>80</v>
       </c>
       <c r="P50">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q50" t="s">
+        <v>220</v>
+      </c>
+      <c r="R50">
+        <v>1</v>
+      </c>
+      <c r="S50">
+        <v>20</v>
+      </c>
+      <c r="T50" t="s">
         <v>221</v>
-      </c>
-      <c r="R50">
-        <v>1</v>
-      </c>
-      <c r="S50">
-        <v>15</v>
-      </c>
-      <c r="T50" t="s">
-        <v>222</v>
       </c>
       <c r="U50">
         <v>0.7</v>
       </c>
       <c r="V50">
-        <v>10.5</v>
-      </c>
-      <c r="W50">
-        <v>5</v>
-      </c>
-      <c r="X50">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="W50" t="s">
+        <v>226</v>
+      </c>
+      <c r="X50" t="s">
+        <v>216</v>
       </c>
       <c r="Y50" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z50" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA50" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>46</v>
       </c>
@@ -6498,7 +6194,7 @@
         <v>155</v>
       </c>
       <c r="F51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G51" t="s">
         <v>25</v>
@@ -6519,52 +6215,46 @@
         <v>0</v>
       </c>
       <c r="M51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N51" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O51" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P51">
-        <v>14</v>
+        <v>18.48</v>
       </c>
       <c r="Q51" t="s">
+        <v>220</v>
+      </c>
+      <c r="R51">
+        <v>1</v>
+      </c>
+      <c r="S51">
+        <v>20</v>
+      </c>
+      <c r="T51" t="s">
         <v>221</v>
-      </c>
-      <c r="R51">
-        <v>1</v>
-      </c>
-      <c r="S51">
-        <v>15</v>
-      </c>
-      <c r="T51" t="s">
-        <v>222</v>
       </c>
       <c r="U51">
         <v>0.7</v>
       </c>
       <c r="V51">
-        <v>10.5</v>
-      </c>
-      <c r="W51">
-        <v>10</v>
-      </c>
-      <c r="X51">
-        <v>50</v>
+        <v>38</v>
+      </c>
+      <c r="W51" t="s">
+        <v>226</v>
+      </c>
+      <c r="X51" t="s">
+        <v>216</v>
       </c>
       <c r="Y51" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z51" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA51" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>46</v>
       </c>
@@ -6581,7 +6271,7 @@
         <v>160</v>
       </c>
       <c r="F52" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G52" t="s">
         <v>25</v>
@@ -6599,10 +6289,10 @@
         <v>1</v>
       </c>
       <c r="L52">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="M52" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N52" t="s">
         <v>147</v>
@@ -6611,43 +6301,37 @@
         <v>80</v>
       </c>
       <c r="P52">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q52" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T52" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U52">
         <v>1</v>
       </c>
       <c r="V52">
-        <v>15</v>
-      </c>
-      <c r="W52">
-        <v>5</v>
-      </c>
-      <c r="X52">
-        <v>93</v>
+        <v>97</v>
+      </c>
+      <c r="W52" t="s">
+        <v>234</v>
+      </c>
+      <c r="X52" t="s">
+        <v>25</v>
       </c>
       <c r="Y52" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z52" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA52" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>46</v>
       </c>
@@ -6664,7 +6348,7 @@
         <v>165</v>
       </c>
       <c r="F53" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G53" t="s">
         <v>25</v>
@@ -6685,7 +6369,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N53" t="s">
         <v>147</v>
@@ -6694,16 +6378,16 @@
         <v>80</v>
       </c>
       <c r="P53">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q53" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R53">
         <v>0.6</v>
       </c>
       <c r="S53">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T53" t="s">
         <v>231</v>
@@ -6712,25 +6396,19 @@
         <v>1</v>
       </c>
       <c r="V53">
-        <v>15</v>
-      </c>
-      <c r="W53">
-        <v>0</v>
-      </c>
-      <c r="X53">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="W53" t="s">
+        <v>226</v>
+      </c>
+      <c r="X53" t="s">
+        <v>216</v>
       </c>
       <c r="Y53" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z53" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>54</v>
       </c>
@@ -6747,7 +6425,7 @@
         <v>96</v>
       </c>
       <c r="F54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G54" t="s">
         <v>25</v>
@@ -6768,52 +6446,46 @@
         <v>0</v>
       </c>
       <c r="M54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N54" t="s">
         <v>80</v>
       </c>
       <c r="O54" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P54">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q54" t="s">
+        <v>220</v>
+      </c>
+      <c r="R54">
+        <v>1</v>
+      </c>
+      <c r="S54">
+        <v>20</v>
+      </c>
+      <c r="T54" t="s">
         <v>221</v>
-      </c>
-      <c r="R54">
-        <v>1</v>
-      </c>
-      <c r="S54">
-        <v>15</v>
-      </c>
-      <c r="T54" t="s">
-        <v>222</v>
       </c>
       <c r="U54">
         <v>0.7</v>
       </c>
       <c r="V54">
-        <v>10.5</v>
-      </c>
-      <c r="W54">
-        <v>5</v>
-      </c>
-      <c r="X54">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="W54" t="s">
+        <v>226</v>
+      </c>
+      <c r="X54" t="s">
+        <v>216</v>
       </c>
       <c r="Y54" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA54" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -6830,7 +6502,7 @@
         <v>105</v>
       </c>
       <c r="F55" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G55" t="s">
         <v>25</v>
@@ -6851,52 +6523,46 @@
         <v>0</v>
       </c>
       <c r="M55" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N55" t="s">
         <v>80</v>
       </c>
       <c r="O55" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P55">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q55" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R55">
         <v>0.3</v>
       </c>
       <c r="S55">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="T55" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U55">
         <v>0.7</v>
       </c>
       <c r="V55">
-        <v>10.5</v>
-      </c>
-      <c r="W55">
-        <v>5</v>
-      </c>
-      <c r="X55">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="W55" t="s">
+        <v>226</v>
+      </c>
+      <c r="X55" t="s">
+        <v>216</v>
       </c>
       <c r="Y55" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z55" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA55" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -6913,7 +6579,7 @@
         <v>109</v>
       </c>
       <c r="F56" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G56" t="s">
         <v>25</v>
@@ -6934,25 +6600,25 @@
         <v>0</v>
       </c>
       <c r="M56" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N56" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O56" t="s">
         <v>80</v>
       </c>
       <c r="P56">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q56" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R56">
         <v>0.3</v>
       </c>
       <c r="S56">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="T56" t="s">
         <v>231</v>
@@ -6961,25 +6627,19 @@
         <v>1</v>
       </c>
       <c r="V56">
-        <v>15</v>
-      </c>
-      <c r="W56">
-        <v>0</v>
-      </c>
-      <c r="X56">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="W56" t="s">
+        <v>226</v>
+      </c>
+      <c r="X56" t="s">
+        <v>216</v>
       </c>
       <c r="Y56" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z56" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA56" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>54</v>
       </c>
@@ -6996,7 +6656,7 @@
         <v>117</v>
       </c>
       <c r="F57" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G57" t="s">
         <v>25</v>
@@ -7017,52 +6677,46 @@
         <v>0</v>
       </c>
       <c r="M57" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N57" t="s">
         <v>80</v>
       </c>
       <c r="O57" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P57">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q57" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R57">
         <v>0.3</v>
       </c>
       <c r="S57">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U57">
         <v>0.7</v>
       </c>
       <c r="V57">
-        <v>10.5</v>
-      </c>
-      <c r="W57">
-        <v>0</v>
-      </c>
-      <c r="X57">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="W57" t="s">
+        <v>226</v>
+      </c>
+      <c r="X57" t="s">
+        <v>216</v>
       </c>
       <c r="Y57" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z57" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA57" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>54</v>
       </c>
@@ -7079,7 +6733,7 @@
         <v>123</v>
       </c>
       <c r="F58" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G58" t="s">
         <v>25</v>
@@ -7100,25 +6754,25 @@
         <v>0</v>
       </c>
       <c r="M58" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N58" t="s">
         <v>80</v>
       </c>
       <c r="O58" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P58">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q58" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R58">
         <v>1</v>
       </c>
       <c r="S58">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T58" t="s">
         <v>237</v>
@@ -7127,25 +6781,19 @@
         <v>0.35</v>
       </c>
       <c r="V58">
-        <v>5.25</v>
-      </c>
-      <c r="W58">
-        <v>5</v>
-      </c>
-      <c r="X58">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="W58" t="s">
+        <v>226</v>
+      </c>
+      <c r="X58" t="s">
+        <v>216</v>
       </c>
       <c r="Y58" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z58" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA58" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>54</v>
       </c>
@@ -7162,7 +6810,7 @@
         <v>129</v>
       </c>
       <c r="F59" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G59" t="s">
         <v>25</v>
@@ -7183,25 +6831,25 @@
         <v>0</v>
       </c>
       <c r="M59" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N59" t="s">
         <v>80</v>
       </c>
       <c r="O59" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P59">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q59" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R59">
         <v>1</v>
       </c>
       <c r="S59">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T59" t="s">
         <v>237</v>
@@ -7210,25 +6858,19 @@
         <v>0.35</v>
       </c>
       <c r="V59">
-        <v>5.25</v>
-      </c>
-      <c r="W59">
-        <v>5</v>
-      </c>
-      <c r="X59">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="W59" t="s">
+        <v>226</v>
+      </c>
+      <c r="X59" t="s">
+        <v>216</v>
       </c>
       <c r="Y59" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z59" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA59" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>54</v>
       </c>
@@ -7245,7 +6887,7 @@
         <v>133</v>
       </c>
       <c r="F60" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G60" t="s">
         <v>25</v>
@@ -7266,52 +6908,46 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N60" t="s">
         <v>80</v>
       </c>
       <c r="O60" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P60">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q60" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R60">
         <v>0.3</v>
       </c>
       <c r="S60">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="T60" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U60">
         <v>0.7</v>
       </c>
       <c r="V60">
-        <v>10.5</v>
-      </c>
-      <c r="W60">
-        <v>5</v>
-      </c>
-      <c r="X60">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="W60" t="s">
+        <v>226</v>
+      </c>
+      <c r="X60" t="s">
+        <v>216</v>
       </c>
       <c r="Y60" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z60" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA60" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>54</v>
       </c>
@@ -7328,7 +6964,7 @@
         <v>138</v>
       </c>
       <c r="F61" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G61" t="s">
         <v>25</v>
@@ -7349,52 +6985,46 @@
         <v>0</v>
       </c>
       <c r="M61" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N61" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O61" t="s">
         <v>80</v>
       </c>
       <c r="P61">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q61" t="s">
+        <v>220</v>
+      </c>
+      <c r="R61">
+        <v>1</v>
+      </c>
+      <c r="S61">
+        <v>20</v>
+      </c>
+      <c r="T61" t="s">
         <v>221</v>
-      </c>
-      <c r="R61">
-        <v>1</v>
-      </c>
-      <c r="S61">
-        <v>15</v>
-      </c>
-      <c r="T61" t="s">
-        <v>222</v>
       </c>
       <c r="U61">
         <v>0.7</v>
       </c>
       <c r="V61">
-        <v>10.5</v>
-      </c>
-      <c r="W61">
-        <v>5</v>
-      </c>
-      <c r="X61">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="W61" t="s">
+        <v>226</v>
+      </c>
+      <c r="X61" t="s">
+        <v>216</v>
       </c>
       <c r="Y61" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z61" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA61" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>54</v>
       </c>
@@ -7411,7 +7041,7 @@
         <v>143</v>
       </c>
       <c r="F62" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G62" t="s">
         <v>25</v>
@@ -7432,52 +7062,46 @@
         <v>0</v>
       </c>
       <c r="M62" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N62" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O62" t="s">
         <v>80</v>
       </c>
       <c r="P62">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q62" t="s">
+        <v>220</v>
+      </c>
+      <c r="R62">
+        <v>1</v>
+      </c>
+      <c r="S62">
+        <v>20</v>
+      </c>
+      <c r="T62" t="s">
         <v>221</v>
-      </c>
-      <c r="R62">
-        <v>1</v>
-      </c>
-      <c r="S62">
-        <v>15</v>
-      </c>
-      <c r="T62" t="s">
-        <v>222</v>
       </c>
       <c r="U62">
         <v>0.7</v>
       </c>
       <c r="V62">
-        <v>10.5</v>
-      </c>
-      <c r="W62">
-        <v>5</v>
-      </c>
-      <c r="X62">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="W62" t="s">
+        <v>226</v>
+      </c>
+      <c r="X62" t="s">
+        <v>216</v>
       </c>
       <c r="Y62" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z62" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA62" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>54</v>
       </c>
@@ -7494,7 +7118,7 @@
         <v>149</v>
       </c>
       <c r="F63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G63" t="s">
         <v>25</v>
@@ -7512,55 +7136,49 @@
         <v>1</v>
       </c>
       <c r="L63">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="M63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N63" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O63" t="s">
         <v>80</v>
       </c>
       <c r="P63">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q63" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R63">
         <v>1</v>
       </c>
       <c r="S63">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T63" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U63">
         <v>1</v>
       </c>
       <c r="V63">
-        <v>15</v>
-      </c>
-      <c r="W63">
-        <v>10</v>
-      </c>
-      <c r="X63">
-        <v>98</v>
+        <v>97</v>
+      </c>
+      <c r="W63" t="s">
+        <v>234</v>
+      </c>
+      <c r="X63" t="s">
+        <v>25</v>
       </c>
       <c r="Y63" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z63" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA63" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>54</v>
       </c>
@@ -7577,7 +7195,7 @@
         <v>155</v>
       </c>
       <c r="F64" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G64" t="s">
         <v>25</v>
@@ -7595,55 +7213,49 @@
         <v>1</v>
       </c>
       <c r="L64">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="M64" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N64" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O64" t="s">
         <v>80</v>
       </c>
       <c r="P64">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q64" t="s">
+        <v>220</v>
+      </c>
+      <c r="R64">
+        <v>1</v>
+      </c>
+      <c r="S64">
+        <v>20</v>
+      </c>
+      <c r="T64" t="s">
         <v>221</v>
-      </c>
-      <c r="R64">
-        <v>1</v>
-      </c>
-      <c r="S64">
-        <v>15</v>
-      </c>
-      <c r="T64" t="s">
-        <v>222</v>
       </c>
       <c r="U64">
         <v>0.7</v>
       </c>
       <c r="V64">
-        <v>10.5</v>
-      </c>
-      <c r="W64">
-        <v>5</v>
-      </c>
-      <c r="X64">
-        <v>88</v>
+        <v>97</v>
+      </c>
+      <c r="W64" t="s">
+        <v>234</v>
+      </c>
+      <c r="X64" t="s">
+        <v>25</v>
       </c>
       <c r="Y64" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z64" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA64" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>54</v>
       </c>
@@ -7660,7 +7272,7 @@
         <v>160</v>
       </c>
       <c r="F65" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G65" t="s">
         <v>25</v>
@@ -7681,52 +7293,46 @@
         <v>0</v>
       </c>
       <c r="M65" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N65" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O65" t="s">
         <v>80</v>
       </c>
       <c r="P65">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q65" t="s">
+        <v>220</v>
+      </c>
+      <c r="R65">
+        <v>1</v>
+      </c>
+      <c r="S65">
+        <v>20</v>
+      </c>
+      <c r="T65" t="s">
         <v>221</v>
-      </c>
-      <c r="R65">
-        <v>1</v>
-      </c>
-      <c r="S65">
-        <v>15</v>
-      </c>
-      <c r="T65" t="s">
-        <v>222</v>
       </c>
       <c r="U65">
         <v>0.7</v>
       </c>
       <c r="V65">
-        <v>10.5</v>
-      </c>
-      <c r="W65">
-        <v>5</v>
-      </c>
-      <c r="X65">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="W65" t="s">
+        <v>226</v>
+      </c>
+      <c r="X65" t="s">
+        <v>216</v>
       </c>
       <c r="Y65" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z65" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA65" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>54</v>
       </c>
@@ -7743,7 +7349,7 @@
         <v>165</v>
       </c>
       <c r="F66" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G66" t="s">
         <v>25</v>
@@ -7764,25 +7370,25 @@
         <v>0</v>
       </c>
       <c r="M66" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N66" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O66" t="s">
         <v>80</v>
       </c>
       <c r="P66">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q66" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R66">
         <v>1</v>
       </c>
       <c r="S66">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T66" t="s">
         <v>231</v>
@@ -7791,25 +7397,19 @@
         <v>1</v>
       </c>
       <c r="V66">
-        <v>15</v>
-      </c>
-      <c r="W66">
-        <v>0</v>
-      </c>
-      <c r="X66">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="W66" t="s">
+        <v>226</v>
+      </c>
+      <c r="X66" t="s">
+        <v>216</v>
       </c>
       <c r="Y66" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA66" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>64</v>
       </c>
@@ -7826,7 +7426,7 @@
         <v>96</v>
       </c>
       <c r="F67" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G67" t="s">
         <v>25</v>
@@ -7847,52 +7447,46 @@
         <v>0</v>
       </c>
       <c r="M67" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N67" t="s">
         <v>80</v>
       </c>
       <c r="O67" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P67">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q67" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R67">
         <v>0.6</v>
       </c>
       <c r="S67">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T67" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U67">
         <v>0.7</v>
       </c>
       <c r="V67">
-        <v>10.5</v>
-      </c>
-      <c r="W67">
-        <v>5</v>
-      </c>
-      <c r="X67">
-        <v>30</v>
+        <v>19</v>
+      </c>
+      <c r="W67" t="s">
+        <v>226</v>
+      </c>
+      <c r="X67" t="s">
+        <v>216</v>
       </c>
       <c r="Y67" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z67" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA67" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>64</v>
       </c>
@@ -7909,7 +7503,7 @@
         <v>105</v>
       </c>
       <c r="F68" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G68" t="s">
         <v>25</v>
@@ -7930,52 +7524,46 @@
         <v>0</v>
       </c>
       <c r="M68" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N68" t="s">
         <v>80</v>
       </c>
       <c r="O68" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P68">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q68" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R68">
         <v>0.1</v>
       </c>
       <c r="S68">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T68" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U68">
         <v>0.7</v>
       </c>
       <c r="V68">
-        <v>10.5</v>
-      </c>
-      <c r="W68">
-        <v>5</v>
-      </c>
-      <c r="X68">
-        <v>22</v>
+        <v>9</v>
+      </c>
+      <c r="W68" t="s">
+        <v>226</v>
+      </c>
+      <c r="X68" t="s">
+        <v>216</v>
       </c>
       <c r="Y68" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z68" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA68" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>64</v>
       </c>
@@ -7992,7 +7580,7 @@
         <v>109</v>
       </c>
       <c r="F69" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G69" t="s">
         <v>25</v>
@@ -8001,37 +7589,37 @@
         <v>80</v>
       </c>
       <c r="I69" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J69" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K69">
         <v>0.1</v>
       </c>
       <c r="L69">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="M69" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N69" t="s">
         <v>80</v>
       </c>
       <c r="O69" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P69">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q69" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R69">
         <v>0.1</v>
       </c>
       <c r="S69">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T69" t="s">
         <v>231</v>
@@ -8040,25 +7628,19 @@
         <v>1</v>
       </c>
       <c r="V69">
-        <v>15</v>
-      </c>
-      <c r="W69">
-        <v>5</v>
-      </c>
-      <c r="X69">
-        <v>30</v>
+        <v>14</v>
+      </c>
+      <c r="W69" t="s">
+        <v>226</v>
+      </c>
+      <c r="X69" t="s">
+        <v>216</v>
       </c>
       <c r="Y69" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z69" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA69" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>64</v>
       </c>
@@ -8075,7 +7657,7 @@
         <v>117</v>
       </c>
       <c r="F70" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G70" t="s">
         <v>25</v>
@@ -8096,52 +7678,46 @@
         <v>0</v>
       </c>
       <c r="M70" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N70" t="s">
         <v>80</v>
       </c>
       <c r="O70" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P70">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q70" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R70">
         <v>0.1</v>
       </c>
       <c r="S70">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T70" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U70">
         <v>0.7</v>
       </c>
       <c r="V70">
-        <v>10.5</v>
-      </c>
-      <c r="W70">
-        <v>0</v>
-      </c>
-      <c r="X70">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="W70" t="s">
+        <v>226</v>
+      </c>
+      <c r="X70" t="s">
+        <v>216</v>
       </c>
       <c r="Y70" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z70" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA70" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>64</v>
       </c>
@@ -8158,7 +7734,7 @@
         <v>123</v>
       </c>
       <c r="F71" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G71" t="s">
         <v>25</v>
@@ -8179,25 +7755,25 @@
         <v>0</v>
       </c>
       <c r="M71" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N71" t="s">
         <v>80</v>
       </c>
       <c r="O71" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P71">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q71" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R71">
         <v>0.6</v>
       </c>
       <c r="S71">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T71" t="s">
         <v>237</v>
@@ -8206,25 +7782,19 @@
         <v>0.35</v>
       </c>
       <c r="V71">
-        <v>5.25</v>
-      </c>
-      <c r="W71">
-        <v>5</v>
-      </c>
-      <c r="X71">
-        <v>25</v>
+        <v>19</v>
+      </c>
+      <c r="W71" t="s">
+        <v>226</v>
+      </c>
+      <c r="X71" t="s">
+        <v>216</v>
       </c>
       <c r="Y71" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z71" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA71" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>64</v>
       </c>
@@ -8241,7 +7811,7 @@
         <v>129</v>
       </c>
       <c r="F72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G72" t="s">
         <v>25</v>
@@ -8262,25 +7832,25 @@
         <v>0</v>
       </c>
       <c r="M72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N72" t="s">
         <v>80</v>
       </c>
       <c r="O72" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P72">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q72" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R72">
         <v>1</v>
       </c>
       <c r="S72">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T72" t="s">
         <v>237</v>
@@ -8289,25 +7859,19 @@
         <v>0.35</v>
       </c>
       <c r="V72">
-        <v>5.25</v>
-      </c>
-      <c r="W72">
-        <v>5</v>
-      </c>
-      <c r="X72">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="W72" t="s">
+        <v>226</v>
+      </c>
+      <c r="X72" t="s">
+        <v>216</v>
       </c>
       <c r="Y72" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z72" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA72" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>64</v>
       </c>
@@ -8324,7 +7888,7 @@
         <v>133</v>
       </c>
       <c r="F73" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G73" t="s">
         <v>25</v>
@@ -8345,52 +7909,46 @@
         <v>0</v>
       </c>
       <c r="M73" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N73" t="s">
         <v>80</v>
       </c>
       <c r="O73" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P73">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q73" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R73">
         <v>0.1</v>
       </c>
       <c r="S73">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T73" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U73">
         <v>0.7</v>
       </c>
       <c r="V73">
-        <v>10.5</v>
-      </c>
-      <c r="W73">
-        <v>5</v>
-      </c>
-      <c r="X73">
-        <v>22</v>
+        <v>9</v>
+      </c>
+      <c r="W73" t="s">
+        <v>226</v>
+      </c>
+      <c r="X73" t="s">
+        <v>216</v>
       </c>
       <c r="Y73" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z73" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA73" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>64</v>
       </c>
@@ -8407,16 +7965,16 @@
         <v>138</v>
       </c>
       <c r="F74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G74" t="s">
         <v>25</v>
       </c>
       <c r="H74" t="s">
+        <v>260</v>
+      </c>
+      <c r="I74" t="s">
         <v>261</v>
-      </c>
-      <c r="I74" t="s">
-        <v>262</v>
       </c>
       <c r="J74" t="s">
         <v>80</v>
@@ -8425,55 +7983,49 @@
         <v>0.7</v>
       </c>
       <c r="L74">
-        <v>24.5</v>
+        <v>32.9</v>
       </c>
       <c r="M74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N74" t="s">
         <v>80</v>
       </c>
       <c r="O74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P74">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q74" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R74">
         <v>0.6</v>
       </c>
       <c r="S74">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T74" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U74">
         <v>0.7</v>
       </c>
       <c r="V74">
-        <v>10.5</v>
-      </c>
-      <c r="W74">
-        <v>5</v>
-      </c>
-      <c r="X74">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="W74" t="s">
+        <v>226</v>
+      </c>
+      <c r="X74" t="s">
+        <v>25</v>
       </c>
       <c r="Y74" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z74" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA74" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>64</v>
       </c>
@@ -8490,7 +8042,7 @@
         <v>143</v>
       </c>
       <c r="F75" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G75" t="s">
         <v>25</v>
@@ -8511,52 +8063,46 @@
         <v>0</v>
       </c>
       <c r="M75" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N75" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O75" t="s">
         <v>80</v>
       </c>
       <c r="P75">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q75" t="s">
+        <v>220</v>
+      </c>
+      <c r="R75">
+        <v>1</v>
+      </c>
+      <c r="S75">
+        <v>20</v>
+      </c>
+      <c r="T75" t="s">
         <v>221</v>
-      </c>
-      <c r="R75">
-        <v>1</v>
-      </c>
-      <c r="S75">
-        <v>15</v>
-      </c>
-      <c r="T75" t="s">
-        <v>222</v>
       </c>
       <c r="U75">
         <v>0.7</v>
       </c>
       <c r="V75">
-        <v>10.5</v>
-      </c>
-      <c r="W75">
-        <v>5</v>
-      </c>
-      <c r="X75">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="W75" t="s">
+        <v>226</v>
+      </c>
+      <c r="X75" t="s">
+        <v>216</v>
       </c>
       <c r="Y75" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z75" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA75" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>64</v>
       </c>
@@ -8573,7 +8119,7 @@
         <v>149</v>
       </c>
       <c r="F76" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G76" t="s">
         <v>25</v>
@@ -8594,52 +8140,46 @@
         <v>0</v>
       </c>
       <c r="M76" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N76" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O76" t="s">
         <v>80</v>
       </c>
       <c r="P76">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q76" t="s">
+        <v>220</v>
+      </c>
+      <c r="R76">
+        <v>1</v>
+      </c>
+      <c r="S76">
+        <v>20</v>
+      </c>
+      <c r="T76" t="s">
         <v>221</v>
-      </c>
-      <c r="R76">
-        <v>1</v>
-      </c>
-      <c r="S76">
-        <v>15</v>
-      </c>
-      <c r="T76" t="s">
-        <v>222</v>
       </c>
       <c r="U76">
         <v>0.7</v>
       </c>
       <c r="V76">
-        <v>10.5</v>
-      </c>
-      <c r="W76">
-        <v>10</v>
-      </c>
-      <c r="X76">
-        <v>58</v>
+        <v>50</v>
+      </c>
+      <c r="W76" t="s">
+        <v>226</v>
+      </c>
+      <c r="X76" t="s">
+        <v>216</v>
       </c>
       <c r="Y76" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z76" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA76" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>64</v>
       </c>
@@ -8656,7 +8196,7 @@
         <v>155</v>
       </c>
       <c r="F77" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G77" t="s">
         <v>25</v>
@@ -8677,52 +8217,46 @@
         <v>0</v>
       </c>
       <c r="M77" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N77" t="s">
         <v>80</v>
       </c>
       <c r="O77" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P77">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q77" t="s">
+        <v>220</v>
+      </c>
+      <c r="R77">
+        <v>1</v>
+      </c>
+      <c r="S77">
+        <v>20</v>
+      </c>
+      <c r="T77" t="s">
         <v>221</v>
-      </c>
-      <c r="R77">
-        <v>1</v>
-      </c>
-      <c r="S77">
-        <v>15</v>
-      </c>
-      <c r="T77" t="s">
-        <v>222</v>
       </c>
       <c r="U77">
         <v>0.7</v>
       </c>
       <c r="V77">
-        <v>10.5</v>
-      </c>
-      <c r="W77">
-        <v>5</v>
-      </c>
-      <c r="X77">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="W77" t="s">
+        <v>226</v>
+      </c>
+      <c r="X77" t="s">
+        <v>216</v>
       </c>
       <c r="Y77" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z77" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA77" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>64</v>
       </c>
@@ -8739,7 +8273,7 @@
         <v>160</v>
       </c>
       <c r="F78" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G78" t="s">
         <v>25</v>
@@ -8760,52 +8294,46 @@
         <v>0</v>
       </c>
       <c r="M78" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N78" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O78" t="s">
         <v>80</v>
       </c>
       <c r="P78">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q78" t="s">
+        <v>220</v>
+      </c>
+      <c r="R78">
+        <v>1</v>
+      </c>
+      <c r="S78">
+        <v>20</v>
+      </c>
+      <c r="T78" t="s">
         <v>221</v>
-      </c>
-      <c r="R78">
-        <v>1</v>
-      </c>
-      <c r="S78">
-        <v>15</v>
-      </c>
-      <c r="T78" t="s">
-        <v>222</v>
       </c>
       <c r="U78">
         <v>0.7</v>
       </c>
       <c r="V78">
-        <v>10.5</v>
-      </c>
-      <c r="W78">
-        <v>10</v>
-      </c>
-      <c r="X78">
-        <v>58</v>
+        <v>50</v>
+      </c>
+      <c r="W78" t="s">
+        <v>226</v>
+      </c>
+      <c r="X78" t="s">
+        <v>216</v>
       </c>
       <c r="Y78" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z78" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA78" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>64</v>
       </c>
@@ -8822,7 +8350,7 @@
         <v>165</v>
       </c>
       <c r="F79" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G79" t="s">
         <v>25</v>
@@ -8840,28 +8368,28 @@
         <v>1</v>
       </c>
       <c r="L79">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="M79" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N79" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O79" t="s">
         <v>80</v>
       </c>
       <c r="P79">
-        <v>22.75</v>
+        <v>30.03</v>
       </c>
       <c r="Q79" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R79">
         <v>1</v>
       </c>
       <c r="S79">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T79" t="s">
         <v>231</v>
@@ -8870,25 +8398,19 @@
         <v>1</v>
       </c>
       <c r="V79">
-        <v>15</v>
-      </c>
-      <c r="W79">
-        <v>5</v>
-      </c>
-      <c r="X79">
-        <v>93</v>
+        <v>97</v>
+      </c>
+      <c r="W79" t="s">
+        <v>234</v>
+      </c>
+      <c r="X79" t="s">
+        <v>25</v>
       </c>
       <c r="Y79" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z79" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA79" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>74</v>
       </c>
@@ -8905,7 +8427,7 @@
         <v>96</v>
       </c>
       <c r="F80" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G80" t="s">
         <v>25</v>
@@ -8914,64 +8436,58 @@
         <v>80</v>
       </c>
       <c r="I80" t="s">
+        <v>262</v>
+      </c>
+      <c r="J80" t="s">
         <v>263</v>
-      </c>
-      <c r="J80" t="s">
-        <v>264</v>
       </c>
       <c r="K80">
         <v>0.1</v>
       </c>
       <c r="L80">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="M80" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N80" t="s">
         <v>80</v>
       </c>
       <c r="O80" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P80">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q80" t="s">
+        <v>220</v>
+      </c>
+      <c r="R80">
+        <v>1</v>
+      </c>
+      <c r="S80">
+        <v>20</v>
+      </c>
+      <c r="T80" t="s">
         <v>221</v>
-      </c>
-      <c r="R80">
-        <v>1</v>
-      </c>
-      <c r="S80">
-        <v>15</v>
-      </c>
-      <c r="T80" t="s">
-        <v>222</v>
       </c>
       <c r="U80">
         <v>0.7</v>
       </c>
       <c r="V80">
-        <v>10.5</v>
-      </c>
-      <c r="W80">
-        <v>10</v>
-      </c>
-      <c r="X80">
-        <v>44</v>
+        <v>32</v>
+      </c>
+      <c r="W80" t="s">
+        <v>226</v>
+      </c>
+      <c r="X80" t="s">
+        <v>216</v>
       </c>
       <c r="Y80" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z80" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA80" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>74</v>
       </c>
@@ -8988,7 +8504,7 @@
         <v>105</v>
       </c>
       <c r="F81" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G81" t="s">
         <v>25</v>
@@ -9009,52 +8525,46 @@
         <v>0</v>
       </c>
       <c r="M81" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N81" t="s">
         <v>80</v>
       </c>
       <c r="O81" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P81">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q81" t="s">
+        <v>220</v>
+      </c>
+      <c r="R81">
+        <v>1</v>
+      </c>
+      <c r="S81">
+        <v>20</v>
+      </c>
+      <c r="T81" t="s">
         <v>221</v>
-      </c>
-      <c r="R81">
-        <v>1</v>
-      </c>
-      <c r="S81">
-        <v>15</v>
-      </c>
-      <c r="T81" t="s">
-        <v>222</v>
       </c>
       <c r="U81">
         <v>0.7</v>
       </c>
       <c r="V81">
-        <v>10.5</v>
-      </c>
-      <c r="W81">
-        <v>10</v>
-      </c>
-      <c r="X81">
-        <v>41</v>
+        <v>27</v>
+      </c>
+      <c r="W81" t="s">
+        <v>226</v>
+      </c>
+      <c r="X81" t="s">
+        <v>216</v>
       </c>
       <c r="Y81" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z81" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA81" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>74</v>
       </c>
@@ -9071,46 +8581,46 @@
         <v>109</v>
       </c>
       <c r="F82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G82" t="s">
         <v>25</v>
       </c>
       <c r="H82" t="s">
+        <v>265</v>
+      </c>
+      <c r="I82" t="s">
+        <v>249</v>
+      </c>
+      <c r="J82" t="s">
         <v>266</v>
-      </c>
-      <c r="I82" t="s">
-        <v>250</v>
-      </c>
-      <c r="J82" t="s">
-        <v>267</v>
       </c>
       <c r="K82">
         <v>0.6</v>
       </c>
       <c r="L82">
-        <v>21</v>
+        <v>28.2</v>
       </c>
       <c r="M82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N82" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O82" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P82">
-        <v>14</v>
+        <v>18.48</v>
       </c>
       <c r="Q82" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R82">
         <v>1</v>
       </c>
       <c r="S82">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T82" t="s">
         <v>231</v>
@@ -9119,25 +8629,19 @@
         <v>1</v>
       </c>
       <c r="V82">
-        <v>15</v>
-      </c>
-      <c r="W82">
-        <v>10</v>
-      </c>
-      <c r="X82">
-        <v>75</v>
+        <v>67</v>
+      </c>
+      <c r="W82" t="s">
+        <v>222</v>
+      </c>
+      <c r="X82" t="s">
+        <v>25</v>
       </c>
       <c r="Y82" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z82" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA82" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>74</v>
       </c>
@@ -9154,73 +8658,67 @@
         <v>117</v>
       </c>
       <c r="F83" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G83" t="s">
         <v>25</v>
       </c>
       <c r="H83" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I83" t="s">
         <v>80</v>
       </c>
       <c r="J83" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K83">
         <v>0.25</v>
       </c>
       <c r="L83">
-        <v>8.75</v>
+        <v>11.75</v>
       </c>
       <c r="M83" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N83" t="s">
         <v>80</v>
       </c>
       <c r="O83" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P83">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q83" t="s">
+        <v>220</v>
+      </c>
+      <c r="R83">
+        <v>1</v>
+      </c>
+      <c r="S83">
+        <v>20</v>
+      </c>
+      <c r="T83" t="s">
         <v>221</v>
-      </c>
-      <c r="R83">
-        <v>1</v>
-      </c>
-      <c r="S83">
-        <v>15</v>
-      </c>
-      <c r="T83" t="s">
-        <v>222</v>
       </c>
       <c r="U83">
         <v>0.7</v>
       </c>
       <c r="V83">
-        <v>10.5</v>
-      </c>
-      <c r="W83">
-        <v>5</v>
-      </c>
-      <c r="X83">
-        <v>45</v>
+        <v>39</v>
+      </c>
+      <c r="W83" t="s">
+        <v>226</v>
+      </c>
+      <c r="X83" t="s">
+        <v>216</v>
       </c>
       <c r="Y83" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z83" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA83" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>74</v>
       </c>
@@ -9237,46 +8735,46 @@
         <v>123</v>
       </c>
       <c r="F84" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G84" t="s">
         <v>25</v>
       </c>
       <c r="H84" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I84" t="s">
         <v>80</v>
       </c>
       <c r="J84" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K84">
         <v>0.75</v>
       </c>
       <c r="L84">
-        <v>26.25</v>
+        <v>35.25</v>
       </c>
       <c r="M84" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N84" t="s">
         <v>80</v>
       </c>
       <c r="O84" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P84">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q84" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R84">
         <v>1</v>
       </c>
       <c r="S84">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T84" t="s">
         <v>237</v>
@@ -9285,25 +8783,19 @@
         <v>0.35</v>
       </c>
       <c r="V84">
-        <v>5.25</v>
-      </c>
-      <c r="W84">
-        <v>10</v>
-      </c>
-      <c r="X84">
         <v>62</v>
       </c>
+      <c r="W84" t="s">
+        <v>222</v>
+      </c>
+      <c r="X84" t="s">
+        <v>25</v>
+      </c>
       <c r="Y84" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z84" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA84" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>74</v>
       </c>
@@ -9320,7 +8812,7 @@
         <v>129</v>
       </c>
       <c r="F85" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G85" t="s">
         <v>25</v>
@@ -9338,28 +8830,28 @@
         <v>1</v>
       </c>
       <c r="L85">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="M85" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N85" t="s">
         <v>80</v>
       </c>
       <c r="O85" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P85">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q85" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R85">
         <v>1</v>
       </c>
       <c r="S85">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T85" t="s">
         <v>237</v>
@@ -9368,25 +8860,19 @@
         <v>0.35</v>
       </c>
       <c r="V85">
-        <v>5.25</v>
-      </c>
-      <c r="W85">
-        <v>10</v>
-      </c>
-      <c r="X85">
-        <v>71</v>
+        <v>74</v>
+      </c>
+      <c r="W85" t="s">
+        <v>222</v>
+      </c>
+      <c r="X85" t="s">
+        <v>25</v>
       </c>
       <c r="Y85" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z85" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA85" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>74</v>
       </c>
@@ -9403,7 +8889,7 @@
         <v>133</v>
       </c>
       <c r="F86" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G86" t="s">
         <v>25</v>
@@ -9412,64 +8898,58 @@
         <v>80</v>
       </c>
       <c r="I86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J86" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K86">
         <v>0.08</v>
       </c>
       <c r="L86">
-        <v>2.8</v>
+        <v>3.76</v>
       </c>
       <c r="M86" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N86" t="s">
         <v>80</v>
       </c>
       <c r="O86" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P86">
-        <v>5.25</v>
+        <v>6.93</v>
       </c>
       <c r="Q86" t="s">
+        <v>220</v>
+      </c>
+      <c r="R86">
+        <v>1</v>
+      </c>
+      <c r="S86">
+        <v>20</v>
+      </c>
+      <c r="T86" t="s">
         <v>221</v>
-      </c>
-      <c r="R86">
-        <v>1</v>
-      </c>
-      <c r="S86">
-        <v>15</v>
-      </c>
-      <c r="T86" t="s">
-        <v>222</v>
       </c>
       <c r="U86">
         <v>0.7</v>
       </c>
       <c r="V86">
-        <v>10.5</v>
-      </c>
-      <c r="W86">
-        <v>10</v>
-      </c>
-      <c r="X86">
-        <v>44</v>
+        <v>31</v>
+      </c>
+      <c r="W86" t="s">
+        <v>226</v>
+      </c>
+      <c r="X86" t="s">
+        <v>216</v>
       </c>
       <c r="Y86" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z86" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA86" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>74</v>
       </c>
@@ -9486,7 +8966,7 @@
         <v>138</v>
       </c>
       <c r="F87" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G87" t="s">
         <v>25</v>
@@ -9495,64 +8975,58 @@
         <v>80</v>
       </c>
       <c r="I87" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J87" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K87">
         <v>0.1</v>
       </c>
       <c r="L87">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="M87" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N87" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O87" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P87">
-        <v>14</v>
+        <v>18.48</v>
       </c>
       <c r="Q87" t="s">
+        <v>220</v>
+      </c>
+      <c r="R87">
+        <v>1</v>
+      </c>
+      <c r="S87">
+        <v>20</v>
+      </c>
+      <c r="T87" t="s">
         <v>221</v>
-      </c>
-      <c r="R87">
-        <v>1</v>
-      </c>
-      <c r="S87">
-        <v>15</v>
-      </c>
-      <c r="T87" t="s">
-        <v>222</v>
       </c>
       <c r="U87">
         <v>0.7</v>
       </c>
       <c r="V87">
-        <v>10.5</v>
-      </c>
-      <c r="W87">
-        <v>5</v>
-      </c>
-      <c r="X87">
-        <v>48</v>
+        <v>43</v>
+      </c>
+      <c r="W87" t="s">
+        <v>226</v>
+      </c>
+      <c r="X87" t="s">
+        <v>216</v>
       </c>
       <c r="Y87" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z87" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA87" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>74</v>
       </c>
@@ -9569,7 +9043,7 @@
         <v>143</v>
       </c>
       <c r="F88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G88" t="s">
         <v>25</v>
@@ -9590,52 +9064,46 @@
         <v>0</v>
       </c>
       <c r="M88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N88" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O88" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P88">
-        <v>14</v>
+        <v>18.48</v>
       </c>
       <c r="Q88" t="s">
+        <v>220</v>
+      </c>
+      <c r="R88">
+        <v>1</v>
+      </c>
+      <c r="S88">
+        <v>20</v>
+      </c>
+      <c r="T88" t="s">
         <v>221</v>
-      </c>
-      <c r="R88">
-        <v>1</v>
-      </c>
-      <c r="S88">
-        <v>15</v>
-      </c>
-      <c r="T88" t="s">
-        <v>222</v>
       </c>
       <c r="U88">
         <v>0.7</v>
       </c>
       <c r="V88">
-        <v>10.5</v>
-      </c>
-      <c r="W88">
-        <v>10</v>
-      </c>
-      <c r="X88">
-        <v>50</v>
+        <v>38</v>
+      </c>
+      <c r="W88" t="s">
+        <v>226</v>
+      </c>
+      <c r="X88" t="s">
+        <v>216</v>
       </c>
       <c r="Y88" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z88" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA88" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>74</v>
       </c>
@@ -9652,7 +9120,7 @@
         <v>149</v>
       </c>
       <c r="F89" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G89" t="s">
         <v>25</v>
@@ -9673,52 +9141,46 @@
         <v>0</v>
       </c>
       <c r="M89" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N89" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O89" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P89">
-        <v>14</v>
+        <v>18.48</v>
       </c>
       <c r="Q89" t="s">
+        <v>220</v>
+      </c>
+      <c r="R89">
+        <v>1</v>
+      </c>
+      <c r="S89">
+        <v>20</v>
+      </c>
+      <c r="T89" t="s">
         <v>221</v>
-      </c>
-      <c r="R89">
-        <v>1</v>
-      </c>
-      <c r="S89">
-        <v>15</v>
-      </c>
-      <c r="T89" t="s">
-        <v>222</v>
       </c>
       <c r="U89">
         <v>0.7</v>
       </c>
       <c r="V89">
-        <v>10.5</v>
-      </c>
-      <c r="W89">
-        <v>10</v>
-      </c>
-      <c r="X89">
-        <v>50</v>
+        <v>38</v>
+      </c>
+      <c r="W89" t="s">
+        <v>226</v>
+      </c>
+      <c r="X89" t="s">
+        <v>216</v>
       </c>
       <c r="Y89" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z89" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA89" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>74</v>
       </c>
@@ -9735,7 +9197,7 @@
         <v>155</v>
       </c>
       <c r="F90" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G90" t="s">
         <v>25</v>
@@ -9756,52 +9218,46 @@
         <v>0</v>
       </c>
       <c r="M90" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N90" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O90" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P90">
-        <v>14</v>
+        <v>18.48</v>
       </c>
       <c r="Q90" t="s">
+        <v>220</v>
+      </c>
+      <c r="R90">
+        <v>1</v>
+      </c>
+      <c r="S90">
+        <v>20</v>
+      </c>
+      <c r="T90" t="s">
         <v>221</v>
-      </c>
-      <c r="R90">
-        <v>1</v>
-      </c>
-      <c r="S90">
-        <v>15</v>
-      </c>
-      <c r="T90" t="s">
-        <v>222</v>
       </c>
       <c r="U90">
         <v>0.7</v>
       </c>
       <c r="V90">
-        <v>10.5</v>
-      </c>
-      <c r="W90">
-        <v>10</v>
-      </c>
-      <c r="X90">
-        <v>50</v>
+        <v>38</v>
+      </c>
+      <c r="W90" t="s">
+        <v>226</v>
+      </c>
+      <c r="X90" t="s">
+        <v>216</v>
       </c>
       <c r="Y90" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z90" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA90" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>74</v>
       </c>
@@ -9818,7 +9274,7 @@
         <v>160</v>
       </c>
       <c r="F91" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G91" t="s">
         <v>25</v>
@@ -9839,52 +9295,46 @@
         <v>0</v>
       </c>
       <c r="M91" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N91" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O91" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P91">
-        <v>14</v>
+        <v>18.48</v>
       </c>
       <c r="Q91" t="s">
+        <v>220</v>
+      </c>
+      <c r="R91">
+        <v>1</v>
+      </c>
+      <c r="S91">
+        <v>20</v>
+      </c>
+      <c r="T91" t="s">
         <v>221</v>
-      </c>
-      <c r="R91">
-        <v>1</v>
-      </c>
-      <c r="S91">
-        <v>15</v>
-      </c>
-      <c r="T91" t="s">
-        <v>222</v>
       </c>
       <c r="U91">
         <v>0.7</v>
       </c>
       <c r="V91">
-        <v>10.5</v>
-      </c>
-      <c r="W91">
-        <v>5</v>
-      </c>
-      <c r="X91">
-        <v>45</v>
+        <v>38</v>
+      </c>
+      <c r="W91" t="s">
+        <v>226</v>
+      </c>
+      <c r="X91" t="s">
+        <v>216</v>
       </c>
       <c r="Y91" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z91" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA91" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>74</v>
       </c>
@@ -9901,7 +9351,7 @@
         <v>165</v>
       </c>
       <c r="F92" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G92" t="s">
         <v>25</v>
@@ -9922,25 +9372,25 @@
         <v>0</v>
       </c>
       <c r="M92" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N92" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O92" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P92">
-        <v>14</v>
+        <v>18.48</v>
       </c>
       <c r="Q92" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R92">
         <v>1</v>
       </c>
       <c r="S92">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T92" t="s">
         <v>231</v>
@@ -9949,22 +9399,16 @@
         <v>1</v>
       </c>
       <c r="V92">
-        <v>15</v>
-      </c>
-      <c r="W92">
-        <v>5</v>
-      </c>
-      <c r="X92">
-        <v>49</v>
+        <v>38</v>
+      </c>
+      <c r="W92" t="s">
+        <v>226</v>
+      </c>
+      <c r="X92" t="s">
+        <v>216</v>
       </c>
       <c r="Y92" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z92" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA92" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/thesis-recommendation-dataset.xlsx
+++ b/thesis-recommendation-dataset.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="311">
   <si>
     <t>PWD ID</t>
   </si>
@@ -550,6 +550,12 @@
     <t>Points for how the applicant's highest education compares to the job's minimum requirement.</t>
   </si>
   <si>
+    <t>Weight: Semantic (ML)</t>
+  </si>
+  <si>
+    <t>Points from real TF-IDF + Cosine Similarity (semantic.ts) between the applicant's skills/education/experience text and the listing's title/skills/description, normalized against this applicant's best-matching candidate job.</t>
+  </si>
+  <si>
     <t>Location (not scored)</t>
   </si>
   <si>
@@ -622,7 +628,7 @@
     <t>Skill Coverage (0-1)</t>
   </si>
   <si>
-    <t>Skills Points (/47)</t>
+    <t>Skills Points (/35)</t>
   </si>
   <si>
     <t>Disability Listed?</t>
@@ -634,7 +640,7 @@
     <t>Accommodations Unmet</t>
   </si>
   <si>
-    <t>Suitability Points (/33)</t>
+    <t>Suitability Points (/25)</t>
   </si>
   <si>
     <t>Education Status</t>
@@ -643,7 +649,16 @@
     <t>Education Fraction (0-1)</t>
   </si>
   <si>
-    <t>Education Points (/20)</t>
+    <t>Education Points (/15)</t>
+  </si>
+  <si>
+    <t>Semantic Similarity (0-1, ML)</t>
+  </si>
+  <si>
+    <t>Semantic Shared Terms</t>
+  </si>
+  <si>
+    <t>Semantic Points (/25)</t>
   </si>
   <si>
     <t>Location Level (filter only, not scored)</t>
@@ -679,54 +694,69 @@
     <t>Met</t>
   </si>
   <si>
+    <t>data, entry, computer</t>
+  </si>
+  <si>
     <t>municipality</t>
   </si>
   <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Computer Literacy, Microsoft Office</t>
+  </si>
+  <si>
+    <t>Network Troubleshooting</t>
+  </si>
+  <si>
+    <t>HTML, CSS</t>
+  </si>
+  <si>
+    <t>computer, office, microsoft</t>
+  </si>
+  <si>
+    <t>Fair</t>
+  </si>
+  <si>
+    <t>Communication</t>
+  </si>
+  <si>
+    <t>English Proficiency</t>
+  </si>
+  <si>
+    <t>Writing, Research</t>
+  </si>
+  <si>
+    <t>Wheelchair-accessible workplace, Screen-reader-compatible tools, Assistive technology provided</t>
+  </si>
+  <si>
+    <t>communication</t>
+  </si>
+  <si>
+    <t>remote</t>
+  </si>
+  <si>
+    <t>Microsoft Office, Computer Literacy, Customer Service</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>office, computer, customer</t>
+  </si>
+  <si>
     <t>Good</t>
   </si>
   <si>
-    <t>Computer Literacy, Microsoft Office</t>
-  </si>
-  <si>
-    <t>Network Troubleshooting</t>
-  </si>
-  <si>
-    <t>HTML, CSS</t>
-  </si>
-  <si>
-    <t>Fair</t>
-  </si>
-  <si>
-    <t>Communication</t>
-  </si>
-  <si>
-    <t>English Proficiency</t>
-  </si>
-  <si>
-    <t>Writing, Research</t>
-  </si>
-  <si>
-    <t>Wheelchair-accessible workplace, Screen-reader-compatible tools, Assistive technology provided</t>
-  </si>
-  <si>
-    <t>remote</t>
-  </si>
-  <si>
-    <t>Microsoft Office, Computer Literacy, Customer Service</t>
-  </si>
-  <si>
-    <t>Administration</t>
-  </si>
-  <si>
-    <t>Excellent</t>
-  </si>
-  <si>
     <t>Communication, Customer Service, Computer Literacy</t>
   </si>
   <si>
     <t>Screen-reader-compatible tools</t>
   </si>
   <si>
+    <t>customer, service, computer</t>
+  </si>
+  <si>
     <t>province</t>
   </si>
   <si>
@@ -736,12 +766,30 @@
     <t>English Proficiency, Typing</t>
   </si>
   <si>
+    <t>customer, communication, service</t>
+  </si>
+  <si>
     <t>Microsoft Excel, Data Entry</t>
   </si>
   <si>
     <t>Accounting, Bookkeeping</t>
   </si>
   <si>
+    <t>data, entry, microsoft</t>
+  </si>
+  <si>
+    <t>office</t>
+  </si>
+  <si>
+    <t>shop</t>
+  </si>
+  <si>
+    <t>data, entry, records</t>
+  </si>
+  <si>
+    <t>office, computer, literacy</t>
+  </si>
+  <si>
     <t>barangay</t>
   </si>
   <si>
@@ -751,15 +799,36 @@
     <t>Customer Service</t>
   </si>
   <si>
+    <t>administration, office, records</t>
+  </si>
+  <si>
     <t>Computer Literacy</t>
   </si>
   <si>
     <t>Communication, Customer Service, English Proficiency</t>
   </si>
   <si>
+    <t>computer, literacy</t>
+  </si>
+  <si>
     <t>Typing</t>
   </si>
   <si>
+    <t>typing</t>
+  </si>
+  <si>
+    <t>data, entry, encoding</t>
+  </si>
+  <si>
+    <t>office, assistant</t>
+  </si>
+  <si>
+    <t>public, assistant</t>
+  </si>
+  <si>
+    <t>barangay, assistant</t>
+  </si>
+  <si>
     <t>Sign-language interpreter, Written instructions</t>
   </si>
   <si>
@@ -769,9 +838,15 @@
     <t>English Proficiency, Research</t>
   </si>
   <si>
+    <t>writing, social, media</t>
+  </si>
+  <si>
     <t>Communication, Customer Service, Typing</t>
   </si>
   <si>
+    <t>social, media, design</t>
+  </si>
+  <si>
     <t>Written instructions</t>
   </si>
   <si>
@@ -784,24 +859,57 @@
     <t>Video Editing, Videography</t>
   </si>
   <si>
+    <t>freelance, photography, social</t>
+  </si>
+  <si>
     <t>Not met</t>
   </si>
   <si>
     <t>Flexible hours</t>
   </si>
   <si>
+    <t>horticulture, plant, care</t>
+  </si>
+  <si>
+    <t>helper</t>
+  </si>
+  <si>
+    <t>carpentry, manual, labor</t>
+  </si>
+  <si>
     <t>Nearly met</t>
   </si>
   <si>
+    <t>processing</t>
+  </si>
+  <si>
+    <t>food, baking, safety</t>
+  </si>
+  <si>
+    <t>food, cooking, kitchen</t>
+  </si>
+  <si>
+    <t>assistant</t>
+  </si>
+  <si>
     <t>English Proficiency, Communication, Research</t>
   </si>
   <si>
+    <t>social, media</t>
+  </si>
+  <si>
     <t>Social Media, Photography</t>
   </si>
   <si>
     <t>Writing, Design</t>
   </si>
   <si>
+    <t>social, media, photography</t>
+  </si>
+  <si>
+    <t>video, videography, editing</t>
+  </si>
+  <si>
     <t>Data Entry</t>
   </si>
   <si>
@@ -811,6 +919,9 @@
     <t>Flexible hours, Quiet workspace</t>
   </si>
   <si>
+    <t>support</t>
+  </si>
+  <si>
     <t>English Proficiency, Communication</t>
   </si>
   <si>
@@ -818,6 +929,18 @@
   </si>
   <si>
     <t>Quiet workspace</t>
+  </si>
+  <si>
+    <t>communication, english, proficiency</t>
+  </si>
+  <si>
+    <t>customer, support, service</t>
+  </si>
+  <si>
+    <t>customer, service, communication</t>
+  </si>
+  <si>
+    <t>customer, call, center</t>
   </si>
   <si>
     <t>Accounting, Bookkeeping, Microsoft Excel, Attention to Detail</t>
@@ -2180,7 +2303,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2204,7 +2327,7 @@
         <v>172</v>
       </c>
       <c r="B2">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
         <v>173</v>
@@ -2215,7 +2338,7 @@
         <v>174</v>
       </c>
       <c r="B3">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
         <v>175</v>
@@ -2226,7 +2349,7 @@
         <v>176</v>
       </c>
       <c r="B4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>177</v>
@@ -2236,19 +2359,19 @@
       <c r="A5" t="s">
         <v>178</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
         <v>179</v>
-      </c>
-      <c r="C5" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" t="s">
         <v>181</v>
-      </c>
-      <c r="B6" t="s">
-        <v>179</v>
       </c>
       <c r="C6" t="s">
         <v>182</v>
@@ -2258,8 +2381,8 @@
       <c r="A7" t="s">
         <v>183</v>
       </c>
-      <c r="B7">
-        <v>40</v>
+      <c r="B7" t="s">
+        <v>181</v>
       </c>
       <c r="C7" t="s">
         <v>184</v>
@@ -2269,33 +2392,44 @@
       <c r="A8" t="s">
         <v>185</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
         <v>186</v>
-      </c>
-      <c r="C8" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" t="s">
         <v>188</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>189</v>
-      </c>
-      <c r="C9" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" t="s">
         <v>191</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>192</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>193</v>
+      </c>
+      <c r="B11" t="s">
+        <v>194</v>
+      </c>
+      <c r="C11" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -2306,7 +2440,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y92"/>
+  <dimension ref="A1:AB92"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2321,18 +2455,21 @@
     <col min="14" max="15" width="26" customWidth="1"/>
     <col min="16" max="18" width="14" customWidth="1"/>
     <col min="19" max="19" width="12" customWidth="1"/>
-    <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="22" width="14" customWidth="1"/>
-    <col min="23" max="23" width="12" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="21" max="21" width="26" customWidth="1"/>
+    <col min="22" max="22" width="12" customWidth="1"/>
+    <col min="23" max="23" width="18" customWidth="1"/>
     <col min="24" max="25" width="14" customWidth="1"/>
+    <col min="26" max="26" width="12" customWidth="1"/>
+    <col min="27" max="28" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
@@ -2341,70 +2478,79 @@
         <v>82</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -2421,67 +2567,76 @@
         <v>96</v>
       </c>
       <c r="F2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G2" t="s">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I2" t="s">
         <v>80</v>
       </c>
       <c r="J2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="K2">
         <v>0.75</v>
       </c>
       <c r="L2">
-        <v>35.25</v>
+        <v>26.25</v>
       </c>
       <c r="M2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N2" t="s">
         <v>101</v>
       </c>
       <c r="O2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="P2">
-        <v>14.63</v>
+        <v>11.08</v>
       </c>
       <c r="Q2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R2">
         <v>1</v>
       </c>
       <c r="S2">
-        <v>20</v>
-      </c>
-      <c r="T2" t="s">
-        <v>221</v>
-      </c>
-      <c r="U2">
+        <v>15</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2" t="s">
+        <v>226</v>
+      </c>
+      <c r="V2">
+        <v>25</v>
+      </c>
+      <c r="W2" t="s">
+        <v>227</v>
+      </c>
+      <c r="X2">
         <v>0.7</v>
       </c>
-      <c r="V2">
-        <v>70</v>
-      </c>
-      <c r="W2" t="s">
-        <v>222</v>
-      </c>
-      <c r="X2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y2">
+        <v>77</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -2498,67 +2653,76 @@
         <v>105</v>
       </c>
       <c r="F3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G3" t="s">
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="I3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="J3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="K3">
         <v>0.48</v>
       </c>
       <c r="L3">
-        <v>22.56</v>
+        <v>16.8</v>
       </c>
       <c r="M3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N3" t="s">
         <v>101</v>
       </c>
       <c r="O3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="P3">
-        <v>14.63</v>
+        <v>11.08</v>
       </c>
       <c r="Q3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R3">
         <v>1</v>
       </c>
       <c r="S3">
-        <v>20</v>
-      </c>
-      <c r="T3" t="s">
-        <v>221</v>
-      </c>
-      <c r="U3">
+        <v>15</v>
+      </c>
+      <c r="T3">
+        <v>0.518</v>
+      </c>
+      <c r="U3" t="s">
+        <v>232</v>
+      </c>
+      <c r="V3">
+        <v>12.95</v>
+      </c>
+      <c r="W3" t="s">
+        <v>227</v>
+      </c>
+      <c r="X3">
         <v>0.7</v>
       </c>
-      <c r="V3">
-        <v>57</v>
-      </c>
-      <c r="W3" t="s">
-        <v>226</v>
-      </c>
-      <c r="X3" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y3">
+        <v>56</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -2575,67 +2739,76 @@
         <v>109</v>
       </c>
       <c r="F4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G4" t="s">
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="I4" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="J4" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="K4">
         <v>0.35</v>
       </c>
       <c r="L4">
-        <v>16.45</v>
+        <v>12.25</v>
       </c>
       <c r="M4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N4" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="O4" t="s">
         <v>80</v>
       </c>
       <c r="P4">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R4">
         <v>1</v>
       </c>
       <c r="S4">
-        <v>20</v>
-      </c>
-      <c r="T4" t="s">
-        <v>231</v>
-      </c>
-      <c r="U4">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="T4">
+        <v>0.083</v>
+      </c>
+      <c r="U4" t="s">
+        <v>238</v>
       </c>
       <c r="V4">
-        <v>66</v>
+        <v>2.06</v>
       </c>
       <c r="W4" t="s">
-        <v>222</v>
-      </c>
-      <c r="X4" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>52</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -2652,16 +2825,16 @@
         <v>117</v>
       </c>
       <c r="F5" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G5" t="s">
         <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="I5" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="J5" t="s">
         <v>80</v>
@@ -2670,49 +2843,58 @@
         <v>0.85</v>
       </c>
       <c r="L5">
-        <v>39.95</v>
+        <v>29.75</v>
       </c>
       <c r="M5" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N5" t="s">
         <v>101</v>
       </c>
       <c r="O5" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="P5">
-        <v>14.63</v>
+        <v>11.08</v>
       </c>
       <c r="Q5" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R5">
         <v>1</v>
       </c>
       <c r="S5">
-        <v>20</v>
-      </c>
-      <c r="T5" t="s">
-        <v>221</v>
-      </c>
-      <c r="U5">
+        <v>15</v>
+      </c>
+      <c r="T5">
+        <v>0.707</v>
+      </c>
+      <c r="U5" t="s">
+        <v>242</v>
+      </c>
+      <c r="V5">
+        <v>17.69</v>
+      </c>
+      <c r="W5" t="s">
+        <v>227</v>
+      </c>
+      <c r="X5">
         <v>0.7</v>
       </c>
-      <c r="V5">
-        <v>75</v>
-      </c>
-      <c r="W5" t="s">
-        <v>234</v>
-      </c>
-      <c r="X5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y5">
+        <v>74</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>243</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2729,16 +2911,16 @@
         <v>123</v>
       </c>
       <c r="F6" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G6" t="s">
         <v>25</v>
       </c>
       <c r="H6" t="s">
+        <v>244</v>
+      </c>
+      <c r="I6" t="s">
         <v>235</v>
-      </c>
-      <c r="I6" t="s">
-        <v>228</v>
       </c>
       <c r="J6" t="s">
         <v>80</v>
@@ -2747,49 +2929,58 @@
         <v>0.85</v>
       </c>
       <c r="L6">
-        <v>39.95</v>
+        <v>29.75</v>
       </c>
       <c r="M6" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N6" t="s">
         <v>127</v>
       </c>
       <c r="O6" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="P6">
-        <v>22.33</v>
+        <v>16.92</v>
       </c>
       <c r="Q6" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R6">
         <v>1</v>
       </c>
       <c r="S6">
-        <v>20</v>
-      </c>
-      <c r="T6" t="s">
-        <v>237</v>
-      </c>
-      <c r="U6">
+        <v>15</v>
+      </c>
+      <c r="T6">
+        <v>0.879</v>
+      </c>
+      <c r="U6" t="s">
+        <v>246</v>
+      </c>
+      <c r="V6">
+        <v>21.97</v>
+      </c>
+      <c r="W6" t="s">
+        <v>247</v>
+      </c>
+      <c r="X6">
         <v>0.35</v>
       </c>
-      <c r="V6">
-        <v>82</v>
-      </c>
-      <c r="W6" t="s">
-        <v>234</v>
-      </c>
-      <c r="X6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y6">
+        <v>84</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2806,16 +2997,16 @@
         <v>129</v>
       </c>
       <c r="F7" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G7" t="s">
         <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="I7" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="J7" t="s">
         <v>80</v>
@@ -2824,49 +3015,58 @@
         <v>0.7</v>
       </c>
       <c r="L7">
-        <v>32.9</v>
+        <v>24.5</v>
       </c>
       <c r="M7" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N7" t="s">
         <v>127</v>
       </c>
       <c r="O7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="P7">
-        <v>22.33</v>
+        <v>16.92</v>
       </c>
       <c r="Q7" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R7">
         <v>1</v>
       </c>
       <c r="S7">
-        <v>20</v>
-      </c>
-      <c r="T7" t="s">
-        <v>237</v>
-      </c>
-      <c r="U7">
+        <v>15</v>
+      </c>
+      <c r="T7">
+        <v>0.332</v>
+      </c>
+      <c r="U7" t="s">
+        <v>250</v>
+      </c>
+      <c r="V7">
+        <v>8.3</v>
+      </c>
+      <c r="W7" t="s">
+        <v>247</v>
+      </c>
+      <c r="X7">
         <v>0.35</v>
       </c>
-      <c r="V7">
-        <v>75</v>
-      </c>
-      <c r="W7" t="s">
-        <v>234</v>
-      </c>
-      <c r="X7" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y7">
+        <v>65</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>243</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2883,67 +3083,76 @@
         <v>133</v>
       </c>
       <c r="F8" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G8" t="s">
         <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="I8" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="J8" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="K8">
         <v>0.56</v>
       </c>
       <c r="L8">
-        <v>26.32</v>
+        <v>19.6</v>
       </c>
       <c r="M8" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N8" t="s">
         <v>101</v>
       </c>
       <c r="O8" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="P8">
-        <v>14.63</v>
+        <v>11.08</v>
       </c>
       <c r="Q8" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R8">
         <v>1</v>
       </c>
       <c r="S8">
-        <v>20</v>
-      </c>
-      <c r="T8" t="s">
-        <v>221</v>
-      </c>
-      <c r="U8">
+        <v>15</v>
+      </c>
+      <c r="T8">
+        <v>0.282</v>
+      </c>
+      <c r="U8" t="s">
+        <v>253</v>
+      </c>
+      <c r="V8">
+        <v>7.05</v>
+      </c>
+      <c r="W8" t="s">
+        <v>227</v>
+      </c>
+      <c r="X8">
         <v>0.7</v>
       </c>
-      <c r="V8">
-        <v>61</v>
-      </c>
-      <c r="W8" t="s">
-        <v>222</v>
-      </c>
-      <c r="X8" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y8">
+        <v>53</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -2960,7 +3169,7 @@
         <v>138</v>
       </c>
       <c r="F9" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G9" t="s">
         <v>25</v>
@@ -2981,46 +3190,55 @@
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="O9" t="s">
         <v>127</v>
       </c>
       <c r="P9">
-        <v>14.63</v>
+        <v>11.08</v>
       </c>
       <c r="Q9" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R9">
         <v>1</v>
       </c>
       <c r="S9">
-        <v>20</v>
-      </c>
-      <c r="T9" t="s">
-        <v>221</v>
-      </c>
-      <c r="U9">
+        <v>15</v>
+      </c>
+      <c r="T9">
+        <v>0.068</v>
+      </c>
+      <c r="U9" t="s">
+        <v>254</v>
+      </c>
+      <c r="V9">
+        <v>1.69</v>
+      </c>
+      <c r="W9" t="s">
+        <v>227</v>
+      </c>
+      <c r="X9">
         <v>0.7</v>
       </c>
-      <c r="V9">
-        <v>35</v>
-      </c>
-      <c r="W9" t="s">
-        <v>226</v>
-      </c>
-      <c r="X9" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y9">
+        <v>28</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -3037,7 +3255,7 @@
         <v>143</v>
       </c>
       <c r="F10" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G10" t="s">
         <v>25</v>
@@ -3058,46 +3276,55 @@
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N10" t="s">
         <v>80</v>
       </c>
       <c r="O10" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="P10">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q10" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R10">
         <v>1</v>
       </c>
       <c r="S10">
+        <v>15</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10" t="s">
+        <v>80</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10" t="s">
+        <v>227</v>
+      </c>
+      <c r="X10">
+        <v>0.7</v>
+      </c>
+      <c r="Y10">
         <v>20</v>
       </c>
-      <c r="T10" t="s">
-        <v>221</v>
-      </c>
-      <c r="U10">
-        <v>0.7</v>
-      </c>
-      <c r="V10">
-        <v>27</v>
-      </c>
-      <c r="W10" t="s">
-        <v>226</v>
-      </c>
-      <c r="X10" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z10" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -3114,7 +3341,7 @@
         <v>149</v>
       </c>
       <c r="F11" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G11" t="s">
         <v>25</v>
@@ -3135,46 +3362,55 @@
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N11" t="s">
         <v>80</v>
       </c>
       <c r="O11" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="P11">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q11" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R11">
         <v>1</v>
       </c>
       <c r="S11">
+        <v>15</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11" t="s">
+        <v>80</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11" t="s">
+        <v>227</v>
+      </c>
+      <c r="X11">
+        <v>0.7</v>
+      </c>
+      <c r="Y11">
         <v>20</v>
       </c>
-      <c r="T11" t="s">
-        <v>221</v>
-      </c>
-      <c r="U11">
-        <v>0.7</v>
-      </c>
-      <c r="V11">
-        <v>27</v>
-      </c>
-      <c r="W11" t="s">
-        <v>226</v>
-      </c>
-      <c r="X11" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z11" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -3191,7 +3427,7 @@
         <v>155</v>
       </c>
       <c r="F12" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G12" t="s">
         <v>25</v>
@@ -3212,46 +3448,55 @@
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N12" t="s">
         <v>101</v>
       </c>
       <c r="O12" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="P12">
-        <v>14.63</v>
+        <v>11.08</v>
       </c>
       <c r="Q12" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R12">
         <v>1</v>
       </c>
       <c r="S12">
-        <v>20</v>
-      </c>
-      <c r="T12" t="s">
-        <v>221</v>
-      </c>
-      <c r="U12">
+        <v>15</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12" t="s">
+        <v>80</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12" t="s">
+        <v>227</v>
+      </c>
+      <c r="X12">
         <v>0.7</v>
       </c>
-      <c r="V12">
-        <v>35</v>
-      </c>
-      <c r="W12" t="s">
-        <v>226</v>
-      </c>
-      <c r="X12" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y12">
+        <v>26</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -3268,7 +3513,7 @@
         <v>160</v>
       </c>
       <c r="F13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G13" t="s">
         <v>25</v>
@@ -3289,46 +3534,55 @@
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N13" t="s">
         <v>80</v>
       </c>
       <c r="O13" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="P13">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q13" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R13">
         <v>1</v>
       </c>
       <c r="S13">
-        <v>20</v>
-      </c>
-      <c r="T13" t="s">
-        <v>221</v>
-      </c>
-      <c r="U13">
+        <v>15</v>
+      </c>
+      <c r="T13">
+        <v>0.155</v>
+      </c>
+      <c r="U13" t="s">
+        <v>255</v>
+      </c>
+      <c r="V13">
+        <v>3.87</v>
+      </c>
+      <c r="W13" t="s">
+        <v>227</v>
+      </c>
+      <c r="X13">
         <v>0.7</v>
       </c>
-      <c r="V13">
-        <v>27</v>
-      </c>
-      <c r="W13" t="s">
-        <v>226</v>
-      </c>
-      <c r="X13" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y13">
+        <v>24</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -3345,7 +3599,7 @@
         <v>165</v>
       </c>
       <c r="F14" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G14" t="s">
         <v>25</v>
@@ -3366,46 +3620,55 @@
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N14" t="s">
         <v>101</v>
       </c>
       <c r="O14" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="P14">
-        <v>14.63</v>
+        <v>11.08</v>
       </c>
       <c r="Q14" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R14">
         <v>1</v>
       </c>
       <c r="S14">
-        <v>20</v>
-      </c>
-      <c r="T14" t="s">
-        <v>231</v>
-      </c>
-      <c r="U14">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14" t="s">
+        <v>80</v>
       </c>
       <c r="V14">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="W14" t="s">
-        <v>226</v>
-      </c>
-      <c r="X14" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+      <c r="X14">
+        <v>1</v>
+      </c>
+      <c r="Y14">
+        <v>26</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -3422,28 +3685,28 @@
         <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G15" t="s">
         <v>25</v>
       </c>
       <c r="H15" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I15" t="s">
         <v>80</v>
       </c>
       <c r="J15" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="K15">
         <v>0.75</v>
       </c>
       <c r="L15">
-        <v>35.25</v>
+        <v>26.25</v>
       </c>
       <c r="M15" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N15" t="s">
         <v>101</v>
@@ -3452,37 +3715,46 @@
         <v>80</v>
       </c>
       <c r="P15">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q15" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R15">
         <v>1</v>
       </c>
       <c r="S15">
-        <v>20</v>
-      </c>
-      <c r="T15" t="s">
-        <v>221</v>
-      </c>
-      <c r="U15">
+        <v>15</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15" t="s">
+        <v>256</v>
+      </c>
+      <c r="V15">
+        <v>25</v>
+      </c>
+      <c r="W15" t="s">
+        <v>227</v>
+      </c>
+      <c r="X15">
         <v>0.7</v>
       </c>
-      <c r="V15">
-        <v>85</v>
-      </c>
-      <c r="W15" t="s">
-        <v>234</v>
-      </c>
-      <c r="X15" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y15">
+        <v>89</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -3499,28 +3771,28 @@
         <v>105</v>
       </c>
       <c r="F16" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G16" t="s">
         <v>25</v>
       </c>
       <c r="H16" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="I16" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="J16" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="K16">
         <v>0.48</v>
       </c>
       <c r="L16">
-        <v>22.56</v>
+        <v>16.8</v>
       </c>
       <c r="M16" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N16" t="s">
         <v>101</v>
@@ -3529,37 +3801,46 @@
         <v>80</v>
       </c>
       <c r="P16">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q16" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R16">
         <v>1</v>
       </c>
       <c r="S16">
-        <v>20</v>
-      </c>
-      <c r="T16" t="s">
-        <v>242</v>
-      </c>
-      <c r="U16">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="T16">
+        <v>0.29</v>
+      </c>
+      <c r="U16" t="s">
+        <v>257</v>
       </c>
       <c r="V16">
-        <v>73</v>
+        <v>7.25</v>
       </c>
       <c r="W16" t="s">
-        <v>222</v>
-      </c>
-      <c r="X16" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
+        <v>62</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>243</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3576,7 +3857,7 @@
         <v>109</v>
       </c>
       <c r="F17" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G17" t="s">
         <v>25</v>
@@ -3597,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N17" t="s">
         <v>101</v>
@@ -3606,37 +3887,46 @@
         <v>80</v>
       </c>
       <c r="P17">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q17" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R17">
         <v>1</v>
       </c>
       <c r="S17">
-        <v>20</v>
-      </c>
-      <c r="T17" t="s">
-        <v>231</v>
-      </c>
-      <c r="U17">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17" t="s">
+        <v>80</v>
       </c>
       <c r="V17">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W17" t="s">
-        <v>226</v>
-      </c>
-      <c r="X17" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>38</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -3653,28 +3943,28 @@
         <v>117</v>
       </c>
       <c r="F18" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G18" t="s">
         <v>25</v>
       </c>
       <c r="H18" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="I18" t="s">
         <v>80</v>
       </c>
       <c r="J18" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="K18">
         <v>0.75</v>
       </c>
       <c r="L18">
-        <v>35.25</v>
+        <v>26.25</v>
       </c>
       <c r="M18" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N18" t="s">
         <v>101</v>
@@ -3683,37 +3973,46 @@
         <v>80</v>
       </c>
       <c r="P18">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q18" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R18">
         <v>1</v>
       </c>
       <c r="S18">
-        <v>20</v>
-      </c>
-      <c r="T18" t="s">
-        <v>221</v>
-      </c>
-      <c r="U18">
+        <v>15</v>
+      </c>
+      <c r="T18">
+        <v>0.739</v>
+      </c>
+      <c r="U18" t="s">
+        <v>261</v>
+      </c>
+      <c r="V18">
+        <v>18.47</v>
+      </c>
+      <c r="W18" t="s">
+        <v>227</v>
+      </c>
+      <c r="X18">
         <v>0.7</v>
       </c>
-      <c r="V18">
-        <v>85</v>
-      </c>
-      <c r="W18" t="s">
-        <v>234</v>
-      </c>
-      <c r="X18" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y18">
+        <v>82</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -3730,28 +4029,28 @@
         <v>123</v>
       </c>
       <c r="F19" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G19" t="s">
         <v>25</v>
       </c>
       <c r="H19" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="I19" t="s">
         <v>80</v>
       </c>
       <c r="J19" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="K19">
         <v>0.25</v>
       </c>
       <c r="L19">
-        <v>11.75</v>
+        <v>8.75</v>
       </c>
       <c r="M19" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N19" t="s">
         <v>101</v>
@@ -3760,37 +4059,46 @@
         <v>80</v>
       </c>
       <c r="P19">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q19" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R19">
         <v>1</v>
       </c>
       <c r="S19">
-        <v>20</v>
-      </c>
-      <c r="T19" t="s">
-        <v>237</v>
-      </c>
-      <c r="U19">
+        <v>15</v>
+      </c>
+      <c r="T19">
+        <v>0.126</v>
+      </c>
+      <c r="U19" t="s">
+        <v>264</v>
+      </c>
+      <c r="V19">
+        <v>3.15</v>
+      </c>
+      <c r="W19" t="s">
+        <v>247</v>
+      </c>
+      <c r="X19">
         <v>0.35</v>
       </c>
-      <c r="V19">
-        <v>62</v>
-      </c>
-      <c r="W19" t="s">
-        <v>222</v>
-      </c>
-      <c r="X19" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y19">
+        <v>50</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -3807,28 +4115,28 @@
         <v>129</v>
       </c>
       <c r="F20" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G20" t="s">
         <v>25</v>
       </c>
       <c r="H20" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="I20" t="s">
         <v>80</v>
       </c>
       <c r="J20" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="K20">
         <v>0.25</v>
       </c>
       <c r="L20">
-        <v>11.75</v>
+        <v>8.75</v>
       </c>
       <c r="M20" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N20" t="s">
         <v>101</v>
@@ -3837,37 +4145,46 @@
         <v>80</v>
       </c>
       <c r="P20">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q20" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R20">
         <v>1</v>
       </c>
       <c r="S20">
-        <v>20</v>
-      </c>
-      <c r="T20" t="s">
-        <v>237</v>
-      </c>
-      <c r="U20">
+        <v>15</v>
+      </c>
+      <c r="T20">
+        <v>0.114</v>
+      </c>
+      <c r="U20" t="s">
+        <v>266</v>
+      </c>
+      <c r="V20">
+        <v>2.86</v>
+      </c>
+      <c r="W20" t="s">
+        <v>247</v>
+      </c>
+      <c r="X20">
         <v>0.35</v>
       </c>
-      <c r="V20">
-        <v>62</v>
-      </c>
-      <c r="W20" t="s">
-        <v>222</v>
-      </c>
-      <c r="X20" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y20">
+        <v>49</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -3884,28 +4201,28 @@
         <v>133</v>
       </c>
       <c r="F21" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G21" t="s">
         <v>25</v>
       </c>
       <c r="H21" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="I21" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="J21" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="K21">
         <v>0.56</v>
       </c>
       <c r="L21">
-        <v>26.32</v>
+        <v>19.6</v>
       </c>
       <c r="M21" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N21" t="s">
         <v>101</v>
@@ -3914,37 +4231,46 @@
         <v>80</v>
       </c>
       <c r="P21">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q21" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R21">
         <v>1</v>
       </c>
       <c r="S21">
-        <v>20</v>
-      </c>
-      <c r="T21" t="s">
-        <v>221</v>
-      </c>
-      <c r="U21">
+        <v>15</v>
+      </c>
+      <c r="T21">
+        <v>0.331</v>
+      </c>
+      <c r="U21" t="s">
+        <v>267</v>
+      </c>
+      <c r="V21">
+        <v>8.26</v>
+      </c>
+      <c r="W21" t="s">
+        <v>227</v>
+      </c>
+      <c r="X21">
         <v>0.7</v>
       </c>
-      <c r="V21">
-        <v>76</v>
-      </c>
-      <c r="W21" t="s">
-        <v>234</v>
-      </c>
-      <c r="X21" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y21">
+        <v>66</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>243</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -3961,7 +4287,7 @@
         <v>138</v>
       </c>
       <c r="F22" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G22" t="s">
         <v>25</v>
@@ -3982,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N22" t="s">
         <v>80</v>
@@ -3991,37 +4317,46 @@
         <v>101</v>
       </c>
       <c r="P22">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q22" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R22">
         <v>1</v>
       </c>
       <c r="S22">
-        <v>20</v>
-      </c>
-      <c r="T22" t="s">
-        <v>221</v>
-      </c>
-      <c r="U22">
+        <v>15</v>
+      </c>
+      <c r="T22">
+        <v>0.105</v>
+      </c>
+      <c r="U22" t="s">
+        <v>268</v>
+      </c>
+      <c r="V22">
+        <v>2.62</v>
+      </c>
+      <c r="W22" t="s">
+        <v>227</v>
+      </c>
+      <c r="X22">
         <v>0.7</v>
       </c>
-      <c r="V22">
-        <v>27</v>
-      </c>
-      <c r="W22" t="s">
-        <v>226</v>
-      </c>
-      <c r="X22" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y22">
+        <v>23</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -4038,7 +4373,7 @@
         <v>143</v>
       </c>
       <c r="F23" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G23" t="s">
         <v>25</v>
@@ -4059,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N23" t="s">
         <v>80</v>
@@ -4068,37 +4403,46 @@
         <v>101</v>
       </c>
       <c r="P23">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q23" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R23">
         <v>1</v>
       </c>
       <c r="S23">
-        <v>20</v>
-      </c>
-      <c r="T23" t="s">
-        <v>242</v>
-      </c>
-      <c r="U23">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="T23">
+        <v>0.152</v>
+      </c>
+      <c r="U23" t="s">
+        <v>269</v>
       </c>
       <c r="V23">
-        <v>27</v>
+        <v>3.81</v>
       </c>
       <c r="W23" t="s">
-        <v>226</v>
-      </c>
-      <c r="X23" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>24</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -4115,7 +4459,7 @@
         <v>149</v>
       </c>
       <c r="F24" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G24" t="s">
         <v>25</v>
@@ -4136,7 +4480,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N24" t="s">
         <v>80</v>
@@ -4145,37 +4489,46 @@
         <v>101</v>
       </c>
       <c r="P24">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q24" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R24">
         <v>1</v>
       </c>
       <c r="S24">
+        <v>15</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24" t="s">
+        <v>80</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24" t="s">
+        <v>227</v>
+      </c>
+      <c r="X24">
+        <v>0.7</v>
+      </c>
+      <c r="Y24">
         <v>20</v>
       </c>
-      <c r="T24" t="s">
-        <v>221</v>
-      </c>
-      <c r="U24">
-        <v>0.7</v>
-      </c>
-      <c r="V24">
-        <v>27</v>
-      </c>
-      <c r="W24" t="s">
-        <v>226</v>
-      </c>
-      <c r="X24" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z24" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -4192,7 +4545,7 @@
         <v>155</v>
       </c>
       <c r="F25" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G25" t="s">
         <v>25</v>
@@ -4213,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N25" t="s">
         <v>101</v>
@@ -4222,37 +4575,46 @@
         <v>80</v>
       </c>
       <c r="P25">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q25" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R25">
         <v>1</v>
       </c>
       <c r="S25">
-        <v>20</v>
-      </c>
-      <c r="T25" t="s">
-        <v>221</v>
-      </c>
-      <c r="U25">
+        <v>15</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25" t="s">
+        <v>80</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25" t="s">
+        <v>227</v>
+      </c>
+      <c r="X25">
         <v>0.7</v>
       </c>
-      <c r="V25">
-        <v>50</v>
-      </c>
-      <c r="W25" t="s">
-        <v>226</v>
-      </c>
-      <c r="X25" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y25">
+        <v>38</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -4269,7 +4631,7 @@
         <v>160</v>
       </c>
       <c r="F26" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G26" t="s">
         <v>25</v>
@@ -4290,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N26" t="s">
         <v>80</v>
@@ -4299,37 +4661,46 @@
         <v>101</v>
       </c>
       <c r="P26">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q26" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R26">
         <v>1</v>
       </c>
       <c r="S26">
-        <v>20</v>
-      </c>
-      <c r="T26" t="s">
-        <v>221</v>
-      </c>
-      <c r="U26">
+        <v>15</v>
+      </c>
+      <c r="T26">
+        <v>0.193</v>
+      </c>
+      <c r="U26" t="s">
+        <v>270</v>
+      </c>
+      <c r="V26">
+        <v>4.83</v>
+      </c>
+      <c r="W26" t="s">
+        <v>227</v>
+      </c>
+      <c r="X26">
         <v>0.7</v>
       </c>
-      <c r="V26">
-        <v>27</v>
-      </c>
-      <c r="W26" t="s">
-        <v>226</v>
-      </c>
-      <c r="X26" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y26">
+        <v>25</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -4346,7 +4717,7 @@
         <v>165</v>
       </c>
       <c r="F27" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G27" t="s">
         <v>25</v>
@@ -4367,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N27" t="s">
         <v>101</v>
@@ -4376,37 +4747,46 @@
         <v>80</v>
       </c>
       <c r="P27">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q27" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R27">
         <v>1</v>
       </c>
       <c r="S27">
-        <v>20</v>
-      </c>
-      <c r="T27" t="s">
-        <v>231</v>
-      </c>
-      <c r="U27">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27" t="s">
+        <v>80</v>
       </c>
       <c r="V27">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W27" t="s">
-        <v>226</v>
-      </c>
-      <c r="X27" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+      <c r="X27">
+        <v>1</v>
+      </c>
+      <c r="Y27">
+        <v>38</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -4423,7 +4803,7 @@
         <v>96</v>
       </c>
       <c r="F28" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G28" t="s">
         <v>25</v>
@@ -4444,46 +4824,55 @@
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N28" t="s">
         <v>80</v>
       </c>
       <c r="O28" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="P28">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q28" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R28">
         <v>1</v>
       </c>
       <c r="S28">
+        <v>15</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28" t="s">
+        <v>80</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28" t="s">
+        <v>227</v>
+      </c>
+      <c r="X28">
+        <v>0.7</v>
+      </c>
+      <c r="Y28">
         <v>20</v>
       </c>
-      <c r="T28" t="s">
-        <v>221</v>
-      </c>
-      <c r="U28">
-        <v>0.7</v>
-      </c>
-      <c r="V28">
-        <v>27</v>
-      </c>
-      <c r="W28" t="s">
-        <v>226</v>
-      </c>
-      <c r="X28" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z28" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -4500,7 +4889,7 @@
         <v>105</v>
       </c>
       <c r="F29" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G29" t="s">
         <v>25</v>
@@ -4521,46 +4910,55 @@
         <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N29" t="s">
         <v>80</v>
       </c>
       <c r="O29" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="P29">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q29" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R29">
         <v>1</v>
       </c>
       <c r="S29">
+        <v>15</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29" t="s">
+        <v>80</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29" t="s">
+        <v>227</v>
+      </c>
+      <c r="X29">
+        <v>0.7</v>
+      </c>
+      <c r="Y29">
         <v>20</v>
       </c>
-      <c r="T29" t="s">
-        <v>221</v>
-      </c>
-      <c r="U29">
-        <v>0.7</v>
-      </c>
-      <c r="V29">
-        <v>27</v>
-      </c>
-      <c r="W29" t="s">
-        <v>226</v>
-      </c>
-      <c r="X29" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z29" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>36</v>
       </c>
@@ -4577,67 +4975,76 @@
         <v>109</v>
       </c>
       <c r="F30" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G30" t="s">
         <v>25</v>
       </c>
       <c r="H30" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="I30" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="J30" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="K30">
         <v>0.45</v>
       </c>
       <c r="L30">
-        <v>21.15</v>
+        <v>15.75</v>
       </c>
       <c r="M30" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N30" t="s">
         <v>80</v>
       </c>
       <c r="O30" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="P30">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q30" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R30">
         <v>1</v>
       </c>
       <c r="S30">
-        <v>20</v>
-      </c>
-      <c r="T30" t="s">
-        <v>231</v>
-      </c>
-      <c r="U30">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="T30">
+        <v>0.314</v>
+      </c>
+      <c r="U30" t="s">
+        <v>274</v>
       </c>
       <c r="V30">
-        <v>48</v>
+        <v>7.84</v>
       </c>
       <c r="W30" t="s">
-        <v>226</v>
-      </c>
-      <c r="X30" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+      <c r="X30">
+        <v>1</v>
+      </c>
+      <c r="Y30">
+        <v>44</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -4654,7 +5061,7 @@
         <v>117</v>
       </c>
       <c r="F31" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G31" t="s">
         <v>25</v>
@@ -4675,46 +5082,55 @@
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N31" t="s">
         <v>80</v>
       </c>
       <c r="O31" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="P31">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q31" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R31">
         <v>1</v>
       </c>
       <c r="S31">
+        <v>15</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31" t="s">
+        <v>80</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31" t="s">
+        <v>227</v>
+      </c>
+      <c r="X31">
+        <v>0.7</v>
+      </c>
+      <c r="Y31">
         <v>20</v>
       </c>
-      <c r="T31" t="s">
-        <v>221</v>
-      </c>
-      <c r="U31">
-        <v>0.7</v>
-      </c>
-      <c r="V31">
-        <v>27</v>
-      </c>
-      <c r="W31" t="s">
-        <v>226</v>
-      </c>
-      <c r="X31" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z31" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -4731,7 +5147,7 @@
         <v>123</v>
       </c>
       <c r="F32" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G32" t="s">
         <v>25</v>
@@ -4740,58 +5156,67 @@
         <v>80</v>
       </c>
       <c r="I32" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="J32" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="K32">
         <v>0.1</v>
       </c>
       <c r="L32">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="M32" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N32" t="s">
         <v>80</v>
       </c>
       <c r="O32" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="P32">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q32" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R32">
         <v>1</v>
       </c>
       <c r="S32">
-        <v>20</v>
-      </c>
-      <c r="T32" t="s">
-        <v>237</v>
-      </c>
-      <c r="U32">
+        <v>15</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32" t="s">
+        <v>80</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32" t="s">
+        <v>247</v>
+      </c>
+      <c r="X32">
         <v>0.35</v>
       </c>
-      <c r="V32">
-        <v>32</v>
-      </c>
-      <c r="W32" t="s">
-        <v>226</v>
-      </c>
-      <c r="X32" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y32">
+        <v>24</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -4808,7 +5233,7 @@
         <v>129</v>
       </c>
       <c r="F33" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G33" t="s">
         <v>25</v>
@@ -4817,58 +5242,67 @@
         <v>80</v>
       </c>
       <c r="I33" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="J33" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="K33">
         <v>0.1</v>
       </c>
       <c r="L33">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="M33" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N33" t="s">
         <v>80</v>
       </c>
       <c r="O33" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="P33">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q33" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R33">
         <v>1</v>
       </c>
       <c r="S33">
-        <v>20</v>
-      </c>
-      <c r="T33" t="s">
-        <v>237</v>
-      </c>
-      <c r="U33">
+        <v>15</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33" t="s">
+        <v>80</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33" t="s">
+        <v>247</v>
+      </c>
+      <c r="X33">
         <v>0.35</v>
       </c>
-      <c r="V33">
-        <v>32</v>
-      </c>
-      <c r="W33" t="s">
-        <v>226</v>
-      </c>
-      <c r="X33" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y33">
+        <v>24</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -4885,7 +5319,7 @@
         <v>133</v>
       </c>
       <c r="F34" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G34" t="s">
         <v>25</v>
@@ -4906,46 +5340,55 @@
         <v>0</v>
       </c>
       <c r="M34" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N34" t="s">
         <v>80</v>
       </c>
       <c r="O34" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="P34">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q34" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R34">
         <v>1</v>
       </c>
       <c r="S34">
+        <v>15</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34" t="s">
+        <v>80</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34" t="s">
+        <v>227</v>
+      </c>
+      <c r="X34">
+        <v>0.7</v>
+      </c>
+      <c r="Y34">
         <v>20</v>
       </c>
-      <c r="T34" t="s">
-        <v>221</v>
-      </c>
-      <c r="U34">
-        <v>0.7</v>
-      </c>
-      <c r="V34">
-        <v>27</v>
-      </c>
-      <c r="W34" t="s">
-        <v>226</v>
-      </c>
-      <c r="X34" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y34" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z34" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -4962,7 +5405,7 @@
         <v>138</v>
       </c>
       <c r="F35" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G35" t="s">
         <v>25</v>
@@ -4980,49 +5423,58 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="M35" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N35" t="s">
         <v>80</v>
       </c>
       <c r="O35" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="P35">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q35" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R35">
         <v>1</v>
       </c>
       <c r="S35">
-        <v>20</v>
-      </c>
-      <c r="T35" t="s">
-        <v>221</v>
-      </c>
-      <c r="U35">
+        <v>15</v>
+      </c>
+      <c r="T35">
+        <v>1</v>
+      </c>
+      <c r="U35" t="s">
+        <v>276</v>
+      </c>
+      <c r="V35">
+        <v>25</v>
+      </c>
+      <c r="W35" t="s">
+        <v>227</v>
+      </c>
+      <c r="X35">
         <v>0.7</v>
       </c>
-      <c r="V35">
-        <v>74</v>
-      </c>
-      <c r="W35" t="s">
-        <v>222</v>
-      </c>
-      <c r="X35" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y35">
+        <v>80</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -5039,7 +5491,7 @@
         <v>143</v>
       </c>
       <c r="F36" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G36" t="s">
         <v>25</v>
@@ -5060,46 +5512,55 @@
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N36" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="O36" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="P36">
-        <v>18.48</v>
+        <v>14</v>
       </c>
       <c r="Q36" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R36">
         <v>1</v>
       </c>
       <c r="S36">
-        <v>20</v>
-      </c>
-      <c r="T36" t="s">
-        <v>221</v>
-      </c>
-      <c r="U36">
+        <v>15</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36" t="s">
+        <v>80</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36" t="s">
+        <v>227</v>
+      </c>
+      <c r="X36">
         <v>0.7</v>
       </c>
-      <c r="V36">
-        <v>38</v>
-      </c>
-      <c r="W36" t="s">
-        <v>226</v>
-      </c>
-      <c r="X36" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y36">
+        <v>29</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -5116,7 +5577,7 @@
         <v>149</v>
       </c>
       <c r="F37" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G37" t="s">
         <v>25</v>
@@ -5137,46 +5598,55 @@
         <v>0</v>
       </c>
       <c r="M37" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N37" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="O37" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="P37">
-        <v>18.48</v>
+        <v>14</v>
       </c>
       <c r="Q37" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R37">
         <v>1</v>
       </c>
       <c r="S37">
-        <v>20</v>
-      </c>
-      <c r="T37" t="s">
-        <v>221</v>
-      </c>
-      <c r="U37">
+        <v>15</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37" t="s">
+        <v>80</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37" t="s">
+        <v>227</v>
+      </c>
+      <c r="X37">
         <v>0.7</v>
       </c>
-      <c r="V37">
-        <v>38</v>
-      </c>
-      <c r="W37" t="s">
-        <v>226</v>
-      </c>
-      <c r="X37" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y37" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y37">
+        <v>29</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -5193,7 +5663,7 @@
         <v>155</v>
       </c>
       <c r="F38" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G38" t="s">
         <v>25</v>
@@ -5214,46 +5684,55 @@
         <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N38" t="s">
         <v>80</v>
       </c>
       <c r="O38" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="P38">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q38" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R38">
         <v>1</v>
       </c>
       <c r="S38">
+        <v>15</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38" t="s">
+        <v>80</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38" t="s">
+        <v>227</v>
+      </c>
+      <c r="X38">
+        <v>0.7</v>
+      </c>
+      <c r="Y38">
         <v>20</v>
       </c>
-      <c r="T38" t="s">
-        <v>221</v>
-      </c>
-      <c r="U38">
-        <v>0.7</v>
-      </c>
-      <c r="V38">
-        <v>27</v>
-      </c>
-      <c r="W38" t="s">
-        <v>226</v>
-      </c>
-      <c r="X38" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z38" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>36</v>
       </c>
@@ -5270,7 +5749,7 @@
         <v>160</v>
       </c>
       <c r="F39" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G39" t="s">
         <v>25</v>
@@ -5291,46 +5770,55 @@
         <v>0</v>
       </c>
       <c r="M39" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N39" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="O39" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="P39">
-        <v>18.48</v>
+        <v>14</v>
       </c>
       <c r="Q39" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R39">
         <v>1</v>
       </c>
       <c r="S39">
-        <v>20</v>
-      </c>
-      <c r="T39" t="s">
-        <v>221</v>
-      </c>
-      <c r="U39">
+        <v>15</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39" t="s">
+        <v>80</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39" t="s">
+        <v>227</v>
+      </c>
+      <c r="X39">
         <v>0.7</v>
       </c>
-      <c r="V39">
-        <v>38</v>
-      </c>
-      <c r="W39" t="s">
-        <v>226</v>
-      </c>
-      <c r="X39" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y39" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y39">
+        <v>29</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>36</v>
       </c>
@@ -5347,16 +5835,16 @@
         <v>165</v>
       </c>
       <c r="F40" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G40" t="s">
         <v>25</v>
       </c>
       <c r="H40" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="I40" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="J40" t="s">
         <v>80</v>
@@ -5365,49 +5853,58 @@
         <v>0.6</v>
       </c>
       <c r="L40">
-        <v>28.2</v>
+        <v>21</v>
       </c>
       <c r="M40" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N40" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="O40" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="P40">
-        <v>18.48</v>
+        <v>14</v>
       </c>
       <c r="Q40" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R40">
         <v>1</v>
       </c>
       <c r="S40">
-        <v>20</v>
-      </c>
-      <c r="T40" t="s">
-        <v>231</v>
-      </c>
-      <c r="U40">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="T40">
+        <v>0.479</v>
+      </c>
+      <c r="U40" t="s">
+        <v>281</v>
       </c>
       <c r="V40">
-        <v>67</v>
+        <v>11.98</v>
       </c>
       <c r="W40" t="s">
-        <v>222</v>
-      </c>
-      <c r="X40" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y40" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+      <c r="X40">
+        <v>1</v>
+      </c>
+      <c r="Y40">
+        <v>62</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>243</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -5424,7 +5921,7 @@
         <v>96</v>
       </c>
       <c r="F41" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G41" t="s">
         <v>25</v>
@@ -5445,7 +5942,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N41" t="s">
         <v>80</v>
@@ -5454,37 +5951,46 @@
         <v>147</v>
       </c>
       <c r="P41">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q41" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="R41">
         <v>0.3</v>
       </c>
       <c r="S41">
-        <v>6</v>
-      </c>
-      <c r="T41" t="s">
-        <v>221</v>
-      </c>
-      <c r="U41">
+        <v>4.5</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41" t="s">
+        <v>80</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41" t="s">
+        <v>227</v>
+      </c>
+      <c r="X41">
         <v>0.7</v>
       </c>
-      <c r="V41">
-        <v>13</v>
-      </c>
-      <c r="W41" t="s">
-        <v>226</v>
-      </c>
-      <c r="X41" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y41" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y41">
+        <v>10</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -5501,7 +6007,7 @@
         <v>105</v>
       </c>
       <c r="F42" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G42" t="s">
         <v>25</v>
@@ -5522,7 +6028,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N42" t="s">
         <v>80</v>
@@ -5531,37 +6037,46 @@
         <v>147</v>
       </c>
       <c r="P42">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q42" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="R42">
         <v>0.1</v>
       </c>
       <c r="S42">
-        <v>2</v>
-      </c>
-      <c r="T42" t="s">
-        <v>221</v>
-      </c>
-      <c r="U42">
+        <v>1.5</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42" t="s">
+        <v>80</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42" t="s">
+        <v>227</v>
+      </c>
+      <c r="X42">
         <v>0.7</v>
       </c>
-      <c r="V42">
-        <v>9</v>
-      </c>
-      <c r="W42" t="s">
-        <v>226</v>
-      </c>
-      <c r="X42" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y42" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y42">
+        <v>7</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -5578,7 +6093,7 @@
         <v>109</v>
       </c>
       <c r="F43" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G43" t="s">
         <v>25</v>
@@ -5599,46 +6114,55 @@
         <v>0</v>
       </c>
       <c r="M43" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N43" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O43" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="P43">
-        <v>18.48</v>
+        <v>14</v>
       </c>
       <c r="Q43" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="R43">
         <v>0.1</v>
       </c>
       <c r="S43">
-        <v>2</v>
-      </c>
-      <c r="T43" t="s">
-        <v>231</v>
-      </c>
-      <c r="U43">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43" t="s">
+        <v>80</v>
       </c>
       <c r="V43">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W43" t="s">
-        <v>226</v>
-      </c>
-      <c r="X43" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y43" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+      <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
+        <v>15</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -5655,7 +6179,7 @@
         <v>117</v>
       </c>
       <c r="F44" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G44" t="s">
         <v>25</v>
@@ -5676,7 +6200,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N44" t="s">
         <v>80</v>
@@ -5685,37 +6209,46 @@
         <v>147</v>
       </c>
       <c r="P44">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q44" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="R44">
         <v>0.1</v>
       </c>
       <c r="S44">
-        <v>2</v>
-      </c>
-      <c r="T44" t="s">
-        <v>221</v>
-      </c>
-      <c r="U44">
+        <v>1.5</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44" t="s">
+        <v>80</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44" t="s">
+        <v>227</v>
+      </c>
+      <c r="X44">
         <v>0.7</v>
       </c>
-      <c r="V44">
-        <v>9</v>
-      </c>
-      <c r="W44" t="s">
-        <v>226</v>
-      </c>
-      <c r="X44" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y44" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y44">
+        <v>7</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -5732,7 +6265,7 @@
         <v>123</v>
       </c>
       <c r="F45" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G45" t="s">
         <v>25</v>
@@ -5753,7 +6286,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N45" t="s">
         <v>80</v>
@@ -5762,37 +6295,46 @@
         <v>147</v>
       </c>
       <c r="P45">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q45" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="R45">
         <v>0.3</v>
       </c>
       <c r="S45">
-        <v>6</v>
-      </c>
-      <c r="T45" t="s">
-        <v>237</v>
-      </c>
-      <c r="U45">
+        <v>4.5</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45" t="s">
+        <v>80</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45" t="s">
+        <v>247</v>
+      </c>
+      <c r="X45">
         <v>0.35</v>
       </c>
-      <c r="V45">
-        <v>13</v>
-      </c>
-      <c r="W45" t="s">
-        <v>226</v>
-      </c>
-      <c r="X45" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y45" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y45">
+        <v>10</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -5809,7 +6351,7 @@
         <v>129</v>
       </c>
       <c r="F46" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G46" t="s">
         <v>25</v>
@@ -5830,7 +6372,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N46" t="s">
         <v>80</v>
@@ -5839,37 +6381,46 @@
         <v>147</v>
       </c>
       <c r="P46">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q46" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R46">
         <v>1</v>
       </c>
       <c r="S46">
+        <v>15</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46" t="s">
+        <v>80</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46" t="s">
+        <v>247</v>
+      </c>
+      <c r="X46">
+        <v>0.35</v>
+      </c>
+      <c r="Y46">
         <v>20</v>
       </c>
-      <c r="T46" t="s">
-        <v>237</v>
-      </c>
-      <c r="U46">
-        <v>0.35</v>
-      </c>
-      <c r="V46">
-        <v>27</v>
-      </c>
-      <c r="W46" t="s">
-        <v>226</v>
-      </c>
-      <c r="X46" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y46" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z46" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -5886,7 +6437,7 @@
         <v>133</v>
       </c>
       <c r="F47" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G47" t="s">
         <v>25</v>
@@ -5907,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N47" t="s">
         <v>80</v>
@@ -5916,37 +6467,46 @@
         <v>147</v>
       </c>
       <c r="P47">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q47" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="R47">
         <v>0.1</v>
       </c>
       <c r="S47">
-        <v>2</v>
-      </c>
-      <c r="T47" t="s">
-        <v>221</v>
-      </c>
-      <c r="U47">
+        <v>1.5</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47" t="s">
+        <v>80</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47" t="s">
+        <v>227</v>
+      </c>
+      <c r="X47">
         <v>0.7</v>
       </c>
-      <c r="V47">
-        <v>9</v>
-      </c>
-      <c r="W47" t="s">
-        <v>226</v>
-      </c>
-      <c r="X47" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y47" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y47">
+        <v>7</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -5963,7 +6523,7 @@
         <v>138</v>
       </c>
       <c r="F48" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G48" t="s">
         <v>25</v>
@@ -5984,46 +6544,55 @@
         <v>0</v>
       </c>
       <c r="M48" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N48" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O48" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="P48">
-        <v>18.48</v>
+        <v>14</v>
       </c>
       <c r="Q48" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="R48">
         <v>0.3</v>
       </c>
       <c r="S48">
-        <v>6</v>
-      </c>
-      <c r="T48" t="s">
-        <v>221</v>
-      </c>
-      <c r="U48">
+        <v>4.5</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48" t="s">
+        <v>80</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48" t="s">
+        <v>227</v>
+      </c>
+      <c r="X48">
         <v>0.7</v>
       </c>
-      <c r="V48">
-        <v>24</v>
-      </c>
-      <c r="W48" t="s">
-        <v>226</v>
-      </c>
-      <c r="X48" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y48" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y48">
+        <v>19</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -6040,7 +6609,7 @@
         <v>143</v>
       </c>
       <c r="F49" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G49" t="s">
         <v>25</v>
@@ -6058,10 +6627,10 @@
         <v>1</v>
       </c>
       <c r="L49">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="M49" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N49" t="s">
         <v>147</v>
@@ -6070,37 +6639,46 @@
         <v>80</v>
       </c>
       <c r="P49">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q49" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R49">
         <v>1</v>
       </c>
       <c r="S49">
-        <v>20</v>
-      </c>
-      <c r="T49" t="s">
-        <v>221</v>
-      </c>
-      <c r="U49">
+        <v>15</v>
+      </c>
+      <c r="T49">
+        <v>0.992</v>
+      </c>
+      <c r="U49" t="s">
+        <v>284</v>
+      </c>
+      <c r="V49">
+        <v>24.8</v>
+      </c>
+      <c r="W49" t="s">
+        <v>227</v>
+      </c>
+      <c r="X49">
         <v>0.7</v>
       </c>
-      <c r="V49">
-        <v>97</v>
-      </c>
-      <c r="W49" t="s">
-        <v>234</v>
-      </c>
-      <c r="X49" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y49" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y49">
+        <v>98</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>46</v>
       </c>
@@ -6117,7 +6695,7 @@
         <v>149</v>
       </c>
       <c r="F50" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G50" t="s">
         <v>25</v>
@@ -6138,7 +6716,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N50" t="s">
         <v>147</v>
@@ -6147,37 +6725,46 @@
         <v>80</v>
       </c>
       <c r="P50">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q50" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R50">
         <v>1</v>
       </c>
       <c r="S50">
-        <v>20</v>
-      </c>
-      <c r="T50" t="s">
-        <v>221</v>
-      </c>
-      <c r="U50">
+        <v>15</v>
+      </c>
+      <c r="T50">
+        <v>0.206</v>
+      </c>
+      <c r="U50" t="s">
+        <v>285</v>
+      </c>
+      <c r="V50">
+        <v>5.15</v>
+      </c>
+      <c r="W50" t="s">
+        <v>227</v>
+      </c>
+      <c r="X50">
         <v>0.7</v>
       </c>
-      <c r="V50">
-        <v>50</v>
-      </c>
-      <c r="W50" t="s">
-        <v>226</v>
-      </c>
-      <c r="X50" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y50" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y50">
+        <v>43</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>46</v>
       </c>
@@ -6194,7 +6781,7 @@
         <v>155</v>
       </c>
       <c r="F51" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G51" t="s">
         <v>25</v>
@@ -6215,46 +6802,55 @@
         <v>0</v>
       </c>
       <c r="M51" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N51" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O51" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="P51">
-        <v>18.48</v>
+        <v>14</v>
       </c>
       <c r="Q51" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R51">
         <v>1</v>
       </c>
       <c r="S51">
-        <v>20</v>
-      </c>
-      <c r="T51" t="s">
-        <v>221</v>
-      </c>
-      <c r="U51">
+        <v>15</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51" t="s">
+        <v>80</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51" t="s">
+        <v>227</v>
+      </c>
+      <c r="X51">
         <v>0.7</v>
       </c>
-      <c r="V51">
-        <v>38</v>
-      </c>
-      <c r="W51" t="s">
-        <v>226</v>
-      </c>
-      <c r="X51" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y51" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y51">
+        <v>29</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>46</v>
       </c>
@@ -6271,7 +6867,7 @@
         <v>160</v>
       </c>
       <c r="F52" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G52" t="s">
         <v>25</v>
@@ -6289,10 +6885,10 @@
         <v>1</v>
       </c>
       <c r="L52">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="M52" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N52" t="s">
         <v>147</v>
@@ -6301,37 +6897,46 @@
         <v>80</v>
       </c>
       <c r="P52">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q52" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>20</v>
-      </c>
-      <c r="T52" t="s">
-        <v>242</v>
-      </c>
-      <c r="U52">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="T52">
+        <v>1</v>
+      </c>
+      <c r="U52" t="s">
+        <v>286</v>
       </c>
       <c r="V52">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="W52" t="s">
-        <v>234</v>
-      </c>
-      <c r="X52" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y52" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+      <c r="X52">
+        <v>1</v>
+      </c>
+      <c r="Y52">
+        <v>98</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>46</v>
       </c>
@@ -6348,7 +6953,7 @@
         <v>165</v>
       </c>
       <c r="F53" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G53" t="s">
         <v>25</v>
@@ -6369,7 +6974,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N53" t="s">
         <v>147</v>
@@ -6378,37 +6983,46 @@
         <v>80</v>
       </c>
       <c r="P53">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q53" t="s">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="R53">
         <v>0.6</v>
       </c>
       <c r="S53">
-        <v>12</v>
-      </c>
-      <c r="T53" t="s">
-        <v>231</v>
-      </c>
-      <c r="U53">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53" t="s">
+        <v>80</v>
       </c>
       <c r="V53">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W53" t="s">
-        <v>226</v>
-      </c>
-      <c r="X53" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y53" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+      <c r="X53">
+        <v>1</v>
+      </c>
+      <c r="Y53">
+        <v>32</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>54</v>
       </c>
@@ -6425,7 +7039,7 @@
         <v>96</v>
       </c>
       <c r="F54" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G54" t="s">
         <v>25</v>
@@ -6446,46 +7060,55 @@
         <v>0</v>
       </c>
       <c r="M54" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N54" t="s">
         <v>80</v>
       </c>
       <c r="O54" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="P54">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q54" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R54">
         <v>1</v>
       </c>
       <c r="S54">
+        <v>15</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54" t="s">
+        <v>80</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54" t="s">
+        <v>227</v>
+      </c>
+      <c r="X54">
+        <v>0.7</v>
+      </c>
+      <c r="Y54">
         <v>20</v>
       </c>
-      <c r="T54" t="s">
-        <v>221</v>
-      </c>
-      <c r="U54">
-        <v>0.7</v>
-      </c>
-      <c r="V54">
-        <v>27</v>
-      </c>
-      <c r="W54" t="s">
-        <v>226</v>
-      </c>
-      <c r="X54" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y54" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z54" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -6502,7 +7125,7 @@
         <v>105</v>
       </c>
       <c r="F55" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G55" t="s">
         <v>25</v>
@@ -6523,46 +7146,55 @@
         <v>0</v>
       </c>
       <c r="M55" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N55" t="s">
         <v>80</v>
       </c>
       <c r="O55" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="P55">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q55" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="R55">
         <v>0.3</v>
       </c>
       <c r="S55">
-        <v>6</v>
-      </c>
-      <c r="T55" t="s">
-        <v>221</v>
-      </c>
-      <c r="U55">
+        <v>4.5</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55" t="s">
+        <v>80</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55" t="s">
+        <v>227</v>
+      </c>
+      <c r="X55">
         <v>0.7</v>
       </c>
-      <c r="V55">
-        <v>13</v>
-      </c>
-      <c r="W55" t="s">
-        <v>226</v>
-      </c>
-      <c r="X55" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y55" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y55">
+        <v>10</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -6579,7 +7211,7 @@
         <v>109</v>
       </c>
       <c r="F56" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G56" t="s">
         <v>25</v>
@@ -6600,46 +7232,55 @@
         <v>0</v>
       </c>
       <c r="M56" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N56" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O56" t="s">
         <v>80</v>
       </c>
       <c r="P56">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q56" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="R56">
         <v>0.3</v>
       </c>
       <c r="S56">
-        <v>6</v>
-      </c>
-      <c r="T56" t="s">
-        <v>231</v>
-      </c>
-      <c r="U56">
-        <v>1</v>
+        <v>4.5</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56" t="s">
+        <v>80</v>
       </c>
       <c r="V56">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="W56" t="s">
-        <v>226</v>
-      </c>
-      <c r="X56" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y56" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+      <c r="X56">
+        <v>1</v>
+      </c>
+      <c r="Y56">
+        <v>27</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>54</v>
       </c>
@@ -6656,7 +7297,7 @@
         <v>117</v>
       </c>
       <c r="F57" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G57" t="s">
         <v>25</v>
@@ -6677,46 +7318,55 @@
         <v>0</v>
       </c>
       <c r="M57" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N57" t="s">
         <v>80</v>
       </c>
       <c r="O57" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="P57">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q57" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="R57">
         <v>0.3</v>
       </c>
       <c r="S57">
-        <v>6</v>
-      </c>
-      <c r="T57" t="s">
-        <v>221</v>
-      </c>
-      <c r="U57">
+        <v>4.5</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57" t="s">
+        <v>80</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57" t="s">
+        <v>227</v>
+      </c>
+      <c r="X57">
         <v>0.7</v>
       </c>
-      <c r="V57">
-        <v>13</v>
-      </c>
-      <c r="W57" t="s">
-        <v>226</v>
-      </c>
-      <c r="X57" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y57" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y57">
+        <v>10</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB57" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>54</v>
       </c>
@@ -6733,7 +7383,7 @@
         <v>123</v>
       </c>
       <c r="F58" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G58" t="s">
         <v>25</v>
@@ -6754,46 +7404,55 @@
         <v>0</v>
       </c>
       <c r="M58" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N58" t="s">
         <v>80</v>
       </c>
       <c r="O58" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="P58">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q58" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R58">
         <v>1</v>
       </c>
       <c r="S58">
-        <v>20</v>
-      </c>
-      <c r="T58" t="s">
-        <v>237</v>
-      </c>
-      <c r="U58">
+        <v>15</v>
+      </c>
+      <c r="T58">
+        <v>0.054</v>
+      </c>
+      <c r="U58" t="s">
+        <v>288</v>
+      </c>
+      <c r="V58">
+        <v>1.36</v>
+      </c>
+      <c r="W58" t="s">
+        <v>247</v>
+      </c>
+      <c r="X58">
         <v>0.35</v>
       </c>
-      <c r="V58">
-        <v>27</v>
-      </c>
-      <c r="W58" t="s">
-        <v>226</v>
-      </c>
-      <c r="X58" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y58" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y58">
+        <v>22</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB58" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>54</v>
       </c>
@@ -6810,7 +7469,7 @@
         <v>129</v>
       </c>
       <c r="F59" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G59" t="s">
         <v>25</v>
@@ -6831,46 +7490,55 @@
         <v>0</v>
       </c>
       <c r="M59" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N59" t="s">
         <v>80</v>
       </c>
       <c r="O59" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="P59">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q59" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R59">
         <v>1</v>
       </c>
       <c r="S59">
+        <v>15</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59" t="s">
+        <v>80</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59" t="s">
+        <v>247</v>
+      </c>
+      <c r="X59">
+        <v>0.35</v>
+      </c>
+      <c r="Y59">
         <v>20</v>
       </c>
-      <c r="T59" t="s">
-        <v>237</v>
-      </c>
-      <c r="U59">
-        <v>0.35</v>
-      </c>
-      <c r="V59">
-        <v>27</v>
-      </c>
-      <c r="W59" t="s">
-        <v>226</v>
-      </c>
-      <c r="X59" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y59" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z59" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB59" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>54</v>
       </c>
@@ -6887,7 +7555,7 @@
         <v>133</v>
       </c>
       <c r="F60" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G60" t="s">
         <v>25</v>
@@ -6908,46 +7576,55 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N60" t="s">
         <v>80</v>
       </c>
       <c r="O60" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="P60">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q60" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="R60">
         <v>0.3</v>
       </c>
       <c r="S60">
-        <v>6</v>
-      </c>
-      <c r="T60" t="s">
-        <v>221</v>
-      </c>
-      <c r="U60">
+        <v>4.5</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60" t="s">
+        <v>80</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60" t="s">
+        <v>227</v>
+      </c>
+      <c r="X60">
         <v>0.7</v>
       </c>
-      <c r="V60">
-        <v>13</v>
-      </c>
-      <c r="W60" t="s">
-        <v>226</v>
-      </c>
-      <c r="X60" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y60" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y60">
+        <v>10</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB60" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>54</v>
       </c>
@@ -6964,7 +7641,7 @@
         <v>138</v>
       </c>
       <c r="F61" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G61" t="s">
         <v>25</v>
@@ -6985,46 +7662,55 @@
         <v>0</v>
       </c>
       <c r="M61" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N61" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O61" t="s">
         <v>80</v>
       </c>
       <c r="P61">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q61" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R61">
         <v>1</v>
       </c>
       <c r="S61">
-        <v>20</v>
-      </c>
-      <c r="T61" t="s">
-        <v>221</v>
-      </c>
-      <c r="U61">
+        <v>15</v>
+      </c>
+      <c r="T61">
+        <v>0</v>
+      </c>
+      <c r="U61" t="s">
+        <v>80</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61" t="s">
+        <v>227</v>
+      </c>
+      <c r="X61">
         <v>0.7</v>
       </c>
-      <c r="V61">
-        <v>50</v>
-      </c>
-      <c r="W61" t="s">
-        <v>226</v>
-      </c>
-      <c r="X61" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y61" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y61">
+        <v>38</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB61" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>54</v>
       </c>
@@ -7041,7 +7727,7 @@
         <v>143</v>
       </c>
       <c r="F62" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G62" t="s">
         <v>25</v>
@@ -7062,46 +7748,55 @@
         <v>0</v>
       </c>
       <c r="M62" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N62" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O62" t="s">
         <v>80</v>
       </c>
       <c r="P62">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q62" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R62">
         <v>1</v>
       </c>
       <c r="S62">
-        <v>20</v>
-      </c>
-      <c r="T62" t="s">
-        <v>221</v>
-      </c>
-      <c r="U62">
+        <v>15</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62" t="s">
+        <v>80</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62" t="s">
+        <v>227</v>
+      </c>
+      <c r="X62">
         <v>0.7</v>
       </c>
-      <c r="V62">
-        <v>50</v>
-      </c>
-      <c r="W62" t="s">
-        <v>226</v>
-      </c>
-      <c r="X62" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y62" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y62">
+        <v>38</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB62" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>54</v>
       </c>
@@ -7118,7 +7813,7 @@
         <v>149</v>
       </c>
       <c r="F63" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G63" t="s">
         <v>25</v>
@@ -7136,49 +7831,58 @@
         <v>1</v>
       </c>
       <c r="L63">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="M63" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N63" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O63" t="s">
         <v>80</v>
       </c>
       <c r="P63">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q63" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R63">
         <v>1</v>
       </c>
       <c r="S63">
-        <v>20</v>
-      </c>
-      <c r="T63" t="s">
-        <v>242</v>
-      </c>
-      <c r="U63">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="T63">
+        <v>1</v>
+      </c>
+      <c r="U63" t="s">
+        <v>289</v>
       </c>
       <c r="V63">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="W63" t="s">
-        <v>234</v>
-      </c>
-      <c r="X63" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y63" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+      <c r="X63">
+        <v>1</v>
+      </c>
+      <c r="Y63">
+        <v>98</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB63" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>54</v>
       </c>
@@ -7195,7 +7899,7 @@
         <v>155</v>
       </c>
       <c r="F64" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G64" t="s">
         <v>25</v>
@@ -7213,49 +7917,58 @@
         <v>1</v>
       </c>
       <c r="L64">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="M64" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N64" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O64" t="s">
         <v>80</v>
       </c>
       <c r="P64">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q64" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R64">
         <v>1</v>
       </c>
       <c r="S64">
-        <v>20</v>
-      </c>
-      <c r="T64" t="s">
-        <v>221</v>
-      </c>
-      <c r="U64">
+        <v>15</v>
+      </c>
+      <c r="T64">
+        <v>0.906</v>
+      </c>
+      <c r="U64" t="s">
+        <v>290</v>
+      </c>
+      <c r="V64">
+        <v>22.64</v>
+      </c>
+      <c r="W64" t="s">
+        <v>227</v>
+      </c>
+      <c r="X64">
         <v>0.7</v>
       </c>
-      <c r="V64">
-        <v>97</v>
-      </c>
-      <c r="W64" t="s">
-        <v>234</v>
-      </c>
-      <c r="X64" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y64" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y64">
+        <v>95</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA64" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB64" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>54</v>
       </c>
@@ -7272,7 +7985,7 @@
         <v>160</v>
       </c>
       <c r="F65" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G65" t="s">
         <v>25</v>
@@ -7293,46 +8006,55 @@
         <v>0</v>
       </c>
       <c r="M65" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N65" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O65" t="s">
         <v>80</v>
       </c>
       <c r="P65">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q65" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R65">
         <v>1</v>
       </c>
       <c r="S65">
-        <v>20</v>
-      </c>
-      <c r="T65" t="s">
-        <v>221</v>
-      </c>
-      <c r="U65">
+        <v>15</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65" t="s">
+        <v>80</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65" t="s">
+        <v>227</v>
+      </c>
+      <c r="X65">
         <v>0.7</v>
       </c>
-      <c r="V65">
-        <v>50</v>
-      </c>
-      <c r="W65" t="s">
-        <v>226</v>
-      </c>
-      <c r="X65" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y65" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y65">
+        <v>38</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB65" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>54</v>
       </c>
@@ -7349,7 +8071,7 @@
         <v>165</v>
       </c>
       <c r="F66" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G66" t="s">
         <v>25</v>
@@ -7370,46 +8092,55 @@
         <v>0</v>
       </c>
       <c r="M66" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N66" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O66" t="s">
         <v>80</v>
       </c>
       <c r="P66">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q66" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R66">
         <v>1</v>
       </c>
       <c r="S66">
-        <v>20</v>
-      </c>
-      <c r="T66" t="s">
-        <v>231</v>
-      </c>
-      <c r="U66">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66" t="s">
+        <v>80</v>
       </c>
       <c r="V66">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W66" t="s">
-        <v>226</v>
-      </c>
-      <c r="X66" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y66" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+      <c r="X66">
+        <v>1</v>
+      </c>
+      <c r="Y66">
+        <v>38</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB66" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>64</v>
       </c>
@@ -7426,7 +8157,7 @@
         <v>96</v>
       </c>
       <c r="F67" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G67" t="s">
         <v>25</v>
@@ -7447,46 +8178,55 @@
         <v>0</v>
       </c>
       <c r="M67" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N67" t="s">
         <v>80</v>
       </c>
       <c r="O67" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="P67">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q67" t="s">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="R67">
         <v>0.6</v>
       </c>
       <c r="S67">
-        <v>12</v>
-      </c>
-      <c r="T67" t="s">
-        <v>221</v>
-      </c>
-      <c r="U67">
+        <v>9</v>
+      </c>
+      <c r="T67">
+        <v>0.044</v>
+      </c>
+      <c r="U67" t="s">
+        <v>291</v>
+      </c>
+      <c r="V67">
+        <v>1.09</v>
+      </c>
+      <c r="W67" t="s">
+        <v>227</v>
+      </c>
+      <c r="X67">
         <v>0.7</v>
       </c>
-      <c r="V67">
-        <v>19</v>
-      </c>
-      <c r="W67" t="s">
-        <v>226</v>
-      </c>
-      <c r="X67" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y67">
+        <v>15</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB67" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>64</v>
       </c>
@@ -7503,7 +8243,7 @@
         <v>105</v>
       </c>
       <c r="F68" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G68" t="s">
         <v>25</v>
@@ -7524,46 +8264,55 @@
         <v>0</v>
       </c>
       <c r="M68" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N68" t="s">
         <v>80</v>
       </c>
       <c r="O68" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="P68">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q68" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="R68">
         <v>0.1</v>
       </c>
       <c r="S68">
-        <v>2</v>
-      </c>
-      <c r="T68" t="s">
-        <v>221</v>
-      </c>
-      <c r="U68">
+        <v>1.5</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68" t="s">
+        <v>80</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68" t="s">
+        <v>227</v>
+      </c>
+      <c r="X68">
         <v>0.7</v>
       </c>
-      <c r="V68">
-        <v>9</v>
-      </c>
-      <c r="W68" t="s">
-        <v>226</v>
-      </c>
-      <c r="X68" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y68" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y68">
+        <v>7</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA68" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB68" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>64</v>
       </c>
@@ -7580,7 +8329,7 @@
         <v>109</v>
       </c>
       <c r="F69" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G69" t="s">
         <v>25</v>
@@ -7589,58 +8338,67 @@
         <v>80</v>
       </c>
       <c r="I69" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="J69" t="s">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="K69">
         <v>0.1</v>
       </c>
       <c r="L69">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="M69" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N69" t="s">
         <v>80</v>
       </c>
       <c r="O69" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="P69">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q69" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="R69">
         <v>0.1</v>
       </c>
       <c r="S69">
-        <v>2</v>
-      </c>
-      <c r="T69" t="s">
-        <v>231</v>
-      </c>
-      <c r="U69">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+      <c r="T69">
+        <v>0.133</v>
+      </c>
+      <c r="U69" t="s">
+        <v>293</v>
       </c>
       <c r="V69">
+        <v>3.32</v>
+      </c>
+      <c r="W69" t="s">
+        <v>239</v>
+      </c>
+      <c r="X69">
+        <v>1</v>
+      </c>
+      <c r="Y69">
         <v>14</v>
       </c>
-      <c r="W69" t="s">
-        <v>226</v>
-      </c>
-      <c r="X69" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y69" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z69" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB69" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>64</v>
       </c>
@@ -7657,7 +8415,7 @@
         <v>117</v>
       </c>
       <c r="F70" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G70" t="s">
         <v>25</v>
@@ -7678,46 +8436,55 @@
         <v>0</v>
       </c>
       <c r="M70" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N70" t="s">
         <v>80</v>
       </c>
       <c r="O70" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="P70">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q70" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="R70">
         <v>0.1</v>
       </c>
       <c r="S70">
-        <v>2</v>
-      </c>
-      <c r="T70" t="s">
-        <v>221</v>
-      </c>
-      <c r="U70">
+        <v>1.5</v>
+      </c>
+      <c r="T70">
+        <v>0.043</v>
+      </c>
+      <c r="U70" t="s">
+        <v>291</v>
+      </c>
+      <c r="V70">
+        <v>1.06</v>
+      </c>
+      <c r="W70" t="s">
+        <v>227</v>
+      </c>
+      <c r="X70">
         <v>0.7</v>
       </c>
-      <c r="V70">
-        <v>9</v>
-      </c>
-      <c r="W70" t="s">
-        <v>226</v>
-      </c>
-      <c r="X70" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y70" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y70">
+        <v>8</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB70" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>64</v>
       </c>
@@ -7734,7 +8501,7 @@
         <v>123</v>
       </c>
       <c r="F71" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G71" t="s">
         <v>25</v>
@@ -7755,46 +8522,55 @@
         <v>0</v>
       </c>
       <c r="M71" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N71" t="s">
         <v>80</v>
       </c>
       <c r="O71" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="P71">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q71" t="s">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="R71">
         <v>0.6</v>
       </c>
       <c r="S71">
-        <v>12</v>
-      </c>
-      <c r="T71" t="s">
-        <v>237</v>
-      </c>
-      <c r="U71">
+        <v>9</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71" t="s">
+        <v>80</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71" t="s">
+        <v>247</v>
+      </c>
+      <c r="X71">
         <v>0.35</v>
       </c>
-      <c r="V71">
-        <v>19</v>
-      </c>
-      <c r="W71" t="s">
-        <v>226</v>
-      </c>
-      <c r="X71" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y71" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y71">
+        <v>14</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB71" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>64</v>
       </c>
@@ -7811,7 +8587,7 @@
         <v>129</v>
       </c>
       <c r="F72" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G72" t="s">
         <v>25</v>
@@ -7832,46 +8608,55 @@
         <v>0</v>
       </c>
       <c r="M72" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N72" t="s">
         <v>80</v>
       </c>
       <c r="O72" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="P72">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q72" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R72">
         <v>1</v>
       </c>
       <c r="S72">
+        <v>15</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72" t="s">
+        <v>80</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72" t="s">
+        <v>247</v>
+      </c>
+      <c r="X72">
+        <v>0.35</v>
+      </c>
+      <c r="Y72">
         <v>20</v>
       </c>
-      <c r="T72" t="s">
-        <v>237</v>
-      </c>
-      <c r="U72">
-        <v>0.35</v>
-      </c>
-      <c r="V72">
-        <v>27</v>
-      </c>
-      <c r="W72" t="s">
-        <v>226</v>
-      </c>
-      <c r="X72" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y72" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z72" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA72" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB72" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>64</v>
       </c>
@@ -7888,7 +8673,7 @@
         <v>133</v>
       </c>
       <c r="F73" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G73" t="s">
         <v>25</v>
@@ -7909,46 +8694,55 @@
         <v>0</v>
       </c>
       <c r="M73" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N73" t="s">
         <v>80</v>
       </c>
       <c r="O73" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="P73">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q73" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="R73">
         <v>0.1</v>
       </c>
       <c r="S73">
-        <v>2</v>
-      </c>
-      <c r="T73" t="s">
-        <v>221</v>
-      </c>
-      <c r="U73">
+        <v>1.5</v>
+      </c>
+      <c r="T73">
+        <v>0.041</v>
+      </c>
+      <c r="U73" t="s">
+        <v>291</v>
+      </c>
+      <c r="V73">
+        <v>1.03</v>
+      </c>
+      <c r="W73" t="s">
+        <v>227</v>
+      </c>
+      <c r="X73">
         <v>0.7</v>
       </c>
-      <c r="V73">
-        <v>9</v>
-      </c>
-      <c r="W73" t="s">
-        <v>226</v>
-      </c>
-      <c r="X73" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y73" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y73">
+        <v>8</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB73" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>64</v>
       </c>
@@ -7965,16 +8759,16 @@
         <v>138</v>
       </c>
       <c r="F74" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G74" t="s">
         <v>25</v>
       </c>
       <c r="H74" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="I74" t="s">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="J74" t="s">
         <v>80</v>
@@ -7983,49 +8777,58 @@
         <v>0.7</v>
       </c>
       <c r="L74">
-        <v>32.9</v>
+        <v>24.5</v>
       </c>
       <c r="M74" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N74" t="s">
         <v>80</v>
       </c>
       <c r="O74" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="P74">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q74" t="s">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="R74">
         <v>0.6</v>
       </c>
       <c r="S74">
-        <v>12</v>
-      </c>
-      <c r="T74" t="s">
-        <v>221</v>
-      </c>
-      <c r="U74">
+        <v>9</v>
+      </c>
+      <c r="T74">
+        <v>0.533</v>
+      </c>
+      <c r="U74" t="s">
+        <v>296</v>
+      </c>
+      <c r="V74">
+        <v>13.32</v>
+      </c>
+      <c r="W74" t="s">
+        <v>227</v>
+      </c>
+      <c r="X74">
         <v>0.7</v>
       </c>
-      <c r="V74">
+      <c r="Y74">
         <v>52</v>
       </c>
-      <c r="W74" t="s">
-        <v>226</v>
-      </c>
-      <c r="X74" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y74" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z74" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB74" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>64</v>
       </c>
@@ -8042,7 +8845,7 @@
         <v>143</v>
       </c>
       <c r="F75" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G75" t="s">
         <v>25</v>
@@ -8063,46 +8866,55 @@
         <v>0</v>
       </c>
       <c r="M75" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N75" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="O75" t="s">
         <v>80</v>
       </c>
       <c r="P75">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q75" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R75">
         <v>1</v>
       </c>
       <c r="S75">
-        <v>20</v>
-      </c>
-      <c r="T75" t="s">
-        <v>221</v>
-      </c>
-      <c r="U75">
+        <v>15</v>
+      </c>
+      <c r="T75">
+        <v>0.038</v>
+      </c>
+      <c r="U75" t="s">
+        <v>291</v>
+      </c>
+      <c r="V75">
+        <v>0.95</v>
+      </c>
+      <c r="W75" t="s">
+        <v>227</v>
+      </c>
+      <c r="X75">
         <v>0.7</v>
       </c>
-      <c r="V75">
-        <v>50</v>
-      </c>
-      <c r="W75" t="s">
-        <v>226</v>
-      </c>
-      <c r="X75" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y75" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y75">
+        <v>39</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB75" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>64</v>
       </c>
@@ -8119,7 +8931,7 @@
         <v>149</v>
       </c>
       <c r="F76" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G76" t="s">
         <v>25</v>
@@ -8140,46 +8952,55 @@
         <v>0</v>
       </c>
       <c r="M76" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N76" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="O76" t="s">
         <v>80</v>
       </c>
       <c r="P76">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q76" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R76">
         <v>1</v>
       </c>
       <c r="S76">
-        <v>20</v>
-      </c>
-      <c r="T76" t="s">
-        <v>221</v>
-      </c>
-      <c r="U76">
+        <v>15</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76" t="s">
+        <v>80</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76" t="s">
+        <v>227</v>
+      </c>
+      <c r="X76">
         <v>0.7</v>
       </c>
-      <c r="V76">
-        <v>50</v>
-      </c>
-      <c r="W76" t="s">
-        <v>226</v>
-      </c>
-      <c r="X76" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y76" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y76">
+        <v>38</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA76" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB76" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>64</v>
       </c>
@@ -8196,7 +9017,7 @@
         <v>155</v>
       </c>
       <c r="F77" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G77" t="s">
         <v>25</v>
@@ -8217,46 +9038,55 @@
         <v>0</v>
       </c>
       <c r="M77" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N77" t="s">
         <v>80</v>
       </c>
       <c r="O77" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="P77">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q77" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R77">
         <v>1</v>
       </c>
       <c r="S77">
+        <v>15</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77" t="s">
+        <v>80</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77" t="s">
+        <v>227</v>
+      </c>
+      <c r="X77">
+        <v>0.7</v>
+      </c>
+      <c r="Y77">
         <v>20</v>
       </c>
-      <c r="T77" t="s">
-        <v>221</v>
-      </c>
-      <c r="U77">
-        <v>0.7</v>
-      </c>
-      <c r="V77">
-        <v>27</v>
-      </c>
-      <c r="W77" t="s">
-        <v>226</v>
-      </c>
-      <c r="X77" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y77" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z77" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA77" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB77" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>64</v>
       </c>
@@ -8273,7 +9103,7 @@
         <v>160</v>
       </c>
       <c r="F78" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G78" t="s">
         <v>25</v>
@@ -8294,46 +9124,55 @@
         <v>0</v>
       </c>
       <c r="M78" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N78" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="O78" t="s">
         <v>80</v>
       </c>
       <c r="P78">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q78" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R78">
         <v>1</v>
       </c>
       <c r="S78">
-        <v>20</v>
-      </c>
-      <c r="T78" t="s">
-        <v>221</v>
-      </c>
-      <c r="U78">
+        <v>15</v>
+      </c>
+      <c r="T78">
+        <v>0.048</v>
+      </c>
+      <c r="U78" t="s">
+        <v>291</v>
+      </c>
+      <c r="V78">
+        <v>1.2</v>
+      </c>
+      <c r="W78" t="s">
+        <v>227</v>
+      </c>
+      <c r="X78">
         <v>0.7</v>
       </c>
-      <c r="V78">
-        <v>50</v>
-      </c>
-      <c r="W78" t="s">
-        <v>226</v>
-      </c>
-      <c r="X78" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y78" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y78">
+        <v>39</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB78" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>64</v>
       </c>
@@ -8350,7 +9189,7 @@
         <v>165</v>
       </c>
       <c r="F79" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G79" t="s">
         <v>25</v>
@@ -8368,49 +9207,58 @@
         <v>1</v>
       </c>
       <c r="L79">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="M79" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N79" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="O79" t="s">
         <v>80</v>
       </c>
       <c r="P79">
-        <v>30.03</v>
+        <v>22.75</v>
       </c>
       <c r="Q79" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R79">
         <v>1</v>
       </c>
       <c r="S79">
-        <v>20</v>
-      </c>
-      <c r="T79" t="s">
-        <v>231</v>
-      </c>
-      <c r="U79">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="T79">
+        <v>1</v>
+      </c>
+      <c r="U79" t="s">
+        <v>297</v>
       </c>
       <c r="V79">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="W79" t="s">
-        <v>234</v>
-      </c>
-      <c r="X79" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y79" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+      <c r="X79">
+        <v>1</v>
+      </c>
+      <c r="Y79">
+        <v>98</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB79" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>74</v>
       </c>
@@ -8427,7 +9275,7 @@
         <v>96</v>
       </c>
       <c r="F80" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G80" t="s">
         <v>25</v>
@@ -8436,58 +9284,67 @@
         <v>80</v>
       </c>
       <c r="I80" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="J80" t="s">
-        <v>263</v>
+        <v>299</v>
       </c>
       <c r="K80">
         <v>0.1</v>
       </c>
       <c r="L80">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="M80" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N80" t="s">
         <v>80</v>
       </c>
       <c r="O80" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="P80">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q80" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R80">
         <v>1</v>
       </c>
       <c r="S80">
-        <v>20</v>
-      </c>
-      <c r="T80" t="s">
-        <v>221</v>
-      </c>
-      <c r="U80">
+        <v>15</v>
+      </c>
+      <c r="T80">
+        <v>0</v>
+      </c>
+      <c r="U80" t="s">
+        <v>80</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80" t="s">
+        <v>227</v>
+      </c>
+      <c r="X80">
         <v>0.7</v>
       </c>
-      <c r="V80">
-        <v>32</v>
-      </c>
-      <c r="W80" t="s">
-        <v>226</v>
-      </c>
-      <c r="X80" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y80" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y80">
+        <v>24</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA80" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB80" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>74</v>
       </c>
@@ -8504,7 +9361,7 @@
         <v>105</v>
       </c>
       <c r="F81" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G81" t="s">
         <v>25</v>
@@ -8525,46 +9382,55 @@
         <v>0</v>
       </c>
       <c r="M81" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N81" t="s">
         <v>80</v>
       </c>
       <c r="O81" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="P81">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q81" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R81">
         <v>1</v>
       </c>
       <c r="S81">
-        <v>20</v>
-      </c>
-      <c r="T81" t="s">
-        <v>221</v>
-      </c>
-      <c r="U81">
+        <v>15</v>
+      </c>
+      <c r="T81">
+        <v>0.129</v>
+      </c>
+      <c r="U81" t="s">
+        <v>301</v>
+      </c>
+      <c r="V81">
+        <v>3.24</v>
+      </c>
+      <c r="W81" t="s">
+        <v>227</v>
+      </c>
+      <c r="X81">
         <v>0.7</v>
       </c>
-      <c r="V81">
-        <v>27</v>
-      </c>
-      <c r="W81" t="s">
-        <v>226</v>
-      </c>
-      <c r="X81" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y81" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y81">
+        <v>23</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB81" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>74</v>
       </c>
@@ -8581,67 +9447,76 @@
         <v>109</v>
       </c>
       <c r="F82" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G82" t="s">
         <v>25</v>
       </c>
       <c r="H82" t="s">
-        <v>265</v>
+        <v>302</v>
       </c>
       <c r="I82" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="J82" t="s">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="K82">
         <v>0.6</v>
       </c>
       <c r="L82">
-        <v>28.2</v>
+        <v>21</v>
       </c>
       <c r="M82" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N82" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O82" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="P82">
-        <v>18.48</v>
+        <v>14</v>
       </c>
       <c r="Q82" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R82">
         <v>1</v>
       </c>
       <c r="S82">
-        <v>20</v>
-      </c>
-      <c r="T82" t="s">
-        <v>231</v>
-      </c>
-      <c r="U82">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="T82">
+        <v>0.227</v>
+      </c>
+      <c r="U82" t="s">
+        <v>305</v>
       </c>
       <c r="V82">
-        <v>67</v>
+        <v>5.67</v>
       </c>
       <c r="W82" t="s">
-        <v>222</v>
-      </c>
-      <c r="X82" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y82" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+      <c r="X82">
+        <v>1</v>
+      </c>
+      <c r="Y82">
+        <v>56</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA82" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB82" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>74</v>
       </c>
@@ -8658,67 +9533,76 @@
         <v>117</v>
       </c>
       <c r="F83" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G83" t="s">
         <v>25</v>
       </c>
       <c r="H83" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="I83" t="s">
         <v>80</v>
       </c>
       <c r="J83" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="K83">
         <v>0.25</v>
       </c>
       <c r="L83">
-        <v>11.75</v>
+        <v>8.75</v>
       </c>
       <c r="M83" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N83" t="s">
         <v>80</v>
       </c>
       <c r="O83" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="P83">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q83" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R83">
         <v>1</v>
       </c>
       <c r="S83">
-        <v>20</v>
-      </c>
-      <c r="T83" t="s">
-        <v>221</v>
-      </c>
-      <c r="U83">
+        <v>15</v>
+      </c>
+      <c r="T83">
+        <v>0.256</v>
+      </c>
+      <c r="U83" t="s">
+        <v>306</v>
+      </c>
+      <c r="V83">
+        <v>6.39</v>
+      </c>
+      <c r="W83" t="s">
+        <v>227</v>
+      </c>
+      <c r="X83">
         <v>0.7</v>
       </c>
-      <c r="V83">
-        <v>39</v>
-      </c>
-      <c r="W83" t="s">
-        <v>226</v>
-      </c>
-      <c r="X83" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y83" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y83">
+        <v>35</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA83" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB83" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>74</v>
       </c>
@@ -8735,67 +9619,76 @@
         <v>123</v>
       </c>
       <c r="F84" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G84" t="s">
         <v>25</v>
       </c>
       <c r="H84" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="I84" t="s">
         <v>80</v>
       </c>
       <c r="J84" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="K84">
         <v>0.75</v>
       </c>
       <c r="L84">
-        <v>35.25</v>
+        <v>26.25</v>
       </c>
       <c r="M84" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N84" t="s">
         <v>80</v>
       </c>
       <c r="O84" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="P84">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q84" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R84">
         <v>1</v>
       </c>
       <c r="S84">
-        <v>20</v>
-      </c>
-      <c r="T84" t="s">
-        <v>237</v>
-      </c>
-      <c r="U84">
+        <v>15</v>
+      </c>
+      <c r="T84">
+        <v>0.714</v>
+      </c>
+      <c r="U84" t="s">
+        <v>307</v>
+      </c>
+      <c r="V84">
+        <v>17.85</v>
+      </c>
+      <c r="W84" t="s">
+        <v>247</v>
+      </c>
+      <c r="X84">
         <v>0.35</v>
       </c>
-      <c r="V84">
-        <v>62</v>
-      </c>
-      <c r="W84" t="s">
-        <v>222</v>
-      </c>
-      <c r="X84" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y84" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y84">
+        <v>64</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>243</v>
+      </c>
+      <c r="AA84" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>74</v>
       </c>
@@ -8812,7 +9705,7 @@
         <v>129</v>
       </c>
       <c r="F85" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G85" t="s">
         <v>25</v>
@@ -8830,49 +9723,58 @@
         <v>1</v>
       </c>
       <c r="L85">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="M85" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N85" t="s">
         <v>80</v>
       </c>
       <c r="O85" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="P85">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q85" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R85">
         <v>1</v>
       </c>
       <c r="S85">
-        <v>20</v>
-      </c>
-      <c r="T85" t="s">
-        <v>237</v>
-      </c>
-      <c r="U85">
+        <v>15</v>
+      </c>
+      <c r="T85">
+        <v>1</v>
+      </c>
+      <c r="U85" t="s">
+        <v>308</v>
+      </c>
+      <c r="V85">
+        <v>25</v>
+      </c>
+      <c r="W85" t="s">
+        <v>247</v>
+      </c>
+      <c r="X85">
         <v>0.35</v>
       </c>
-      <c r="V85">
-        <v>74</v>
-      </c>
-      <c r="W85" t="s">
-        <v>222</v>
-      </c>
-      <c r="X85" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y85" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y85">
+        <v>80</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA85" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB85" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>74</v>
       </c>
@@ -8889,7 +9791,7 @@
         <v>133</v>
       </c>
       <c r="F86" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G86" t="s">
         <v>25</v>
@@ -8898,58 +9800,67 @@
         <v>80</v>
       </c>
       <c r="I86" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="J86" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="K86">
         <v>0.08</v>
       </c>
       <c r="L86">
-        <v>3.76</v>
+        <v>2.8</v>
       </c>
       <c r="M86" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N86" t="s">
         <v>80</v>
       </c>
       <c r="O86" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="P86">
-        <v>6.93</v>
+        <v>5.25</v>
       </c>
       <c r="Q86" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R86">
         <v>1</v>
       </c>
       <c r="S86">
-        <v>20</v>
-      </c>
-      <c r="T86" t="s">
-        <v>221</v>
-      </c>
-      <c r="U86">
+        <v>15</v>
+      </c>
+      <c r="T86">
+        <v>0</v>
+      </c>
+      <c r="U86" t="s">
+        <v>80</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86" t="s">
+        <v>227</v>
+      </c>
+      <c r="X86">
         <v>0.7</v>
       </c>
-      <c r="V86">
-        <v>31</v>
-      </c>
-      <c r="W86" t="s">
-        <v>226</v>
-      </c>
-      <c r="X86" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y86" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y86">
+        <v>23</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA86" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB86" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>74</v>
       </c>
@@ -8966,7 +9877,7 @@
         <v>138</v>
       </c>
       <c r="F87" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G87" t="s">
         <v>25</v>
@@ -8975,58 +9886,67 @@
         <v>80</v>
       </c>
       <c r="I87" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="J87" t="s">
-        <v>269</v>
+        <v>310</v>
       </c>
       <c r="K87">
         <v>0.1</v>
       </c>
       <c r="L87">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="M87" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N87" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O87" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="P87">
-        <v>18.48</v>
+        <v>14</v>
       </c>
       <c r="Q87" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R87">
         <v>1</v>
       </c>
       <c r="S87">
-        <v>20</v>
-      </c>
-      <c r="T87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U87">
+        <v>15</v>
+      </c>
+      <c r="T87">
+        <v>0</v>
+      </c>
+      <c r="U87" t="s">
+        <v>80</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87" t="s">
+        <v>227</v>
+      </c>
+      <c r="X87">
         <v>0.7</v>
       </c>
-      <c r="V87">
-        <v>43</v>
-      </c>
-      <c r="W87" t="s">
-        <v>226</v>
-      </c>
-      <c r="X87" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y87" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y87">
+        <v>33</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB87" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>74</v>
       </c>
@@ -9043,7 +9963,7 @@
         <v>143</v>
       </c>
       <c r="F88" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G88" t="s">
         <v>25</v>
@@ -9064,46 +9984,55 @@
         <v>0</v>
       </c>
       <c r="M88" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N88" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O88" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="P88">
-        <v>18.48</v>
+        <v>14</v>
       </c>
       <c r="Q88" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R88">
         <v>1</v>
       </c>
       <c r="S88">
-        <v>20</v>
-      </c>
-      <c r="T88" t="s">
-        <v>221</v>
-      </c>
-      <c r="U88">
+        <v>15</v>
+      </c>
+      <c r="T88">
+        <v>0</v>
+      </c>
+      <c r="U88" t="s">
+        <v>80</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88" t="s">
+        <v>227</v>
+      </c>
+      <c r="X88">
         <v>0.7</v>
       </c>
-      <c r="V88">
-        <v>38</v>
-      </c>
-      <c r="W88" t="s">
-        <v>226</v>
-      </c>
-      <c r="X88" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y88" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y88">
+        <v>29</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA88" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB88" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>74</v>
       </c>
@@ -9120,7 +10049,7 @@
         <v>149</v>
       </c>
       <c r="F89" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G89" t="s">
         <v>25</v>
@@ -9141,46 +10070,55 @@
         <v>0</v>
       </c>
       <c r="M89" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N89" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O89" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="P89">
-        <v>18.48</v>
+        <v>14</v>
       </c>
       <c r="Q89" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R89">
         <v>1</v>
       </c>
       <c r="S89">
-        <v>20</v>
-      </c>
-      <c r="T89" t="s">
-        <v>221</v>
-      </c>
-      <c r="U89">
+        <v>15</v>
+      </c>
+      <c r="T89">
+        <v>0</v>
+      </c>
+      <c r="U89" t="s">
+        <v>80</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89" t="s">
+        <v>227</v>
+      </c>
+      <c r="X89">
         <v>0.7</v>
       </c>
-      <c r="V89">
-        <v>38</v>
-      </c>
-      <c r="W89" t="s">
-        <v>226</v>
-      </c>
-      <c r="X89" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y89" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y89">
+        <v>29</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA89" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB89" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>74</v>
       </c>
@@ -9197,7 +10135,7 @@
         <v>155</v>
       </c>
       <c r="F90" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G90" t="s">
         <v>25</v>
@@ -9218,46 +10156,55 @@
         <v>0</v>
       </c>
       <c r="M90" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N90" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O90" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="P90">
-        <v>18.48</v>
+        <v>14</v>
       </c>
       <c r="Q90" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R90">
         <v>1</v>
       </c>
       <c r="S90">
-        <v>20</v>
-      </c>
-      <c r="T90" t="s">
-        <v>221</v>
-      </c>
-      <c r="U90">
+        <v>15</v>
+      </c>
+      <c r="T90">
+        <v>0</v>
+      </c>
+      <c r="U90" t="s">
+        <v>80</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90" t="s">
+        <v>227</v>
+      </c>
+      <c r="X90">
         <v>0.7</v>
       </c>
-      <c r="V90">
-        <v>38</v>
-      </c>
-      <c r="W90" t="s">
-        <v>226</v>
-      </c>
-      <c r="X90" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y90" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y90">
+        <v>29</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA90" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB90" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>74</v>
       </c>
@@ -9274,7 +10221,7 @@
         <v>160</v>
       </c>
       <c r="F91" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G91" t="s">
         <v>25</v>
@@ -9295,46 +10242,55 @@
         <v>0</v>
       </c>
       <c r="M91" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N91" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O91" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="P91">
-        <v>18.48</v>
+        <v>14</v>
       </c>
       <c r="Q91" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R91">
         <v>1</v>
       </c>
       <c r="S91">
-        <v>20</v>
-      </c>
-      <c r="T91" t="s">
-        <v>221</v>
-      </c>
-      <c r="U91">
+        <v>15</v>
+      </c>
+      <c r="T91">
+        <v>0</v>
+      </c>
+      <c r="U91" t="s">
+        <v>80</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91" t="s">
+        <v>227</v>
+      </c>
+      <c r="X91">
         <v>0.7</v>
       </c>
-      <c r="V91">
-        <v>38</v>
-      </c>
-      <c r="W91" t="s">
-        <v>226</v>
-      </c>
-      <c r="X91" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y91" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y91">
+        <v>29</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA91" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB91" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>74</v>
       </c>
@@ -9351,7 +10307,7 @@
         <v>165</v>
       </c>
       <c r="F92" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G92" t="s">
         <v>25</v>
@@ -9372,43 +10328,52 @@
         <v>0</v>
       </c>
       <c r="M92" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N92" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="O92" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="P92">
-        <v>18.48</v>
+        <v>14</v>
       </c>
       <c r="Q92" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R92">
         <v>1</v>
       </c>
       <c r="S92">
-        <v>20</v>
-      </c>
-      <c r="T92" t="s">
-        <v>231</v>
-      </c>
-      <c r="U92">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="T92">
+        <v>0</v>
+      </c>
+      <c r="U92" t="s">
+        <v>80</v>
       </c>
       <c r="V92">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="W92" t="s">
-        <v>226</v>
-      </c>
-      <c r="X92" t="s">
-        <v>216</v>
-      </c>
-      <c r="Y92" t="s">
-        <v>216</v>
+        <v>239</v>
+      </c>
+      <c r="X92">
+        <v>1</v>
+      </c>
+      <c r="Y92">
+        <v>29</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>233</v>
+      </c>
+      <c r="AA92" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB92" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
